--- a/workbooks/scenarios/ShowerRAGScenarios.xlsx
+++ b/workbooks/scenarios/ShowerRAGScenarios.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S46"/>
+  <dimension ref="A1:S61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,34 +515,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>How long should my showers be?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Blue Bell, PA</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="I2" t="n">
         <v>5</v>
@@ -551,10 +551,10 @@
         <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>8.380000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>9.26</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="M2" t="n">
         <v>7.43</v>
@@ -563,51 +563,51 @@
         <v>3.48</v>
       </c>
       <c r="O2" t="n">
-        <v>7.763</v>
+        <v>8.2645</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.943973094425551</v>
+        <v>1.06147102298792</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3693548879408547</v>
+        <v>0.2016794943677048</v>
       </c>
       <c r="S2" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>How long should my showers be?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Blue Bell, PA</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="I3" t="n">
         <v>8</v>
@@ -616,10 +616,10 @@
         <v>8</v>
       </c>
       <c r="K3" t="n">
-        <v>6.73</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>8.15</v>
+        <v>8.74</v>
       </c>
       <c r="M3" t="n">
         <v>9.960000000000001</v>
@@ -628,51 +628,51 @@
         <v>7.6</v>
       </c>
       <c r="O3" t="n">
-        <v>8.003500000000001</v>
+        <v>8.807</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.110356951080881</v>
+        <v>1.698353636780672</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5909678207053675</v>
+        <v>0.3226871909883277</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>How long should my showers be?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Blue Bell, PA</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="I4" t="n">
         <v>12</v>
@@ -681,10 +681,10 @@
         <v>12</v>
       </c>
       <c r="K4" t="n">
-        <v>4.54</v>
+        <v>7.53</v>
       </c>
       <c r="L4" t="n">
-        <v>6.67</v>
+        <v>7.56</v>
       </c>
       <c r="M4" t="n">
         <v>9.210000000000001</v>
@@ -693,433 +693,433 @@
         <v>6.69</v>
       </c>
       <c r="O4" t="n">
-        <v>6.542</v>
+        <v>7.7505</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.665535426621322</v>
+        <v>2.547530455171008</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8864517310580511</v>
+        <v>0.4840307864824915</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>How long should my showers be?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Media, PA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>2.5</v>
       </c>
       <c r="F5" t="n">
-        <v>280</v>
+        <v>255</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>7.37</v>
+        <v>9.24</v>
       </c>
       <c r="L5" t="n">
-        <v>8.52</v>
+        <v>9.26</v>
       </c>
       <c r="M5" t="n">
-        <v>9.32</v>
+        <v>7.43</v>
       </c>
       <c r="N5" t="n">
-        <v>3.07</v>
+        <v>3.48</v>
       </c>
       <c r="O5" t="n">
-        <v>7.517499999999999</v>
+        <v>8.020999999999999</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.656763229048253</v>
+        <v>1.3268387787349</v>
       </c>
       <c r="R5" t="n">
-        <v>0.504785013519168</v>
+        <v>0.2520993679596309</v>
       </c>
       <c r="S5" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>How long should my showers be?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Media, PA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
         <v>2.5</v>
       </c>
       <c r="F6" t="n">
-        <v>280</v>
+        <v>255</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K6" t="n">
-        <v>5.77</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>7.41</v>
+        <v>8.15</v>
       </c>
       <c r="M6" t="n">
-        <v>8.82</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>5.71</v>
+        <v>4.64</v>
       </c>
       <c r="O6" t="n">
-        <v>6.944999999999999</v>
+        <v>7.976499999999999</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.795376041497505</v>
+        <v>2.12294204597584</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7211214478845259</v>
+        <v>0.4033589887354095</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>How long should my showers be?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Media, PA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>2.5</v>
       </c>
       <c r="F7" t="n">
-        <v>280</v>
+        <v>255</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="I7" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J7" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1</v>
+        <v>6.63</v>
       </c>
       <c r="L7" t="n">
-        <v>5.56</v>
+        <v>6.67</v>
       </c>
       <c r="M7" t="n">
-        <v>5.53</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>5.19</v>
+        <v>6.69</v>
       </c>
       <c r="O7" t="n">
-        <v>4.7605</v>
+        <v>7.169</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.693064062246257</v>
+        <v>3.18441306896376</v>
       </c>
       <c r="R7" t="n">
-        <v>1.081682171826789</v>
+        <v>0.6050384831031144</v>
       </c>
       <c r="S7" t="n">
-        <v>37.5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>What's the ideal shower length?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lancaster, PA</t>
+          <t>Indiana, PA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>250</v>
+        <v>155</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>8.9</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>9.33</v>
+        <v>9.93</v>
       </c>
       <c r="M8" t="n">
-        <v>8.42</v>
+        <v>6.34</v>
       </c>
       <c r="N8" t="n">
-        <v>5.01</v>
+        <v>2.86</v>
       </c>
       <c r="O8" t="n">
-        <v>8.370999999999999</v>
+        <v>8.0345</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.569989699117017</v>
+        <v>1.115778842768697</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2982980428322332</v>
+        <v>0.2119979801260525</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>What's the ideal shower length?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lancaster, PA</t>
+          <t>Indiana, PA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>250</v>
+        <v>155</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>7.8</v>
+        <v>8.76</v>
       </c>
       <c r="L9" t="n">
-        <v>8.44</v>
+        <v>9.33</v>
       </c>
       <c r="M9" t="n">
-        <v>9.779999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="N9" t="n">
-        <v>5.19</v>
+        <v>5.01</v>
       </c>
       <c r="O9" t="n">
-        <v>8.028499999999999</v>
+        <v>8.328999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.354984548675525</v>
+        <v>1.673668264153046</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4474470642483497</v>
+        <v>0.3179969701890787</v>
       </c>
       <c r="S9" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>What's the ideal shower length?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lancaster, PA</t>
+          <t>Indiana, PA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>250</v>
+        <v>155</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="I10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>6.69</v>
+        <v>7.19</v>
       </c>
       <c r="L10" t="n">
-        <v>7.56</v>
+        <v>8.15</v>
       </c>
       <c r="M10" t="n">
-        <v>9.210000000000001</v>
+        <v>9.59</v>
       </c>
       <c r="N10" t="n">
-        <v>6.69</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>7.498500000000001</v>
+        <v>8.195</v>
       </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.139979398234034</v>
+        <v>2.789447106921743</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5965960856644664</v>
+        <v>0.5299949503151312</v>
       </c>
       <c r="S10" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>How long should my showers be?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Harrisburg, PA</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
         <v>2.5</v>
       </c>
       <c r="F11" t="n">
-        <v>190</v>
+        <v>245</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1127,64 +1127,64 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>9.24</v>
+        <v>9.82</v>
       </c>
       <c r="L11" t="n">
-        <v>9.26</v>
+        <v>10</v>
       </c>
       <c r="M11" t="n">
-        <v>7.43</v>
+        <v>5.13</v>
       </c>
       <c r="N11" t="n">
-        <v>3.48</v>
+        <v>2.2</v>
       </c>
       <c r="O11" t="n">
-        <v>8.020999999999999</v>
+        <v>7.802</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.3268387787349</v>
+        <v>0.916444458800617</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2520993679596309</v>
+        <v>0.1741244471721172</v>
       </c>
       <c r="S11" t="n">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>How long should my showers be?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Harrisburg, PA</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
         <v>2.5</v>
       </c>
       <c r="F12" t="n">
-        <v>190</v>
+        <v>245</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1192,64 +1192,64 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>8.5</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>8.52</v>
+        <v>9.26</v>
       </c>
       <c r="M12" t="n">
-        <v>9.32</v>
+        <v>7.43</v>
       </c>
       <c r="N12" t="n">
-        <v>6.37</v>
+        <v>3.48</v>
       </c>
       <c r="O12" t="n">
-        <v>8.3515</v>
+        <v>7.937</v>
       </c>
       <c r="P12" t="n">
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.85757429022886</v>
+        <v>1.527407431334362</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3529391151434833</v>
+        <v>0.2902074119535287</v>
       </c>
       <c r="S12" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>How long should my showers be?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Harrisburg, PA</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
         <v>2.5</v>
       </c>
       <c r="F13" t="n">
-        <v>190</v>
+        <v>245</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1257,64 +1257,64 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="I13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K13" t="n">
-        <v>7.38</v>
+        <v>7.67</v>
       </c>
       <c r="L13" t="n">
-        <v>7.41</v>
+        <v>8.15</v>
       </c>
       <c r="M13" t="n">
-        <v>9.59</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>5.71</v>
+        <v>4.64</v>
       </c>
       <c r="O13" t="n">
-        <v>7.581999999999999</v>
+        <v>7.841499999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.6536775574698</v>
+        <v>2.443851890134979</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5041987359192619</v>
+        <v>0.464331859125646</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
+        <v>62</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>How long should I shower?</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>West Mifflin, PA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>4</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>How long should my showers be?</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Allentown, PA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>3</v>
-      </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
-        <v>260</v>
+        <v>295</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1322,64 +1322,64 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>8.029999999999999</v>
+        <v>9.69</v>
       </c>
       <c r="L14" t="n">
-        <v>8.74</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>9.960000000000001</v>
+        <v>5.13</v>
       </c>
       <c r="N14" t="n">
-        <v>7.6</v>
+        <v>2.2</v>
       </c>
       <c r="O14" t="n">
-        <v>8.6</v>
+        <v>7.685999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.192061089333193</v>
+        <v>1.010866009101286</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4164916069733066</v>
+        <v>0.1920645417292444</v>
       </c>
       <c r="S14" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
+        <v>62</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>How long should I shower?</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>West Mifflin, PA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>4</v>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>How long should my showers be?</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Allentown, PA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>3</v>
-      </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>260</v>
+        <v>295</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1387,64 +1387,64 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="I15" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>7.25</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>8.15</v>
+        <v>9.33</v>
       </c>
       <c r="M15" t="n">
-        <v>9.59</v>
+        <v>6.34</v>
       </c>
       <c r="N15" t="n">
-        <v>5.71</v>
+        <v>2.86</v>
       </c>
       <c r="O15" t="n">
-        <v>7.802</v>
+        <v>7.7255</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.740076361666491</v>
+        <v>1.347821345468382</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5206145087166333</v>
+        <v>0.2560860556389926</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
+        <v>62</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>How long should I shower?</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>West Mifflin, PA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>4</v>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>How long should my showers be?</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Allentown, PA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>3</v>
-      </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>260</v>
+        <v>295</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1452,468 +1452,468 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="I16" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J16" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K16" t="n">
-        <v>6.1</v>
+        <v>8.27</v>
       </c>
       <c r="L16" t="n">
-        <v>7.26</v>
+        <v>8.44</v>
       </c>
       <c r="M16" t="n">
-        <v>9.01</v>
+        <v>8.42</v>
       </c>
       <c r="N16" t="n">
-        <v>6.21</v>
+        <v>1.51</v>
       </c>
       <c r="O16" t="n">
-        <v>7.1045</v>
+        <v>7.345499999999999</v>
       </c>
       <c r="P16" t="n">
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.562099270166438</v>
+        <v>2.021732018202572</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6767988613316234</v>
+        <v>0.3841290834584888</v>
       </c>
       <c r="S16" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>For a high-flow showerhead in Carlisle, what duration is reasonable?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Carlisle, PA</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Single-family</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>8.630000000000001</v>
+        <v>9.77</v>
       </c>
       <c r="L17" t="n">
-        <v>9.33</v>
+        <v>10</v>
       </c>
       <c r="M17" t="n">
-        <v>6.34</v>
+        <v>5.13</v>
       </c>
       <c r="N17" t="n">
-        <v>2.86</v>
+        <v>2.2</v>
       </c>
       <c r="O17" t="n">
-        <v>7.5515</v>
+        <v>7.786999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.7625356056125</v>
+        <v>0.955323920689128</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3348817650663749</v>
+        <v>0.1815115449309343</v>
       </c>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>For a high-flow showerhead in Carlisle, what duration is reasonable?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Carlisle, PA</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Single-family</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K18" t="n">
-        <v>6.77</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>8</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>9.32</v>
+        <v>7.43</v>
       </c>
       <c r="N18" t="n">
-        <v>3.07</v>
+        <v>3.48</v>
       </c>
       <c r="O18" t="n">
-        <v>7.155499999999999</v>
+        <v>8.039499999999999</v>
       </c>
       <c r="P18" t="n">
         <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.084437309821875</v>
+        <v>1.59220653448188</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5860430888661562</v>
+        <v>0.3025192415515572</v>
       </c>
       <c r="S18" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>For a high-flow showerhead in Carlisle, what duration is reasonable?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Carlisle, PA</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Single-family</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K19" t="n">
-        <v>4.91</v>
+        <v>7.53</v>
       </c>
       <c r="L19" t="n">
-        <v>6.67</v>
+        <v>8.74</v>
       </c>
       <c r="M19" t="n">
-        <v>9.59</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>5.71</v>
+        <v>7.6</v>
       </c>
       <c r="O19" t="n">
-        <v>6.582</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.406339014031249</v>
+        <v>2.547530455171008</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8372044126659374</v>
+        <v>0.4840307864824915</v>
       </c>
       <c r="S19" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>For a high-flow showerhead and larger household in DuBois, what duration is best?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DuBois, PA</t>
+          <t>Exton, PA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="F20" t="n">
-        <v>350</v>
+        <v>260</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="I20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>7.69</v>
+        <v>9.82</v>
       </c>
       <c r="L20" t="n">
-        <v>8.74</v>
+        <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>6.34</v>
+        <v>5.13</v>
       </c>
       <c r="N20" t="n">
-        <v>1.51</v>
+        <v>2.2</v>
       </c>
       <c r="O20" t="n">
-        <v>6.860499999999999</v>
+        <v>7.802</v>
       </c>
       <c r="P20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.429040666558403</v>
+        <v>0.916444458800617</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4615177266460965</v>
+        <v>0.1741244471721172</v>
       </c>
       <c r="S20" t="n">
-        <v>16</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>For a high-flow showerhead and larger household in DuBois, what duration is best?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DuBois, PA</t>
+          <t>Exton, PA</t>
         </is>
       </c>
       <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>260</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Condo</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>62</v>
+      </c>
+      <c r="I21" t="n">
         <v>5</v>
       </c>
-      <c r="E21" t="n">
-        <v>4</v>
-      </c>
-      <c r="F21" t="n">
-        <v>350</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Single-family</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>38</v>
-      </c>
-      <c r="I21" t="n">
-        <v>7</v>
-      </c>
       <c r="J21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K21" t="n">
-        <v>5.13</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>6.96</v>
+        <v>9.26</v>
       </c>
       <c r="M21" t="n">
-        <v>9.32</v>
+        <v>7.43</v>
       </c>
       <c r="N21" t="n">
-        <v>3.07</v>
+        <v>3.48</v>
       </c>
       <c r="O21" t="n">
-        <v>6.299499999999999</v>
+        <v>7.937</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.250821166477206</v>
+        <v>1.527407431334362</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8076560216306691</v>
+        <v>0.2902074119535287</v>
       </c>
       <c r="S21" t="n">
-        <v>28</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>For a high-flow showerhead and larger household in DuBois, what duration is best?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DuBois, PA</t>
+          <t>Exton, PA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="F22" t="n">
-        <v>350</v>
+        <v>260</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="I22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K22" t="n">
-        <v>2.56</v>
+        <v>7.67</v>
       </c>
       <c r="L22" t="n">
-        <v>5.19</v>
+        <v>8.15</v>
       </c>
       <c r="M22" t="n">
-        <v>8.82</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>5.71</v>
+        <v>4.64</v>
       </c>
       <c r="O22" t="n">
-        <v>5.205</v>
+        <v>7.841499999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.072601666396007</v>
+        <v>2.443851890134979</v>
       </c>
       <c r="R22" t="n">
-        <v>1.153794316615241</v>
+        <v>0.464331859125646</v>
       </c>
       <c r="S22" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>What's the ideal shower length?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Gettysburg, PA</t>
+          <t>Pottstown, PA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
         <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>235</v>
+        <v>195</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
         <v>10</v>
@@ -1922,554 +1922,554 @@
         <v>10</v>
       </c>
       <c r="M23" t="n">
-        <v>0.24</v>
+        <v>5.13</v>
       </c>
       <c r="N23" t="n">
-        <v>1.51</v>
+        <v>2.2</v>
       </c>
       <c r="O23" t="n">
-        <v>6.7745</v>
+        <v>7.856</v>
       </c>
       <c r="P23" t="n">
         <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.2616649498528361</v>
+        <v>0.636882613792752</v>
       </c>
       <c r="R23" t="n">
-        <v>0.0497163404720388</v>
+        <v>0.1210076966206229</v>
       </c>
       <c r="S23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>What's the ideal shower length?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Gettysburg, PA</t>
+          <t>Pottstown, PA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
         <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>235</v>
+        <v>195</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K24" t="n">
-        <v>8.9</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>9.33</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>8.42</v>
+        <v>7.43</v>
       </c>
       <c r="N24" t="n">
-        <v>5.01</v>
+        <v>3.48</v>
       </c>
       <c r="O24" t="n">
-        <v>8.370999999999999</v>
+        <v>8.2645</v>
       </c>
       <c r="P24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.569989699117017</v>
+        <v>1.06147102298792</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2982980428322332</v>
+        <v>0.2016794943677048</v>
       </c>
       <c r="S24" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>What's the ideal shower length?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Gettysburg, PA</t>
+          <t>Pottstown, PA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
         <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>235</v>
+        <v>195</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="I25" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J25" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K25" t="n">
-        <v>6.69</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>7.56</v>
+        <v>8.74</v>
       </c>
       <c r="M25" t="n">
-        <v>9.210000000000001</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>6.69</v>
+        <v>7.6</v>
       </c>
       <c r="O25" t="n">
-        <v>7.498500000000001</v>
+        <v>8.807</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.139979398234034</v>
+        <v>1.698353636780672</v>
       </c>
       <c r="R25" t="n">
-        <v>0.5965960856644664</v>
+        <v>0.3226871909883277</v>
       </c>
       <c r="S25" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>For a long-shower comparison in Easton, what duration should I choose?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Easton, PA</t>
+          <t>Phoenixville, PA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
         <v>2.5</v>
       </c>
       <c r="F26" t="n">
-        <v>190</v>
+        <v>310</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I26" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
-        <v>8.1</v>
+        <v>9.73</v>
       </c>
       <c r="L26" t="n">
-        <v>8.52</v>
+        <v>10</v>
       </c>
       <c r="M26" t="n">
-        <v>9.32</v>
+        <v>5.13</v>
       </c>
       <c r="N26" t="n">
-        <v>6.37</v>
+        <v>2.2</v>
       </c>
       <c r="O26" t="n">
-        <v>8.231499999999999</v>
+        <v>7.775</v>
       </c>
       <c r="P26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.138370403868106</v>
+        <v>0.9812435619481353</v>
       </c>
       <c r="R26" t="n">
-        <v>0.4062903767349402</v>
+        <v>0.1864362767701457</v>
       </c>
       <c r="S26" t="n">
-        <v>17.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>For a long-shower comparison in Easton, what duration should I choose?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Easton, PA</t>
+          <t>Phoenixville, PA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
         <v>2.5</v>
       </c>
       <c r="F27" t="n">
-        <v>190</v>
+        <v>310</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I27" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J27" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>5.09</v>
+        <v>8.81</v>
       </c>
       <c r="L27" t="n">
-        <v>5.93</v>
+        <v>9.26</v>
       </c>
       <c r="M27" t="n">
-        <v>8.81</v>
+        <v>7.43</v>
       </c>
       <c r="N27" t="n">
-        <v>5.71</v>
+        <v>3.48</v>
       </c>
       <c r="O27" t="n">
-        <v>6.221</v>
+        <v>7.892</v>
       </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.276740807736212</v>
+        <v>1.635405936580226</v>
       </c>
       <c r="R27" t="n">
-        <v>0.8125807534698803</v>
+        <v>0.3107271279502429</v>
       </c>
       <c r="S27" t="n">
-        <v>35</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>For a long-shower comparison in Easton, what duration should I choose?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Easton, PA</t>
+          <t>Phoenixville, PA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
         <v>2.5</v>
       </c>
       <c r="F28" t="n">
-        <v>190</v>
+        <v>310</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I28" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="J28" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="K28" t="n">
-        <v>1.65</v>
+        <v>7.89</v>
       </c>
       <c r="L28" t="n">
-        <v>2.96</v>
+        <v>8.52</v>
       </c>
       <c r="M28" t="n">
-        <v>5.63</v>
+        <v>9.32</v>
       </c>
       <c r="N28" t="n">
-        <v>2.27</v>
+        <v>3.07</v>
       </c>
       <c r="O28" t="n">
-        <v>2.9975</v>
+        <v>7.6735</v>
       </c>
       <c r="P28" t="n">
         <v>3</v>
       </c>
       <c r="Q28" t="n">
-        <v>6.720592697871191</v>
+        <v>2.289568311212316</v>
       </c>
       <c r="R28" t="n">
-        <v>1.276912612595526</v>
+        <v>0.43501797913034</v>
       </c>
       <c r="S28" t="n">
-        <v>55</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>With a cooler water heater in Butler, how long should showers be?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Butler, PA</t>
+          <t>Bethlehem, PA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
         <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>245</v>
+        <v>200</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Rowhouse</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="I29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K29" t="n">
-        <v>9.18</v>
+        <v>10</v>
       </c>
       <c r="L29" t="n">
-        <v>9.630000000000001</v>
+        <v>10</v>
       </c>
       <c r="M29" t="n">
-        <v>5.63</v>
+        <v>5.13</v>
       </c>
       <c r="N29" t="n">
-        <v>3.48</v>
+        <v>2.2</v>
       </c>
       <c r="O29" t="n">
-        <v>7.772500000000001</v>
+        <v>7.856</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.370038180833246</v>
+        <v>0.7331555670404936</v>
       </c>
       <c r="R29" t="n">
-        <v>0.2603072543583166</v>
+        <v>0.1392995577376938</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>With a cooler water heater in Butler, how long should showers be?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Butler, PA</t>
+          <t>Bethlehem, PA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
         <v>2</v>
       </c>
       <c r="F30" t="n">
-        <v>245</v>
+        <v>200</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Rowhouse</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="I30" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J30" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K30" t="n">
-        <v>8.029999999999999</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>8.74</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>8.56</v>
+        <v>7.43</v>
       </c>
       <c r="N30" t="n">
-        <v>4.64</v>
+        <v>3.48</v>
       </c>
       <c r="O30" t="n">
-        <v>7.875999999999999</v>
+        <v>8.195499999999999</v>
       </c>
       <c r="P30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.192061089333193</v>
+        <v>1.221925945067489</v>
       </c>
       <c r="R30" t="n">
-        <v>0.4164916069733066</v>
+        <v>0.232165929562823</v>
       </c>
       <c r="S30" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>With a cooler water heater in Butler, how long should showers be?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Butler, PA</t>
+          <t>Bethlehem, PA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
         <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>245</v>
+        <v>200</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Rowhouse</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="I31" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J31" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K31" t="n">
-        <v>6.48</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>7.56</v>
+        <v>8.74</v>
       </c>
       <c r="M31" t="n">
-        <v>7.7</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>6.69</v>
+        <v>7.6</v>
       </c>
       <c r="O31" t="n">
-        <v>7.1335</v>
+        <v>8.699</v>
       </c>
       <c r="P31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.288091633999789</v>
+        <v>1.955081512107983</v>
       </c>
       <c r="R31" t="n">
-        <v>0.62473741045996</v>
+        <v>0.3714654873005167</v>
       </c>
       <c r="S31" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>What's the ideal shower length?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2478,63 +2478,63 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
         <v>2.5</v>
       </c>
       <c r="F32" t="n">
-        <v>205</v>
+        <v>250</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Rowhouse</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K32" t="n">
-        <v>8.869999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>9.26</v>
+        <v>10</v>
       </c>
       <c r="M32" t="n">
-        <v>6.57</v>
+        <v>5.13</v>
       </c>
       <c r="N32" t="n">
-        <v>3.48</v>
+        <v>2.2</v>
       </c>
       <c r="O32" t="n">
-        <v>7.737999999999999</v>
+        <v>7.747999999999999</v>
       </c>
       <c r="P32" t="n">
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.589120862903426</v>
+        <v>1.046042665095654</v>
       </c>
       <c r="R32" t="n">
-        <v>0.301932963951651</v>
+        <v>0.1987481063681742</v>
       </c>
       <c r="S32" t="n">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>What's the ideal shower length?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2543,63 +2543,63 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
         <v>2.5</v>
       </c>
       <c r="F33" t="n">
-        <v>205</v>
+        <v>250</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Rowhouse</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="I33" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J33" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K33" t="n">
-        <v>7.53</v>
+        <v>8.66</v>
       </c>
       <c r="L33" t="n">
-        <v>8.15</v>
+        <v>9.26</v>
       </c>
       <c r="M33" t="n">
-        <v>9.289999999999999</v>
+        <v>7.43</v>
       </c>
       <c r="N33" t="n">
-        <v>7.6</v>
+        <v>3.48</v>
       </c>
       <c r="O33" t="n">
-        <v>8.109499999999999</v>
+        <v>7.847</v>
       </c>
       <c r="P33" t="n">
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.542593380645482</v>
+        <v>1.743404441826089</v>
       </c>
       <c r="R33" t="n">
-        <v>0.4830927423226416</v>
+        <v>0.331246843946957</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>What's the ideal shower length?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2608,458 +2608,458 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
         <v>2.5</v>
       </c>
       <c r="F34" t="n">
-        <v>205</v>
+        <v>250</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Rowhouse</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="I34" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J34" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K34" t="n">
-        <v>5.74</v>
+        <v>7.19</v>
       </c>
       <c r="L34" t="n">
-        <v>6.67</v>
+        <v>8.15</v>
       </c>
       <c r="M34" t="n">
-        <v>8.48</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>6.69</v>
+        <v>4.64</v>
       </c>
       <c r="O34" t="n">
-        <v>6.755999999999999</v>
+        <v>7.6975</v>
       </c>
       <c r="P34" t="n">
         <v>3</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.813890070968224</v>
+        <v>2.789447106921743</v>
       </c>
       <c r="R34" t="n">
-        <v>0.7246391134839625</v>
+        <v>0.5299949503151312</v>
       </c>
       <c r="S34" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>With a small water heater and four occupants, how long should showers be?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lebanon, PA</t>
+          <t>Wilkes-Barre, PA</t>
         </is>
       </c>
       <c r="D35" t="n">
         <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F35" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Rowhouse</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="I35" t="n">
+        <v>3</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3</v>
+      </c>
+      <c r="K35" t="n">
+        <v>10</v>
+      </c>
+      <c r="L35" t="n">
+        <v>10</v>
+      </c>
+      <c r="M35" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O35" t="n">
+        <v>7.856</v>
+      </c>
+      <c r="P35" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.6739106727341909</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.1280430278194963</v>
+      </c>
+      <c r="S35" t="n">
         <v>6</v>
-      </c>
-      <c r="J35" t="n">
-        <v>6</v>
-      </c>
-      <c r="K35" t="n">
-        <v>8.35</v>
-      </c>
-      <c r="L35" t="n">
-        <v>8.890000000000001</v>
-      </c>
-      <c r="M35" t="n">
-        <v>8.42</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="O35" t="n">
-        <v>7.527</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1.962487123896271</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0.3728725535402914</v>
-      </c>
-      <c r="S35" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>With a small water heater and four occupants, how long should showers be?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lebanon, PA</t>
+          <t>Wilkes-Barre, PA</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F36" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Rowhouse</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="I36" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J36" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K36" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="L36" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="M36" t="n">
         <v>7.43</v>
       </c>
-      <c r="L36" t="n">
-        <v>8.15</v>
-      </c>
-      <c r="M36" t="n">
-        <v>9.9</v>
-      </c>
       <c r="N36" t="n">
-        <v>4.64</v>
+        <v>3.48</v>
       </c>
       <c r="O36" t="n">
-        <v>7.7575</v>
+        <v>8.237499999999999</v>
       </c>
       <c r="P36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.616649498528361</v>
+        <v>1.123184454556985</v>
       </c>
       <c r="R36" t="n">
-        <v>0.4971634047203885</v>
+        <v>0.2134050463658271</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>With a small water heater and four occupants, how long should showers be?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lebanon, PA</t>
+          <t>Wilkes-Barre, PA</t>
         </is>
       </c>
       <c r="D37" t="n">
         <v>4</v>
       </c>
       <c r="E37" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F37" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Rowhouse</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="I37" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J37" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K37" t="n">
-        <v>6.51</v>
+        <v>8.9</v>
       </c>
       <c r="L37" t="n">
-        <v>7.41</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>8.82</v>
+        <v>9.32</v>
       </c>
       <c r="N37" t="n">
-        <v>5.71</v>
+        <v>6.37</v>
       </c>
       <c r="O37" t="n">
-        <v>7.167</v>
+        <v>8.653499999999999</v>
       </c>
       <c r="P37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.270811873160451</v>
+        <v>1.572458236379779</v>
       </c>
       <c r="R37" t="n">
-        <v>0.6214542559004858</v>
+        <v>0.298767064912158</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>What's the ideal shower length?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Monroeville, PA</t>
+          <t>Meadville, PA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F38" t="n">
-        <v>490</v>
+        <v>140</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="I38" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J38" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K38" t="n">
-        <v>7.53</v>
+        <v>9.83</v>
       </c>
       <c r="L38" t="n">
-        <v>8.15</v>
+        <v>10</v>
       </c>
       <c r="M38" t="n">
-        <v>9.9</v>
+        <v>4.33</v>
       </c>
       <c r="N38" t="n">
-        <v>4.64</v>
+        <v>2.86</v>
       </c>
       <c r="O38" t="n">
-        <v>7.7875</v>
+        <v>7.744</v>
       </c>
       <c r="P38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.542593380645482</v>
+        <v>0.9108902499594012</v>
       </c>
       <c r="R38" t="n">
-        <v>0.4830927423226416</v>
+        <v>0.1730691474922862</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>What's the ideal shower length?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Monroeville, PA</t>
+          <t>Meadville, PA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F39" t="n">
-        <v>490</v>
+        <v>140</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="I39" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J39" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K39" t="n">
-        <v>6.64</v>
+        <v>9.19</v>
       </c>
       <c r="L39" t="n">
-        <v>7.41</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>8.82</v>
+        <v>6.79</v>
       </c>
       <c r="N39" t="n">
-        <v>5.71</v>
+        <v>5.01</v>
       </c>
       <c r="O39" t="n">
-        <v>7.205999999999999</v>
+        <v>8.2895</v>
       </c>
       <c r="P39" t="n">
         <v>2</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.178241725806853</v>
+        <v>1.366335374939102</v>
       </c>
       <c r="R39" t="n">
-        <v>0.6038659279033021</v>
+        <v>0.2596037212384293</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>What's the ideal shower length?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Monroeville, PA</t>
+          <t>Meadville, PA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F40" t="n">
-        <v>490</v>
+        <v>140</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="I40" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J40" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K40" t="n">
-        <v>5.74</v>
+        <v>7.91</v>
       </c>
       <c r="L40" t="n">
-        <v>6.67</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="M40" t="n">
-        <v>7.62</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="N40" t="n">
-        <v>6.69</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O40" t="n">
-        <v>6.584</v>
+        <v>8.379999999999999</v>
       </c>
       <c r="P40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.813890070968224</v>
+        <v>2.277225624898503</v>
       </c>
       <c r="R40" t="n">
-        <v>0.7246391134839625</v>
+        <v>0.4326728687307156</v>
       </c>
       <c r="S40" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>How long should my showers be?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bradford, PA</t>
+          <t>Uniontown, PA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -3069,62 +3069,62 @@
         <v>2</v>
       </c>
       <c r="F41" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="I41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K41" t="n">
-        <v>8.869999999999999</v>
+        <v>9.98</v>
       </c>
       <c r="L41" t="n">
-        <v>9.630000000000001</v>
+        <v>10</v>
       </c>
       <c r="M41" t="n">
-        <v>7.43</v>
+        <v>5.13</v>
       </c>
       <c r="N41" t="n">
-        <v>3.48</v>
+        <v>2.2</v>
       </c>
       <c r="O41" t="n">
-        <v>8.039499999999999</v>
+        <v>7.85</v>
       </c>
       <c r="P41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.59220653448188</v>
+        <v>0.8072116849233715</v>
       </c>
       <c r="R41" t="n">
-        <v>0.3025192415515572</v>
+        <v>0.1533702201354406</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>How long should my showers be?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bradford, PA</t>
+          <t>Uniontown, PA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -3134,62 +3134,62 @@
         <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H42" t="n">
+        <v>52</v>
+      </c>
+      <c r="I42" t="n">
         <v>5</v>
       </c>
-      <c r="I42" t="n">
-        <v>8</v>
-      </c>
       <c r="J42" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K42" t="n">
-        <v>7.53</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>8.74</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>9.960000000000001</v>
+        <v>7.43</v>
       </c>
       <c r="N42" t="n">
-        <v>7.6</v>
+        <v>3.48</v>
       </c>
       <c r="O42" t="n">
-        <v>8.449999999999999</v>
+        <v>8.144499999999999</v>
       </c>
       <c r="P42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.547530455171008</v>
+        <v>1.345352808205619</v>
       </c>
       <c r="R42" t="n">
-        <v>0.4840307864824915</v>
+        <v>0.2556170335590677</v>
       </c>
       <c r="S42" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>How long should my showers be?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bradford, PA</t>
+          <t>Uniontown, PA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -3199,62 +3199,62 @@
         <v>2</v>
       </c>
       <c r="F43" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="I43" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J43" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K43" t="n">
-        <v>5.73</v>
+        <v>8.08</v>
       </c>
       <c r="L43" t="n">
-        <v>7.56</v>
+        <v>8.74</v>
       </c>
       <c r="M43" t="n">
-        <v>9.210000000000001</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="N43" t="n">
-        <v>6.69</v>
+        <v>7.6</v>
       </c>
       <c r="O43" t="n">
-        <v>7.210500000000001</v>
+        <v>8.615</v>
       </c>
       <c r="P43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.821295682756512</v>
+        <v>2.152564493128991</v>
       </c>
       <c r="R43" t="n">
-        <v>0.7260461797237373</v>
+        <v>0.4089872536945083</v>
       </c>
       <c r="S43" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>For a warm day in Media, what shower duration balances comfort and water use?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Media, PA</t>
+          <t>Williamsport, PA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -3268,58 +3268,58 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single-family</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="I44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K44" t="n">
-        <v>9.24</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>9.26</v>
+        <v>10</v>
       </c>
       <c r="M44" t="n">
-        <v>7.43</v>
+        <v>5.13</v>
       </c>
       <c r="N44" t="n">
-        <v>3.48</v>
+        <v>2.2</v>
       </c>
       <c r="O44" t="n">
-        <v>8.020999999999999</v>
+        <v>7.747999999999999</v>
       </c>
       <c r="P44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.3268387787349</v>
+        <v>1.046042665095654</v>
       </c>
       <c r="R44" t="n">
-        <v>0.2520993679596309</v>
+        <v>0.1987481063681742</v>
       </c>
       <c r="S44" t="n">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>For a warm day in Media, what shower duration balances comfort and water use?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Media, PA</t>
+          <t>Williamsport, PA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -3333,58 +3333,58 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single-family</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="I45" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J45" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K45" t="n">
-        <v>8.119999999999999</v>
+        <v>8.66</v>
       </c>
       <c r="L45" t="n">
-        <v>8.15</v>
+        <v>9.26</v>
       </c>
       <c r="M45" t="n">
-        <v>9.960000000000001</v>
+        <v>7.43</v>
       </c>
       <c r="N45" t="n">
-        <v>4.64</v>
+        <v>3.48</v>
       </c>
       <c r="O45" t="n">
-        <v>7.976499999999999</v>
+        <v>7.847</v>
       </c>
       <c r="P45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.12294204597584</v>
+        <v>1.743404441826089</v>
       </c>
       <c r="R45" t="n">
-        <v>0.4033589887354095</v>
+        <v>0.331246843946957</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>For a warm day in Media, what shower duration balances comfort and water use?</t>
+          <t>How long should I shower?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Media, PA</t>
+          <t>Williamsport, PA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -3398,43 +3398,1018 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
+          <t>Single-family</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>48</v>
+      </c>
+      <c r="I46" t="n">
+        <v>8</v>
+      </c>
+      <c r="J46" t="n">
+        <v>8</v>
+      </c>
+      <c r="K46" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="L46" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="M46" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="N46" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="O46" t="n">
+        <v>7.6975</v>
+      </c>
+      <c r="P46" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>2.789447106921743</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.5299949503151312</v>
+      </c>
+      <c r="S46" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>74</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>How long should I shower?</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Williamsport, PA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" t="n">
+        <v>195</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>35</v>
+      </c>
+      <c r="I47" t="n">
+        <v>3</v>
+      </c>
+      <c r="J47" t="n">
+        <v>3</v>
+      </c>
+      <c r="K47" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L47" t="n">
+        <v>10</v>
+      </c>
+      <c r="M47" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="N47" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O47" t="n">
+        <v>7.795999999999999</v>
+      </c>
+      <c r="P47" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.9331070853242645</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0.1772903462116102</v>
+      </c>
+      <c r="S47" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>74</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>How long should I shower?</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Williamsport, PA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2</v>
+      </c>
+      <c r="F48" t="n">
+        <v>195</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>35</v>
+      </c>
+      <c r="I48" t="n">
+        <v>5</v>
+      </c>
+      <c r="J48" t="n">
+        <v>5</v>
+      </c>
+      <c r="K48" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="L48" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="M48" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="O48" t="n">
+        <v>8.054499999999999</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1.555178475540441</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0.2954839103526837</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>74</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>How long should I shower?</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Williamsport, PA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" t="n">
+        <v>195</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>35</v>
+      </c>
+      <c r="I49" t="n">
+        <v>8</v>
+      </c>
+      <c r="J49" t="n">
+        <v>8</v>
+      </c>
+      <c r="K49" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="L49" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="M49" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="N49" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="O49" t="n">
+        <v>8.474</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2.488285560864705</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0.472774256564294</v>
+      </c>
+      <c r="S49" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>75</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>How long should I shower?</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>West Mifflin, PA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F50" t="n">
+        <v>250</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H46" t="n">
-        <v>85</v>
-      </c>
-      <c r="I46" t="n">
+      <c r="H50" t="n">
+        <v>60</v>
+      </c>
+      <c r="I50" t="n">
+        <v>3</v>
+      </c>
+      <c r="J50" t="n">
+        <v>3</v>
+      </c>
+      <c r="K50" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L50" t="n">
+        <v>10</v>
+      </c>
+      <c r="M50" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O50" t="n">
+        <v>7.795999999999999</v>
+      </c>
+      <c r="P50" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.9349584882713364</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0.1776421127715539</v>
+      </c>
+      <c r="S50" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>75</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>How long should I shower?</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>West Mifflin, PA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F51" t="n">
+        <v>250</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>60</v>
+      </c>
+      <c r="I51" t="n">
+        <v>5</v>
+      </c>
+      <c r="J51" t="n">
+        <v>5</v>
+      </c>
+      <c r="K51" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="L51" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="M51" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="N51" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="O51" t="n">
+        <v>7.925</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1.558264147118894</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0.2960701879525898</v>
+      </c>
+      <c r="S51" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>75</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>How long should I shower?</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>West Mifflin, PA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F52" t="n">
+        <v>250</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>60</v>
+      </c>
+      <c r="I52" t="n">
+        <v>8</v>
+      </c>
+      <c r="J52" t="n">
+        <v>8</v>
+      </c>
+      <c r="K52" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L52" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="M52" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="N52" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="O52" t="n">
+        <v>7.8205</v>
+      </c>
+      <c r="P52" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>2.49322263539023</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0.4737123007241438</v>
+      </c>
+      <c r="S52" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>77</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>With a high-flow showerhead and small tank on a cold morning, how long should I shower?</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Altoona, PA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>4</v>
+      </c>
+      <c r="E53" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F53" t="n">
+        <v>240</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Rowhouse</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>18</v>
+      </c>
+      <c r="I53" t="n">
+        <v>4</v>
+      </c>
+      <c r="J53" t="n">
+        <v>4</v>
+      </c>
+      <c r="K53" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="L53" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="M53" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="N53" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="O53" t="n">
+        <v>7.049499999999999</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>2.229089148274632</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0.4235269381721801</v>
+      </c>
+      <c r="S53" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>77</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>With a high-flow showerhead and small tank on a cold morning, how long should I shower?</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Altoona, PA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>4</v>
+      </c>
+      <c r="E54" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F54" t="n">
+        <v>240</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Rowhouse</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>18</v>
+      </c>
+      <c r="I54" t="n">
+        <v>6</v>
+      </c>
+      <c r="J54" t="n">
+        <v>6</v>
+      </c>
+      <c r="K54" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="L54" t="n">
+        <v>8</v>
+      </c>
+      <c r="M54" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="N54" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="O54" t="n">
+        <v>6.6335</v>
+      </c>
+      <c r="P54" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>3.343633722411948</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0.6352904072582701</v>
+      </c>
+      <c r="S54" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>77</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>With a high-flow showerhead and small tank on a cold morning, how long should I shower?</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Altoona, PA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>4</v>
+      </c>
+      <c r="E55" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F55" t="n">
+        <v>240</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Rowhouse</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>18</v>
+      </c>
+      <c r="I55" t="n">
+        <v>8</v>
+      </c>
+      <c r="J55" t="n">
+        <v>8</v>
+      </c>
+      <c r="K55" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="L55" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="M55" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="N55" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="O55" t="n">
+        <v>6.564</v>
+      </c>
+      <c r="P55" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>4.458178296549264</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0.8470538763443601</v>
+      </c>
+      <c r="S55" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>78</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>On a hot day with a low-flow showerhead, what shower duration makes sense?</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Chester, PA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F56" t="n">
+        <v>150</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Condo</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>90</v>
+      </c>
+      <c r="I56" t="n">
+        <v>4</v>
+      </c>
+      <c r="J56" t="n">
+        <v>4</v>
+      </c>
+      <c r="K56" t="n">
+        <v>10</v>
+      </c>
+      <c r="L56" t="n">
+        <v>10</v>
+      </c>
+      <c r="M56" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="N56" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O56" t="n">
+        <v>8.196999999999999</v>
+      </c>
+      <c r="P56" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0.6368826137927521</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.1210076966206229</v>
+      </c>
+      <c r="S56" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>78</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>On a hot day with a low-flow showerhead, what shower duration makes sense?</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Chester, PA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F57" t="n">
+        <v>150</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Condo</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>90</v>
+      </c>
+      <c r="I57" t="n">
+        <v>7</v>
+      </c>
+      <c r="J57" t="n">
+        <v>7</v>
+      </c>
+      <c r="K57" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="L57" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="M57" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="N57" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="O57" t="n">
+        <v>9.027500000000002</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1.114544574137316</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0.2117634690860901</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>78</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>On a hot day with a low-flow showerhead, what shower duration makes sense?</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Chester, PA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F58" t="n">
+        <v>150</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Condo</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>90</v>
+      </c>
+      <c r="I58" t="n">
+        <v>10</v>
+      </c>
+      <c r="J58" t="n">
+        <v>10</v>
+      </c>
+      <c r="K58" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="L58" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="M58" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="N58" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="O58" t="n">
+        <v>8.957999999999998</v>
+      </c>
+      <c r="P58" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1.59220653448188</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0.3025192415515572</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>79</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>With six people sharing a tank tonight, how long should showers be?</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Johnstown, PA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>6</v>
+      </c>
+      <c r="E59" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F59" t="n">
+        <v>340</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Single-family</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>40</v>
+      </c>
+      <c r="I59" t="n">
+        <v>5</v>
+      </c>
+      <c r="J59" t="n">
+        <v>5</v>
+      </c>
+      <c r="K59" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="L59" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="M59" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="N59" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="O59" t="n">
+        <v>7.4975</v>
+      </c>
+      <c r="P59" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1.86683130496422</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0.3546979479432018</v>
+      </c>
+      <c r="S59" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>79</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>With six people sharing a tank tonight, how long should showers be?</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Johnstown, PA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>6</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F60" t="n">
+        <v>340</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Single-family</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>40</v>
+      </c>
+      <c r="I60" t="n">
+        <v>8</v>
+      </c>
+      <c r="J60" t="n">
+        <v>8</v>
+      </c>
+      <c r="K60" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="L60" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="M60" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="N60" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="O60" t="n">
+        <v>7.6015</v>
+      </c>
+      <c r="P60" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>2.986930087942751</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0.5675167167091227</v>
+      </c>
+      <c r="S60" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>79</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>With six people sharing a tank tonight, how long should showers be?</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Johnstown, PA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>6</v>
+      </c>
+      <c r="E61" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F61" t="n">
+        <v>340</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Single-family</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>40</v>
+      </c>
+      <c r="I61" t="n">
         <v>12</v>
       </c>
-      <c r="J46" t="n">
+      <c r="J61" t="n">
         <v>12</v>
       </c>
-      <c r="K46" t="n">
-        <v>6.63</v>
-      </c>
-      <c r="L46" t="n">
+      <c r="K61" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="L61" t="n">
         <v>6.67</v>
       </c>
-      <c r="M46" t="n">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="N46" t="n">
+      <c r="M61" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="N61" t="n">
         <v>6.69</v>
       </c>
-      <c r="O46" t="n">
-        <v>7.169</v>
-      </c>
-      <c r="P46" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>3.18441306896376</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0.6050384831031144</v>
-      </c>
-      <c r="S46" t="n">
+      <c r="O61" t="n">
+        <v>6.305</v>
+      </c>
+      <c r="P61" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>4.480395131914127</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0.8512750750636842</v>
+      </c>
+      <c r="S61" t="n">
         <v>30</v>
       </c>
     </row>

--- a/workbooks/scenarios/ShowerRAGScenarios.xlsx
+++ b/workbooks/scenarios/ShowerRAGScenarios.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/workbooks/scenarios/ShowerRAGScenarios.xlsx
+++ b/workbooks/scenarios/ShowerRAGScenarios.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>question</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -434,7 +434,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>occupants</t>
+          <t>household_size</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">

--- a/workbooks/scenarios/ShowerRAGScenarios.xlsx
+++ b/workbooks/scenarios/ShowerRAGScenarios.xlsx
@@ -544,8 +544,10 @@
       <c r="H2" t="n">
         <v>75</v>
       </c>
-      <c r="I2" t="n">
-        <v>5</v>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J2" t="n">
         <v>5</v>
@@ -609,8 +611,10 @@
       <c r="H3" t="n">
         <v>75</v>
       </c>
-      <c r="I3" t="n">
-        <v>8</v>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J3" t="n">
         <v>8</v>
@@ -674,8 +678,10 @@
       <c r="H4" t="n">
         <v>75</v>
       </c>
-      <c r="I4" t="n">
-        <v>12</v>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J4" t="n">
         <v>12</v>
@@ -739,8 +745,10 @@
       <c r="H5" t="n">
         <v>85</v>
       </c>
-      <c r="I5" t="n">
-        <v>5</v>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J5" t="n">
         <v>5</v>
@@ -804,8 +812,10 @@
       <c r="H6" t="n">
         <v>85</v>
       </c>
-      <c r="I6" t="n">
-        <v>8</v>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J6" t="n">
         <v>8</v>
@@ -869,8 +879,10 @@
       <c r="H7" t="n">
         <v>85</v>
       </c>
-      <c r="I7" t="n">
-        <v>12</v>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J7" t="n">
         <v>12</v>
@@ -934,8 +946,10 @@
       <c r="H8" t="n">
         <v>48</v>
       </c>
-      <c r="I8" t="n">
-        <v>4</v>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="J8" t="n">
         <v>4</v>
@@ -999,8 +1013,10 @@
       <c r="H9" t="n">
         <v>48</v>
       </c>
-      <c r="I9" t="n">
-        <v>6</v>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="J9" t="n">
         <v>6</v>
@@ -1064,8 +1080,10 @@
       <c r="H10" t="n">
         <v>48</v>
       </c>
-      <c r="I10" t="n">
-        <v>10</v>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J10" t="n">
         <v>10</v>
@@ -1129,8 +1147,10 @@
       <c r="H11" t="n">
         <v>62</v>
       </c>
-      <c r="I11" t="n">
-        <v>3</v>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J11" t="n">
         <v>3</v>
@@ -1194,8 +1214,10 @@
       <c r="H12" t="n">
         <v>62</v>
       </c>
-      <c r="I12" t="n">
-        <v>5</v>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J12" t="n">
         <v>5</v>
@@ -1259,8 +1281,10 @@
       <c r="H13" t="n">
         <v>62</v>
       </c>
-      <c r="I13" t="n">
-        <v>8</v>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J13" t="n">
         <v>8</v>
@@ -1324,8 +1348,10 @@
       <c r="H14" t="n">
         <v>70</v>
       </c>
-      <c r="I14" t="n">
-        <v>3</v>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J14" t="n">
         <v>3</v>
@@ -1389,8 +1415,10 @@
       <c r="H15" t="n">
         <v>70</v>
       </c>
-      <c r="I15" t="n">
-        <v>4</v>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="J15" t="n">
         <v>4</v>
@@ -1454,8 +1482,10 @@
       <c r="H16" t="n">
         <v>70</v>
       </c>
-      <c r="I16" t="n">
-        <v>6</v>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="J16" t="n">
         <v>6</v>
@@ -1519,8 +1549,10 @@
       <c r="H17" t="n">
         <v>28</v>
       </c>
-      <c r="I17" t="n">
-        <v>3</v>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J17" t="n">
         <v>3</v>
@@ -1584,8 +1616,10 @@
       <c r="H18" t="n">
         <v>28</v>
       </c>
-      <c r="I18" t="n">
-        <v>5</v>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J18" t="n">
         <v>5</v>
@@ -1649,8 +1683,10 @@
       <c r="H19" t="n">
         <v>28</v>
       </c>
-      <c r="I19" t="n">
-        <v>8</v>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J19" t="n">
         <v>8</v>
@@ -1714,8 +1750,10 @@
       <c r="H20" t="n">
         <v>62</v>
       </c>
-      <c r="I20" t="n">
-        <v>3</v>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J20" t="n">
         <v>3</v>
@@ -1779,8 +1817,10 @@
       <c r="H21" t="n">
         <v>62</v>
       </c>
-      <c r="I21" t="n">
-        <v>5</v>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J21" t="n">
         <v>5</v>
@@ -1844,8 +1884,10 @@
       <c r="H22" t="n">
         <v>62</v>
       </c>
-      <c r="I22" t="n">
-        <v>8</v>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J22" t="n">
         <v>8</v>
@@ -1909,8 +1951,10 @@
       <c r="H23" t="n">
         <v>75</v>
       </c>
-      <c r="I23" t="n">
-        <v>3</v>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J23" t="n">
         <v>3</v>
@@ -1974,8 +2018,10 @@
       <c r="H24" t="n">
         <v>75</v>
       </c>
-      <c r="I24" t="n">
-        <v>5</v>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J24" t="n">
         <v>5</v>
@@ -2039,8 +2085,10 @@
       <c r="H25" t="n">
         <v>75</v>
       </c>
-      <c r="I25" t="n">
-        <v>8</v>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J25" t="n">
         <v>8</v>
@@ -2104,8 +2152,10 @@
       <c r="H26" t="n">
         <v>55</v>
       </c>
-      <c r="I26" t="n">
-        <v>3</v>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J26" t="n">
         <v>3</v>
@@ -2169,8 +2219,10 @@
       <c r="H27" t="n">
         <v>55</v>
       </c>
-      <c r="I27" t="n">
-        <v>5</v>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J27" t="n">
         <v>5</v>
@@ -2234,8 +2286,10 @@
       <c r="H28" t="n">
         <v>55</v>
       </c>
-      <c r="I28" t="n">
-        <v>7</v>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="J28" t="n">
         <v>7</v>
@@ -2299,8 +2353,10 @@
       <c r="H29" t="n">
         <v>62</v>
       </c>
-      <c r="I29" t="n">
-        <v>3</v>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J29" t="n">
         <v>3</v>
@@ -2364,8 +2420,10 @@
       <c r="H30" t="n">
         <v>62</v>
       </c>
-      <c r="I30" t="n">
-        <v>5</v>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J30" t="n">
         <v>5</v>
@@ -2429,8 +2487,10 @@
       <c r="H31" t="n">
         <v>62</v>
       </c>
-      <c r="I31" t="n">
-        <v>8</v>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J31" t="n">
         <v>8</v>
@@ -2494,8 +2554,10 @@
       <c r="H32" t="n">
         <v>48</v>
       </c>
-      <c r="I32" t="n">
-        <v>3</v>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J32" t="n">
         <v>3</v>
@@ -2559,8 +2621,10 @@
       <c r="H33" t="n">
         <v>48</v>
       </c>
-      <c r="I33" t="n">
-        <v>5</v>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J33" t="n">
         <v>5</v>
@@ -2624,8 +2688,10 @@
       <c r="H34" t="n">
         <v>48</v>
       </c>
-      <c r="I34" t="n">
-        <v>8</v>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J34" t="n">
         <v>8</v>
@@ -2689,8 +2755,10 @@
       <c r="H35" t="n">
         <v>70</v>
       </c>
-      <c r="I35" t="n">
-        <v>3</v>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J35" t="n">
         <v>3</v>
@@ -2754,8 +2822,10 @@
       <c r="H36" t="n">
         <v>70</v>
       </c>
-      <c r="I36" t="n">
-        <v>5</v>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J36" t="n">
         <v>5</v>
@@ -2819,8 +2889,10 @@
       <c r="H37" t="n">
         <v>70</v>
       </c>
-      <c r="I37" t="n">
-        <v>7</v>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="J37" t="n">
         <v>7</v>
@@ -2884,8 +2956,10 @@
       <c r="H38" t="n">
         <v>38</v>
       </c>
-      <c r="I38" t="n">
-        <v>4</v>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="J38" t="n">
         <v>4</v>
@@ -2949,8 +3023,10 @@
       <c r="H39" t="n">
         <v>38</v>
       </c>
-      <c r="I39" t="n">
-        <v>6</v>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="J39" t="n">
         <v>6</v>
@@ -3014,8 +3090,10 @@
       <c r="H40" t="n">
         <v>38</v>
       </c>
-      <c r="I40" t="n">
-        <v>10</v>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J40" t="n">
         <v>10</v>
@@ -3079,8 +3157,10 @@
       <c r="H41" t="n">
         <v>52</v>
       </c>
-      <c r="I41" t="n">
-        <v>3</v>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J41" t="n">
         <v>3</v>
@@ -3144,8 +3224,10 @@
       <c r="H42" t="n">
         <v>52</v>
       </c>
-      <c r="I42" t="n">
-        <v>5</v>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J42" t="n">
         <v>5</v>
@@ -3209,8 +3291,10 @@
       <c r="H43" t="n">
         <v>52</v>
       </c>
-      <c r="I43" t="n">
-        <v>8</v>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J43" t="n">
         <v>8</v>
@@ -3274,8 +3358,10 @@
       <c r="H44" t="n">
         <v>48</v>
       </c>
-      <c r="I44" t="n">
-        <v>3</v>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J44" t="n">
         <v>3</v>
@@ -3339,8 +3425,10 @@
       <c r="H45" t="n">
         <v>48</v>
       </c>
-      <c r="I45" t="n">
-        <v>5</v>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J45" t="n">
         <v>5</v>
@@ -3404,8 +3492,10 @@
       <c r="H46" t="n">
         <v>48</v>
       </c>
-      <c r="I46" t="n">
-        <v>8</v>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J46" t="n">
         <v>8</v>
@@ -3469,8 +3559,10 @@
       <c r="H47" t="n">
         <v>35</v>
       </c>
-      <c r="I47" t="n">
-        <v>3</v>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J47" t="n">
         <v>3</v>
@@ -3534,8 +3626,10 @@
       <c r="H48" t="n">
         <v>35</v>
       </c>
-      <c r="I48" t="n">
-        <v>5</v>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J48" t="n">
         <v>5</v>
@@ -3599,8 +3693,10 @@
       <c r="H49" t="n">
         <v>35</v>
       </c>
-      <c r="I49" t="n">
-        <v>8</v>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J49" t="n">
         <v>8</v>
@@ -3664,8 +3760,10 @@
       <c r="H50" t="n">
         <v>60</v>
       </c>
-      <c r="I50" t="n">
-        <v>3</v>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J50" t="n">
         <v>3</v>
@@ -3729,8 +3827,10 @@
       <c r="H51" t="n">
         <v>60</v>
       </c>
-      <c r="I51" t="n">
-        <v>5</v>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J51" t="n">
         <v>5</v>
@@ -3794,8 +3894,10 @@
       <c r="H52" t="n">
         <v>60</v>
       </c>
-      <c r="I52" t="n">
-        <v>8</v>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J52" t="n">
         <v>8</v>
@@ -3859,8 +3961,10 @@
       <c r="H53" t="n">
         <v>18</v>
       </c>
-      <c r="I53" t="n">
-        <v>4</v>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="J53" t="n">
         <v>4</v>
@@ -3924,8 +4028,10 @@
       <c r="H54" t="n">
         <v>18</v>
       </c>
-      <c r="I54" t="n">
-        <v>6</v>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="J54" t="n">
         <v>6</v>
@@ -3989,8 +4095,10 @@
       <c r="H55" t="n">
         <v>18</v>
       </c>
-      <c r="I55" t="n">
-        <v>8</v>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J55" t="n">
         <v>8</v>
@@ -4054,8 +4162,10 @@
       <c r="H56" t="n">
         <v>90</v>
       </c>
-      <c r="I56" t="n">
-        <v>4</v>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="J56" t="n">
         <v>4</v>
@@ -4119,8 +4229,10 @@
       <c r="H57" t="n">
         <v>90</v>
       </c>
-      <c r="I57" t="n">
-        <v>7</v>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="J57" t="n">
         <v>7</v>
@@ -4184,8 +4296,10 @@
       <c r="H58" t="n">
         <v>90</v>
       </c>
-      <c r="I58" t="n">
-        <v>10</v>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J58" t="n">
         <v>10</v>
@@ -4249,8 +4363,10 @@
       <c r="H59" t="n">
         <v>40</v>
       </c>
-      <c r="I59" t="n">
-        <v>5</v>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J59" t="n">
         <v>5</v>
@@ -4314,8 +4430,10 @@
       <c r="H60" t="n">
         <v>40</v>
       </c>
-      <c r="I60" t="n">
-        <v>8</v>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J60" t="n">
         <v>8</v>
@@ -4379,8 +4497,10 @@
       <c r="H61" t="n">
         <v>40</v>
       </c>
-      <c r="I61" t="n">
-        <v>12</v>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J61" t="n">
         <v>12</v>

--- a/workbooks/scenarios/ShowerRAGScenarios.xlsx
+++ b/workbooks/scenarios/ShowerRAGScenarios.xlsx
@@ -46,8 +46,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S61"/>
+  <dimension ref="A1:T61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,72 +443,77 @@
           <t>gpm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>flow_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>utility_budget</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>housing_type</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>outdoor_temp</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>alternative</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>duration_min</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>energy_cost_score</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>environmental_score</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>comfort_score</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>practicality_score</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>mavt_score</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>raw_kwh</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>raw_cost</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>raw_water_gallons</t>
         </is>
@@ -533,50 +539,55 @@
       <c r="E2" t="n">
         <v>2</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>195</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>75</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>5</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>9.619999999999999</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>7.43</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>3.48</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>8.2645</v>
       </c>
-      <c r="P2" t="n">
-        <v>2</v>
-      </c>
       <c r="Q2" t="n">
+        <v>2</v>
+      </c>
+      <c r="R2" t="n">
         <v>1.06147102298792</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>0.2016794943677048</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>10</v>
       </c>
     </row>
@@ -600,50 +611,55 @@
       <c r="E3" t="n">
         <v>2</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>195</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>75</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>8</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>8.720000000000001</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>8.74</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>9.960000000000001</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>7.6</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8.807</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>1.698353636780672</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>0.3226871909883277</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>16</v>
       </c>
     </row>
@@ -667,50 +683,55 @@
       <c r="E4" t="n">
         <v>2</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>195</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>75</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>12</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>7.53</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>7.56</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>9.210000000000001</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>6.69</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>7.7505</v>
       </c>
-      <c r="P4" t="n">
-        <v>3</v>
-      </c>
       <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
         <v>2.547530455171008</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>0.4840307864824915</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>24</v>
       </c>
     </row>
@@ -734,50 +755,55 @@
       <c r="E5" t="n">
         <v>2.5</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>255</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>85</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>5</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>9.24</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>9.26</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>7.43</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>3.48</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>8.020999999999999</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>1.3268387787349</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>0.2520993679596309</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>12.5</v>
       </c>
     </row>
@@ -801,50 +827,55 @@
       <c r="E6" t="n">
         <v>2.5</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>255</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>85</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>8</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>8.119999999999999</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>8.15</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>9.960000000000001</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>4.64</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>7.976499999999999</v>
       </c>
-      <c r="P6" t="n">
-        <v>2</v>
-      </c>
       <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" t="n">
         <v>2.12294204597584</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>0.4033589887354095</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>20</v>
       </c>
     </row>
@@ -868,50 +899,55 @@
       <c r="E7" t="n">
         <v>2.5</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>255</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>85</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>12</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>6.63</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>6.67</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>9.210000000000001</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>6.69</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>7.169</v>
       </c>
-      <c r="P7" t="n">
-        <v>3</v>
-      </c>
       <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
         <v>3.18441306896376</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>0.6050384831031144</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>30</v>
       </c>
     </row>
@@ -935,50 +971,55 @@
       <c r="E8" t="n">
         <v>2</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
         <v>155</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>48</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>4</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>9.539999999999999</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>9.93</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>6.34</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>2.86</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>8.0345</v>
       </c>
-      <c r="P8" t="n">
-        <v>3</v>
-      </c>
       <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
         <v>1.115778842768697</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>0.2119979801260525</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1002,50 +1043,55 @@
       <c r="E9" t="n">
         <v>2</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
         <v>155</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>48</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>6</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>8.76</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>9.33</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>8.42</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>5.01</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>8.328999999999999</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>1</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>1.673668264153046</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>0.3179969701890787</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1069,50 +1115,55 @@
       <c r="E10" t="n">
         <v>2</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
         <v>155</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>48</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>10</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>7.19</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>8.15</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>9.59</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>8.195</v>
       </c>
-      <c r="P10" t="n">
-        <v>2</v>
-      </c>
       <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
         <v>2.789447106921743</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>0.5299949503151312</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1136,50 +1187,55 @@
       <c r="E11" t="n">
         <v>2.5</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
         <v>245</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>62</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J11" t="n">
-        <v>3</v>
-      </c>
       <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
         <v>9.82</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>10</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>5.13</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>2.2</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>7.802</v>
       </c>
-      <c r="P11" t="n">
-        <v>3</v>
-      </c>
       <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
         <v>0.916444458800617</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>0.1741244471721172</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>7.5</v>
       </c>
     </row>
@@ -1203,50 +1259,55 @@
       <c r="E12" t="n">
         <v>2.5</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
         <v>245</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>62</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>5</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>8.960000000000001</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>9.26</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>7.43</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>3.48</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>7.937</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>1</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>1.527407431334362</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>0.2902074119535287</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>12.5</v>
       </c>
     </row>
@@ -1270,50 +1331,55 @@
       <c r="E13" t="n">
         <v>2.5</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
         <v>245</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>62</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>8</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>7.67</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>8.15</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>9.960000000000001</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>4.64</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>7.841499999999999</v>
       </c>
-      <c r="P13" t="n">
-        <v>2</v>
-      </c>
       <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
         <v>2.443851890134979</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>0.464331859125646</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1337,50 +1403,55 @@
       <c r="E14" t="n">
         <v>3</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
         <v>295</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>70</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J14" t="n">
-        <v>3</v>
-      </c>
       <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
         <v>9.69</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>9.779999999999999</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>5.13</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>2.2</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>7.685999999999999</v>
       </c>
-      <c r="P14" t="n">
-        <v>2</v>
-      </c>
       <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
         <v>1.010866009101286</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>0.1920645417292444</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1404,50 +1475,55 @@
       <c r="E15" t="n">
         <v>3</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
         <v>295</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>70</v>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>4</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>9.210000000000001</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>9.33</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>6.34</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>2.86</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>7.7255</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>1</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>1.347821345468382</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>0.2560860556389926</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1471,50 +1547,55 @@
       <c r="E16" t="n">
         <v>3</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
         <v>295</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>70</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>6</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>8.27</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>8.44</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>8.42</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>1.51</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>7.345499999999999</v>
       </c>
-      <c r="P16" t="n">
-        <v>3</v>
-      </c>
       <c r="Q16" t="n">
+        <v>3</v>
+      </c>
+      <c r="R16" t="n">
         <v>2.021732018202572</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>0.3841290834584888</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>18</v>
       </c>
     </row>
@@ -1538,50 +1619,55 @@
       <c r="E17" t="n">
         <v>2</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
         <v>185</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>28</v>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J17" t="n">
-        <v>3</v>
-      </c>
       <c r="K17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" t="n">
         <v>9.77</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>10</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>5.13</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>2.2</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>7.786999999999999</v>
       </c>
-      <c r="P17" t="n">
-        <v>3</v>
-      </c>
       <c r="Q17" t="n">
+        <v>3</v>
+      </c>
+      <c r="R17" t="n">
         <v>0.955323920689128</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>0.1815115449309343</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1605,50 +1691,55 @@
       <c r="E18" t="n">
         <v>2</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
         <v>185</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>28</v>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>5</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>8.869999999999999</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>7.43</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>3.48</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>8.039499999999999</v>
       </c>
-      <c r="P18" t="n">
-        <v>2</v>
-      </c>
       <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.59220653448188</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>0.3025192415515572</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1672,50 +1763,55 @@
       <c r="E19" t="n">
         <v>2</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
         <v>185</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>28</v>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>8</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>7.53</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>8.74</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>9.960000000000001</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>7.6</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>1</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>2.547530455171008</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>0.4840307864824915</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>16</v>
       </c>
     </row>
@@ -1739,50 +1835,55 @@
       <c r="E20" t="n">
         <v>2.5</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
         <v>260</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>62</v>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J20" t="n">
-        <v>3</v>
-      </c>
       <c r="K20" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" t="n">
         <v>9.82</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>10</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>5.13</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>2.2</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>7.802</v>
       </c>
-      <c r="P20" t="n">
-        <v>3</v>
-      </c>
       <c r="Q20" t="n">
+        <v>3</v>
+      </c>
+      <c r="R20" t="n">
         <v>0.916444458800617</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>0.1741244471721172</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>7.5</v>
       </c>
     </row>
@@ -1806,50 +1907,55 @@
       <c r="E21" t="n">
         <v>2.5</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
         <v>260</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>62</v>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>5</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>8.960000000000001</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>9.26</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>7.43</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>3.48</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>7.937</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>1</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>1.527407431334362</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>0.2902074119535287</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>12.5</v>
       </c>
     </row>
@@ -1873,50 +1979,55 @@
       <c r="E22" t="n">
         <v>2.5</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
         <v>260</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>62</v>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>8</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>7.67</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>8.15</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>9.960000000000001</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>4.64</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>7.841499999999999</v>
       </c>
-      <c r="P22" t="n">
-        <v>2</v>
-      </c>
       <c r="Q22" t="n">
+        <v>2</v>
+      </c>
+      <c r="R22" t="n">
         <v>2.443851890134979</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>0.464331859125646</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1940,50 +2051,55 @@
       <c r="E23" t="n">
         <v>2</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
         <v>195</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>75</v>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J23" t="n">
-        <v>3</v>
-      </c>
       <c r="K23" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L23" t="n">
         <v>10</v>
       </c>
       <c r="M23" t="n">
+        <v>10</v>
+      </c>
+      <c r="N23" t="n">
         <v>5.13</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>2.2</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>7.856</v>
       </c>
-      <c r="P23" t="n">
-        <v>3</v>
-      </c>
       <c r="Q23" t="n">
+        <v>3</v>
+      </c>
+      <c r="R23" t="n">
         <v>0.636882613792752</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>0.1210076966206229</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2007,50 +2123,55 @@
       <c r="E24" t="n">
         <v>2</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
         <v>195</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>75</v>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>5</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>9.619999999999999</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>7.43</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>3.48</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>8.2645</v>
       </c>
-      <c r="P24" t="n">
-        <v>2</v>
-      </c>
       <c r="Q24" t="n">
+        <v>2</v>
+      </c>
+      <c r="R24" t="n">
         <v>1.06147102298792</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>0.2016794943677048</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2074,50 +2195,55 @@
       <c r="E25" t="n">
         <v>2</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
         <v>195</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>75</v>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>8</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>8.720000000000001</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>8.74</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>9.960000000000001</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>7.6</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>8.807</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>1</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>1.698353636780672</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="n">
         <v>0.3226871909883277</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>16</v>
       </c>
     </row>
@@ -2141,50 +2267,55 @@
       <c r="E26" t="n">
         <v>2.5</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
         <v>310</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>55</v>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J26" t="n">
-        <v>3</v>
-      </c>
       <c r="K26" t="n">
+        <v>3</v>
+      </c>
+      <c r="L26" t="n">
         <v>9.73</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>10</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>5.13</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>2.2</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>7.775</v>
       </c>
-      <c r="P26" t="n">
-        <v>2</v>
-      </c>
       <c r="Q26" t="n">
+        <v>2</v>
+      </c>
+      <c r="R26" t="n">
         <v>0.9812435619481353</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>0.1864362767701457</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>7.5</v>
       </c>
     </row>
@@ -2208,50 +2339,55 @@
       <c r="E27" t="n">
         <v>2.5</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
         <v>310</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>55</v>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>5</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>8.81</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>9.26</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>7.43</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>3.48</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>7.892</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>1.635405936580226</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>0.3107271279502429</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>12.5</v>
       </c>
     </row>
@@ -2275,50 +2411,55 @@
       <c r="E28" t="n">
         <v>2.5</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
         <v>310</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>55</v>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>7</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>7.89</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>8.52</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>9.32</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>3.07</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>7.6735</v>
       </c>
-      <c r="P28" t="n">
-        <v>3</v>
-      </c>
       <c r="Q28" t="n">
+        <v>3</v>
+      </c>
+      <c r="R28" t="n">
         <v>2.289568311212316</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
         <v>0.43501797913034</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>17.5</v>
       </c>
     </row>
@@ -2342,50 +2483,55 @@
       <c r="E29" t="n">
         <v>2</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
         <v>200</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>62</v>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J29" t="n">
-        <v>3</v>
-      </c>
       <c r="K29" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L29" t="n">
         <v>10</v>
       </c>
       <c r="M29" t="n">
+        <v>10</v>
+      </c>
+      <c r="N29" t="n">
         <v>5.13</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>2.2</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>7.856</v>
       </c>
-      <c r="P29" t="n">
-        <v>3</v>
-      </c>
       <c r="Q29" t="n">
+        <v>3</v>
+      </c>
+      <c r="R29" t="n">
         <v>0.7331555670404936</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
         <v>0.1392995577376938</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2409,50 +2555,55 @@
       <c r="E30" t="n">
         <v>2</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
         <v>200</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>62</v>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>5</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>9.390000000000001</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>7.43</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>3.48</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>8.195499999999999</v>
       </c>
-      <c r="P30" t="n">
-        <v>2</v>
-      </c>
       <c r="Q30" t="n">
+        <v>2</v>
+      </c>
+      <c r="R30" t="n">
         <v>1.221925945067489</v>
       </c>
-      <c r="R30" t="n">
+      <c r="S30" t="n">
         <v>0.232165929562823</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2476,50 +2627,55 @@
       <c r="E31" t="n">
         <v>2</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
         <v>200</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>62</v>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>8</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>8.359999999999999</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>8.74</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>9.960000000000001</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>7.6</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>8.699</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>1</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>1.955081512107983</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>0.3714654873005167</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>16</v>
       </c>
     </row>
@@ -2543,50 +2699,55 @@
       <c r="E32" t="n">
         <v>2.5</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
         <v>250</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>48</v>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J32" t="n">
-        <v>3</v>
-      </c>
       <c r="K32" t="n">
+        <v>3</v>
+      </c>
+      <c r="L32" t="n">
         <v>9.640000000000001</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>10</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>5.13</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>2.2</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>7.747999999999999</v>
       </c>
-      <c r="P32" t="n">
-        <v>2</v>
-      </c>
       <c r="Q32" t="n">
+        <v>2</v>
+      </c>
+      <c r="R32" t="n">
         <v>1.046042665095654</v>
       </c>
-      <c r="R32" t="n">
+      <c r="S32" t="n">
         <v>0.1987481063681742</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>7.5</v>
       </c>
     </row>
@@ -2610,50 +2771,55 @@
       <c r="E33" t="n">
         <v>2.5</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
         <v>250</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>48</v>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>5</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>8.66</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>9.26</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>7.43</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>3.48</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>7.847</v>
       </c>
-      <c r="P33" t="n">
+      <c r="Q33" t="n">
         <v>1</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>1.743404441826089</v>
       </c>
-      <c r="R33" t="n">
+      <c r="S33" t="n">
         <v>0.331246843946957</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>12.5</v>
       </c>
     </row>
@@ -2677,50 +2843,55 @@
       <c r="E34" t="n">
         <v>2.5</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
         <v>250</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>48</v>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
         <v>8</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>7.19</v>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>8.15</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>9.960000000000001</v>
       </c>
-      <c r="N34" t="n">
+      <c r="O34" t="n">
         <v>4.64</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>7.6975</v>
       </c>
-      <c r="P34" t="n">
-        <v>3</v>
-      </c>
       <c r="Q34" t="n">
+        <v>3</v>
+      </c>
+      <c r="R34" t="n">
         <v>2.789447106921743</v>
       </c>
-      <c r="R34" t="n">
+      <c r="S34" t="n">
         <v>0.5299949503151312</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2744,50 +2915,55 @@
       <c r="E35" t="n">
         <v>2</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
         <v>280</v>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>70</v>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J35" t="n">
-        <v>3</v>
-      </c>
       <c r="K35" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L35" t="n">
         <v>10</v>
       </c>
       <c r="M35" t="n">
+        <v>10</v>
+      </c>
+      <c r="N35" t="n">
         <v>5.13</v>
       </c>
-      <c r="N35" t="n">
+      <c r="O35" t="n">
         <v>2.2</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>7.856</v>
       </c>
-      <c r="P35" t="n">
-        <v>3</v>
-      </c>
       <c r="Q35" t="n">
+        <v>3</v>
+      </c>
+      <c r="R35" t="n">
         <v>0.6739106727341909</v>
       </c>
-      <c r="R35" t="n">
+      <c r="S35" t="n">
         <v>0.1280430278194963</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2811,50 +2987,55 @@
       <c r="E36" t="n">
         <v>2</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
         <v>280</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>70</v>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>5</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>9.529999999999999</v>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>7.43</v>
       </c>
-      <c r="N36" t="n">
+      <c r="O36" t="n">
         <v>3.48</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>8.237499999999999</v>
       </c>
-      <c r="P36" t="n">
-        <v>2</v>
-      </c>
       <c r="Q36" t="n">
+        <v>2</v>
+      </c>
+      <c r="R36" t="n">
         <v>1.123184454556985</v>
       </c>
-      <c r="R36" t="n">
+      <c r="S36" t="n">
         <v>0.2134050463658271</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2878,50 +3059,55 @@
       <c r="E37" t="n">
         <v>2</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
         <v>280</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>70</v>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
         <v>7</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>8.9</v>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>9.039999999999999</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>9.32</v>
       </c>
-      <c r="N37" t="n">
+      <c r="O37" t="n">
         <v>6.37</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>8.653499999999999</v>
       </c>
-      <c r="P37" t="n">
+      <c r="Q37" t="n">
         <v>1</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>1.572458236379779</v>
       </c>
-      <c r="R37" t="n">
+      <c r="S37" t="n">
         <v>0.298767064912158</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>14</v>
       </c>
     </row>
@@ -2945,50 +3131,55 @@
       <c r="E38" t="n">
         <v>1.5</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
         <v>140</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>38</v>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J38" t="n">
+      <c r="K38" t="n">
         <v>4</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>9.83</v>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
         <v>10</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>4.33</v>
       </c>
-      <c r="N38" t="n">
+      <c r="O38" t="n">
         <v>2.86</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>7.744</v>
       </c>
-      <c r="P38" t="n">
-        <v>3</v>
-      </c>
       <c r="Q38" t="n">
+        <v>3</v>
+      </c>
+      <c r="R38" t="n">
         <v>0.9108902499594012</v>
       </c>
-      <c r="R38" t="n">
+      <c r="S38" t="n">
         <v>0.1730691474922862</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3012,50 +3203,55 @@
       <c r="E39" t="n">
         <v>1.5</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
         <v>140</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>38</v>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
         <v>6</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>9.19</v>
       </c>
-      <c r="L39" t="n">
+      <c r="M39" t="n">
         <v>9.779999999999999</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>6.79</v>
       </c>
-      <c r="N39" t="n">
+      <c r="O39" t="n">
         <v>5.01</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>8.2895</v>
       </c>
-      <c r="P39" t="n">
-        <v>2</v>
-      </c>
       <c r="Q39" t="n">
+        <v>2</v>
+      </c>
+      <c r="R39" t="n">
         <v>1.366335374939102</v>
       </c>
-      <c r="R39" t="n">
+      <c r="S39" t="n">
         <v>0.2596037212384293</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>9</v>
       </c>
     </row>
@@ -3079,50 +3275,55 @@
       <c r="E40" t="n">
         <v>1.5</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
         <v>140</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>38</v>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J40" t="n">
+      <c r="K40" t="n">
         <v>10</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>7.91</v>
       </c>
-      <c r="L40" t="n">
+      <c r="M40" t="n">
         <v>8.890000000000001</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>8.140000000000001</v>
       </c>
-      <c r="N40" t="n">
+      <c r="O40" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>8.379999999999999</v>
       </c>
-      <c r="P40" t="n">
+      <c r="Q40" t="n">
         <v>1</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>2.277225624898503</v>
       </c>
-      <c r="R40" t="n">
+      <c r="S40" t="n">
         <v>0.4326728687307156</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>15</v>
       </c>
     </row>
@@ -3146,50 +3347,55 @@
       <c r="E41" t="n">
         <v>2</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
         <v>160</v>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>52</v>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J41" t="n">
-        <v>3</v>
-      </c>
       <c r="K41" t="n">
+        <v>3</v>
+      </c>
+      <c r="L41" t="n">
         <v>9.98</v>
       </c>
-      <c r="L41" t="n">
+      <c r="M41" t="n">
         <v>10</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>5.13</v>
       </c>
-      <c r="N41" t="n">
+      <c r="O41" t="n">
         <v>2.2</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>7.85</v>
       </c>
-      <c r="P41" t="n">
-        <v>3</v>
-      </c>
       <c r="Q41" t="n">
+        <v>3</v>
+      </c>
+      <c r="R41" t="n">
         <v>0.8072116849233715</v>
       </c>
-      <c r="R41" t="n">
+      <c r="S41" t="n">
         <v>0.1533702201354406</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3213,50 +3419,55 @@
       <c r="E42" t="n">
         <v>2</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
         <v>160</v>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>52</v>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
         <v>5</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>9.220000000000001</v>
       </c>
-      <c r="L42" t="n">
+      <c r="M42" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>7.43</v>
       </c>
-      <c r="N42" t="n">
+      <c r="O42" t="n">
         <v>3.48</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>8.144499999999999</v>
       </c>
-      <c r="P42" t="n">
-        <v>2</v>
-      </c>
       <c r="Q42" t="n">
+        <v>2</v>
+      </c>
+      <c r="R42" t="n">
         <v>1.345352808205619</v>
       </c>
-      <c r="R42" t="n">
+      <c r="S42" t="n">
         <v>0.2556170335590677</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3280,50 +3491,55 @@
       <c r="E43" t="n">
         <v>2</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
         <v>160</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
         <v>52</v>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J43" t="n">
+      <c r="K43" t="n">
         <v>8</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>8.08</v>
       </c>
-      <c r="L43" t="n">
+      <c r="M43" t="n">
         <v>8.74</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>9.960000000000001</v>
       </c>
-      <c r="N43" t="n">
+      <c r="O43" t="n">
         <v>7.6</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>8.615</v>
       </c>
-      <c r="P43" t="n">
+      <c r="Q43" t="n">
         <v>1</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>2.152564493128991</v>
       </c>
-      <c r="R43" t="n">
+      <c r="S43" t="n">
         <v>0.4089872536945083</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>16</v>
       </c>
     </row>
@@ -3347,50 +3563,55 @@
       <c r="E44" t="n">
         <v>2.5</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
         <v>255</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>48</v>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J44" t="n">
-        <v>3</v>
-      </c>
       <c r="K44" t="n">
+        <v>3</v>
+      </c>
+      <c r="L44" t="n">
         <v>9.640000000000001</v>
       </c>
-      <c r="L44" t="n">
+      <c r="M44" t="n">
         <v>10</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>5.13</v>
       </c>
-      <c r="N44" t="n">
+      <c r="O44" t="n">
         <v>2.2</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>7.747999999999999</v>
       </c>
-      <c r="P44" t="n">
-        <v>2</v>
-      </c>
       <c r="Q44" t="n">
+        <v>2</v>
+      </c>
+      <c r="R44" t="n">
         <v>1.046042665095654</v>
       </c>
-      <c r="R44" t="n">
+      <c r="S44" t="n">
         <v>0.1987481063681742</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>7.5</v>
       </c>
     </row>
@@ -3414,50 +3635,55 @@
       <c r="E45" t="n">
         <v>2.5</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
         <v>255</v>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
         <v>48</v>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
         <v>5</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>8.66</v>
       </c>
-      <c r="L45" t="n">
+      <c r="M45" t="n">
         <v>9.26</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>7.43</v>
       </c>
-      <c r="N45" t="n">
+      <c r="O45" t="n">
         <v>3.48</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>7.847</v>
       </c>
-      <c r="P45" t="n">
+      <c r="Q45" t="n">
         <v>1</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>1.743404441826089</v>
       </c>
-      <c r="R45" t="n">
+      <c r="S45" t="n">
         <v>0.331246843946957</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>12.5</v>
       </c>
     </row>
@@ -3481,50 +3707,55 @@
       <c r="E46" t="n">
         <v>2.5</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F46" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
         <v>255</v>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>48</v>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J46" t="n">
+      <c r="K46" t="n">
         <v>8</v>
       </c>
-      <c r="K46" t="n">
+      <c r="L46" t="n">
         <v>7.19</v>
       </c>
-      <c r="L46" t="n">
+      <c r="M46" t="n">
         <v>8.15</v>
       </c>
-      <c r="M46" t="n">
+      <c r="N46" t="n">
         <v>9.960000000000001</v>
       </c>
-      <c r="N46" t="n">
+      <c r="O46" t="n">
         <v>4.64</v>
       </c>
-      <c r="O46" t="n">
+      <c r="P46" t="n">
         <v>7.6975</v>
       </c>
-      <c r="P46" t="n">
-        <v>3</v>
-      </c>
       <c r="Q46" t="n">
+        <v>3</v>
+      </c>
+      <c r="R46" t="n">
         <v>2.789447106921743</v>
       </c>
-      <c r="R46" t="n">
+      <c r="S46" t="n">
         <v>0.5299949503151312</v>
       </c>
-      <c r="S46" t="n">
+      <c r="T46" t="n">
         <v>20</v>
       </c>
     </row>
@@ -3548,50 +3779,55 @@
       <c r="E47" t="n">
         <v>2</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F47" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
         <v>195</v>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H47" t="n">
+      <c r="I47" t="n">
         <v>35</v>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J47" t="n">
-        <v>3</v>
-      </c>
       <c r="K47" t="n">
+        <v>3</v>
+      </c>
+      <c r="L47" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="L47" t="n">
+      <c r="M47" t="n">
         <v>10</v>
       </c>
-      <c r="M47" t="n">
+      <c r="N47" t="n">
         <v>5.13</v>
       </c>
-      <c r="N47" t="n">
+      <c r="O47" t="n">
         <v>2.2</v>
       </c>
-      <c r="O47" t="n">
+      <c r="P47" t="n">
         <v>7.795999999999999</v>
       </c>
-      <c r="P47" t="n">
-        <v>3</v>
-      </c>
       <c r="Q47" t="n">
+        <v>3</v>
+      </c>
+      <c r="R47" t="n">
         <v>0.9331070853242645</v>
       </c>
-      <c r="R47" t="n">
+      <c r="S47" t="n">
         <v>0.1772903462116102</v>
       </c>
-      <c r="S47" t="n">
+      <c r="T47" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3615,50 +3851,55 @@
       <c r="E48" t="n">
         <v>2</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F48" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
         <v>195</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
         <v>35</v>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J48" t="n">
+      <c r="K48" t="n">
         <v>5</v>
       </c>
-      <c r="K48" t="n">
+      <c r="L48" t="n">
         <v>8.92</v>
       </c>
-      <c r="L48" t="n">
+      <c r="M48" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="M48" t="n">
+      <c r="N48" t="n">
         <v>7.43</v>
       </c>
-      <c r="N48" t="n">
+      <c r="O48" t="n">
         <v>3.48</v>
       </c>
-      <c r="O48" t="n">
+      <c r="P48" t="n">
         <v>8.054499999999999</v>
       </c>
-      <c r="P48" t="n">
-        <v>2</v>
-      </c>
       <c r="Q48" t="n">
+        <v>2</v>
+      </c>
+      <c r="R48" t="n">
         <v>1.555178475540441</v>
       </c>
-      <c r="R48" t="n">
+      <c r="S48" t="n">
         <v>0.2954839103526837</v>
       </c>
-      <c r="S48" t="n">
+      <c r="T48" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3682,50 +3923,55 @@
       <c r="E49" t="n">
         <v>2</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F49" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
         <v>195</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
         <v>35</v>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J49" t="n">
+      <c r="K49" t="n">
         <v>8</v>
       </c>
-      <c r="K49" t="n">
+      <c r="L49" t="n">
         <v>7.61</v>
       </c>
-      <c r="L49" t="n">
+      <c r="M49" t="n">
         <v>8.74</v>
       </c>
-      <c r="M49" t="n">
+      <c r="N49" t="n">
         <v>9.960000000000001</v>
       </c>
-      <c r="N49" t="n">
+      <c r="O49" t="n">
         <v>7.6</v>
       </c>
-      <c r="O49" t="n">
+      <c r="P49" t="n">
         <v>8.474</v>
       </c>
-      <c r="P49" t="n">
+      <c r="Q49" t="n">
         <v>1</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="R49" t="n">
         <v>2.488285560864705</v>
       </c>
-      <c r="R49" t="n">
+      <c r="S49" t="n">
         <v>0.472774256564294</v>
       </c>
-      <c r="S49" t="n">
+      <c r="T49" t="n">
         <v>16</v>
       </c>
     </row>
@@ -3749,50 +3995,55 @@
       <c r="E50" t="n">
         <v>2.5</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F50" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
         <v>250</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H50" t="n">
+      <c r="I50" t="n">
         <v>60</v>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J50" t="n">
-        <v>3</v>
-      </c>
       <c r="K50" t="n">
+        <v>3</v>
+      </c>
+      <c r="L50" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="L50" t="n">
+      <c r="M50" t="n">
         <v>10</v>
       </c>
-      <c r="M50" t="n">
+      <c r="N50" t="n">
         <v>5.13</v>
       </c>
-      <c r="N50" t="n">
+      <c r="O50" t="n">
         <v>2.2</v>
       </c>
-      <c r="O50" t="n">
+      <c r="P50" t="n">
         <v>7.795999999999999</v>
       </c>
-      <c r="P50" t="n">
-        <v>3</v>
-      </c>
       <c r="Q50" t="n">
+        <v>3</v>
+      </c>
+      <c r="R50" t="n">
         <v>0.9349584882713364</v>
       </c>
-      <c r="R50" t="n">
+      <c r="S50" t="n">
         <v>0.1776421127715539</v>
       </c>
-      <c r="S50" t="n">
+      <c r="T50" t="n">
         <v>7.5</v>
       </c>
     </row>
@@ -3816,50 +4067,55 @@
       <c r="E51" t="n">
         <v>2.5</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F51" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
         <v>250</v>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
         <v>60</v>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J51" t="n">
+      <c r="K51" t="n">
         <v>5</v>
       </c>
-      <c r="K51" t="n">
+      <c r="L51" t="n">
         <v>8.92</v>
       </c>
-      <c r="L51" t="n">
+      <c r="M51" t="n">
         <v>9.26</v>
       </c>
-      <c r="M51" t="n">
+      <c r="N51" t="n">
         <v>7.43</v>
       </c>
-      <c r="N51" t="n">
+      <c r="O51" t="n">
         <v>3.48</v>
       </c>
-      <c r="O51" t="n">
+      <c r="P51" t="n">
         <v>7.925</v>
       </c>
-      <c r="P51" t="n">
+      <c r="Q51" t="n">
         <v>1</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="R51" t="n">
         <v>1.558264147118894</v>
       </c>
-      <c r="R51" t="n">
+      <c r="S51" t="n">
         <v>0.2960701879525898</v>
       </c>
-      <c r="S51" t="n">
+      <c r="T51" t="n">
         <v>12.5</v>
       </c>
     </row>
@@ -3883,50 +4139,55 @@
       <c r="E52" t="n">
         <v>2.5</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F52" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
         <v>250</v>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H52" t="n">
+      <c r="I52" t="n">
         <v>60</v>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J52" t="n">
+      <c r="K52" t="n">
         <v>8</v>
       </c>
-      <c r="K52" t="n">
+      <c r="L52" t="n">
         <v>7.6</v>
       </c>
-      <c r="L52" t="n">
+      <c r="M52" t="n">
         <v>8.15</v>
       </c>
-      <c r="M52" t="n">
+      <c r="N52" t="n">
         <v>9.960000000000001</v>
       </c>
-      <c r="N52" t="n">
+      <c r="O52" t="n">
         <v>4.64</v>
       </c>
-      <c r="O52" t="n">
+      <c r="P52" t="n">
         <v>7.8205</v>
       </c>
-      <c r="P52" t="n">
-        <v>2</v>
-      </c>
       <c r="Q52" t="n">
+        <v>2</v>
+      </c>
+      <c r="R52" t="n">
         <v>2.49322263539023</v>
       </c>
-      <c r="R52" t="n">
+      <c r="S52" t="n">
         <v>0.4737123007241438</v>
       </c>
-      <c r="S52" t="n">
+      <c r="T52" t="n">
         <v>20</v>
       </c>
     </row>
@@ -3950,50 +4211,55 @@
       <c r="E53" t="n">
         <v>3.5</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F53" s="1" t="inlineStr">
+        <is>
+          <t>high_flow</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
         <v>240</v>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H53" t="n">
+      <c r="I53" t="n">
         <v>18</v>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
         <v>4</v>
       </c>
-      <c r="K53" t="n">
+      <c r="L53" t="n">
         <v>7.97</v>
       </c>
-      <c r="L53" t="n">
+      <c r="M53" t="n">
         <v>9.039999999999999</v>
       </c>
-      <c r="M53" t="n">
+      <c r="N53" t="n">
         <v>6.34</v>
       </c>
-      <c r="N53" t="n">
+      <c r="O53" t="n">
         <v>1.51</v>
       </c>
-      <c r="O53" t="n">
+      <c r="P53" t="n">
         <v>7.049499999999999</v>
       </c>
-      <c r="P53" t="n">
+      <c r="Q53" t="n">
         <v>1</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="R53" t="n">
         <v>2.229089148274632</v>
       </c>
-      <c r="R53" t="n">
+      <c r="S53" t="n">
         <v>0.4235269381721801</v>
       </c>
-      <c r="S53" t="n">
+      <c r="T53" t="n">
         <v>14</v>
       </c>
     </row>
@@ -4017,50 +4283,55 @@
       <c r="E54" t="n">
         <v>3.5</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F54" s="1" t="inlineStr">
+        <is>
+          <t>high_flow</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
         <v>240</v>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H54" t="n">
+      <c r="I54" t="n">
         <v>18</v>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J54" t="n">
+      <c r="K54" t="n">
         <v>6</v>
       </c>
-      <c r="K54" t="n">
+      <c r="L54" t="n">
         <v>6.41</v>
       </c>
-      <c r="L54" t="n">
+      <c r="M54" t="n">
         <v>8</v>
       </c>
-      <c r="M54" t="n">
+      <c r="N54" t="n">
         <v>8.42</v>
       </c>
-      <c r="N54" t="n">
+      <c r="O54" t="n">
         <v>1.51</v>
       </c>
-      <c r="O54" t="n">
+      <c r="P54" t="n">
         <v>6.6335</v>
       </c>
-      <c r="P54" t="n">
-        <v>2</v>
-      </c>
       <c r="Q54" t="n">
+        <v>2</v>
+      </c>
+      <c r="R54" t="n">
         <v>3.343633722411948</v>
       </c>
-      <c r="R54" t="n">
+      <c r="S54" t="n">
         <v>0.6352904072582701</v>
       </c>
-      <c r="S54" t="n">
+      <c r="T54" t="n">
         <v>21</v>
       </c>
     </row>
@@ -4084,50 +4355,55 @@
       <c r="E55" t="n">
         <v>3.5</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F55" s="1" t="inlineStr">
+        <is>
+          <t>high_flow</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
         <v>240</v>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H55" t="n">
+      <c r="I55" t="n">
         <v>18</v>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
         <v>8</v>
       </c>
-      <c r="K55" t="n">
+      <c r="L55" t="n">
         <v>4.84</v>
       </c>
-      <c r="L55" t="n">
+      <c r="M55" t="n">
         <v>6.96</v>
       </c>
-      <c r="M55" t="n">
+      <c r="N55" t="n">
         <v>9.9</v>
       </c>
-      <c r="N55" t="n">
+      <c r="O55" t="n">
         <v>4.64</v>
       </c>
-      <c r="O55" t="n">
+      <c r="P55" t="n">
         <v>6.564</v>
       </c>
-      <c r="P55" t="n">
-        <v>3</v>
-      </c>
       <c r="Q55" t="n">
+        <v>3</v>
+      </c>
+      <c r="R55" t="n">
         <v>4.458178296549264</v>
       </c>
-      <c r="R55" t="n">
+      <c r="S55" t="n">
         <v>0.8470538763443601</v>
       </c>
-      <c r="S55" t="n">
+      <c r="T55" t="n">
         <v>28</v>
       </c>
     </row>
@@ -4151,50 +4427,55 @@
       <c r="E56" t="n">
         <v>1.5</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F56" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
         <v>150</v>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="H56" t="n">
+      <c r="I56" t="n">
         <v>90</v>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J56" t="n">
+      <c r="K56" t="n">
         <v>4</v>
-      </c>
-      <c r="K56" t="n">
-        <v>10</v>
       </c>
       <c r="L56" t="n">
         <v>10</v>
       </c>
       <c r="M56" t="n">
+        <v>10</v>
+      </c>
+      <c r="N56" t="n">
         <v>6.34</v>
       </c>
-      <c r="N56" t="n">
+      <c r="O56" t="n">
         <v>2.86</v>
       </c>
-      <c r="O56" t="n">
+      <c r="P56" t="n">
         <v>8.196999999999999</v>
       </c>
-      <c r="P56" t="n">
-        <v>3</v>
-      </c>
       <c r="Q56" t="n">
+        <v>3</v>
+      </c>
+      <c r="R56" t="n">
         <v>0.6368826137927521</v>
       </c>
-      <c r="R56" t="n">
+      <c r="S56" t="n">
         <v>0.1210076966206229</v>
       </c>
-      <c r="S56" t="n">
+      <c r="T56" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4218,50 +4499,55 @@
       <c r="E57" t="n">
         <v>1.5</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F57" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
         <v>150</v>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="H57" t="n">
+      <c r="I57" t="n">
         <v>90</v>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J57" t="n">
+      <c r="K57" t="n">
         <v>7</v>
       </c>
-      <c r="K57" t="n">
+      <c r="L57" t="n">
         <v>9.539999999999999</v>
       </c>
-      <c r="L57" t="n">
+      <c r="M57" t="n">
         <v>9.56</v>
       </c>
-      <c r="M57" t="n">
+      <c r="N57" t="n">
         <v>9.32</v>
       </c>
-      <c r="N57" t="n">
+      <c r="O57" t="n">
         <v>6.37</v>
       </c>
-      <c r="O57" t="n">
+      <c r="P57" t="n">
         <v>9.027500000000002</v>
       </c>
-      <c r="P57" t="n">
+      <c r="Q57" t="n">
         <v>1</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="R57" t="n">
         <v>1.114544574137316</v>
       </c>
-      <c r="R57" t="n">
+      <c r="S57" t="n">
         <v>0.2117634690860901</v>
       </c>
-      <c r="S57" t="n">
+      <c r="T57" t="n">
         <v>10.5</v>
       </c>
     </row>
@@ -4285,50 +4571,55 @@
       <c r="E58" t="n">
         <v>1.5</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
         <v>150</v>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>90</v>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>10</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>8.869999999999999</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>8.890000000000001</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>9.59</v>
       </c>
-      <c r="N58" t="n">
+      <c r="O58" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="O58" t="n">
+      <c r="P58" t="n">
         <v>8.957999999999998</v>
       </c>
-      <c r="P58" t="n">
-        <v>2</v>
-      </c>
       <c r="Q58" t="n">
+        <v>2</v>
+      </c>
+      <c r="R58" t="n">
         <v>1.59220653448188</v>
       </c>
-      <c r="R58" t="n">
+      <c r="S58" t="n">
         <v>0.3025192415515572</v>
       </c>
-      <c r="S58" t="n">
+      <c r="T58" t="n">
         <v>15</v>
       </c>
     </row>
@@ -4352,50 +4643,55 @@
       <c r="E59" t="n">
         <v>2.5</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F59" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
         <v>340</v>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H59" t="n">
+      <c r="I59" t="n">
         <v>40</v>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J59" t="n">
+      <c r="K59" t="n">
         <v>5</v>
       </c>
-      <c r="K59" t="n">
+      <c r="L59" t="n">
         <v>8.48</v>
       </c>
-      <c r="L59" t="n">
+      <c r="M59" t="n">
         <v>9.26</v>
       </c>
-      <c r="M59" t="n">
+      <c r="N59" t="n">
         <v>7.43</v>
       </c>
-      <c r="N59" t="n">
+      <c r="O59" t="n">
         <v>1.51</v>
       </c>
-      <c r="O59" t="n">
+      <c r="P59" t="n">
         <v>7.4975</v>
       </c>
-      <c r="P59" t="n">
-        <v>2</v>
-      </c>
       <c r="Q59" t="n">
+        <v>2</v>
+      </c>
+      <c r="R59" t="n">
         <v>1.86683130496422</v>
       </c>
-      <c r="R59" t="n">
+      <c r="S59" t="n">
         <v>0.3546979479432018</v>
       </c>
-      <c r="S59" t="n">
+      <c r="T59" t="n">
         <v>12.5</v>
       </c>
     </row>
@@ -4419,50 +4715,55 @@
       <c r="E60" t="n">
         <v>2.5</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F60" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
         <v>340</v>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H60" t="n">
+      <c r="I60" t="n">
         <v>40</v>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J60" t="n">
+      <c r="K60" t="n">
         <v>8</v>
       </c>
-      <c r="K60" t="n">
+      <c r="L60" t="n">
         <v>6.91</v>
       </c>
-      <c r="L60" t="n">
+      <c r="M60" t="n">
         <v>8.15</v>
       </c>
-      <c r="M60" t="n">
+      <c r="N60" t="n">
         <v>9.9</v>
       </c>
-      <c r="N60" t="n">
+      <c r="O60" t="n">
         <v>4.64</v>
       </c>
-      <c r="O60" t="n">
+      <c r="P60" t="n">
         <v>7.6015</v>
       </c>
-      <c r="P60" t="n">
+      <c r="Q60" t="n">
         <v>1</v>
       </c>
-      <c r="Q60" t="n">
+      <c r="R60" t="n">
         <v>2.986930087942751</v>
       </c>
-      <c r="R60" t="n">
+      <c r="S60" t="n">
         <v>0.5675167167091227</v>
       </c>
-      <c r="S60" t="n">
+      <c r="T60" t="n">
         <v>20</v>
       </c>
     </row>
@@ -4486,50 +4787,55 @@
       <c r="E61" t="n">
         <v>2.5</v>
       </c>
-      <c r="F61" t="n">
+      <c r="F61" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
         <v>340</v>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H61" t="n">
+      <c r="I61" t="n">
         <v>40</v>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J61" t="n">
+      <c r="K61" t="n">
         <v>12</v>
       </c>
-      <c r="K61" t="n">
+      <c r="L61" t="n">
         <v>4.81</v>
       </c>
-      <c r="L61" t="n">
+      <c r="M61" t="n">
         <v>6.67</v>
       </c>
-      <c r="M61" t="n">
+      <c r="N61" t="n">
         <v>7.62</v>
       </c>
-      <c r="N61" t="n">
+      <c r="O61" t="n">
         <v>6.69</v>
       </c>
-      <c r="O61" t="n">
+      <c r="P61" t="n">
         <v>6.305</v>
       </c>
-      <c r="P61" t="n">
-        <v>3</v>
-      </c>
       <c r="Q61" t="n">
+        <v>3</v>
+      </c>
+      <c r="R61" t="n">
         <v>4.480395131914127</v>
       </c>
-      <c r="R61" t="n">
+      <c r="S61" t="n">
         <v>0.8512750750636842</v>
       </c>
-      <c r="S61" t="n">
+      <c r="T61" t="n">
         <v>30</v>
       </c>
     </row>

--- a/workbooks/scenarios/ShowerRAGScenarios.xlsx
+++ b/workbooks/scenarios/ShowerRAGScenarios.xlsx
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.######"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -48,11 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -422,4794 +417,4794 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>scenario_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>question</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>household_size</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>gpm</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>flow_rate</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>tank_size</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>water_heater_temp</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>utility_budget</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>housing_type</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>outdoor_temp</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>alternative</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>duration_min</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>energy_cost_score</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>environmental_score</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>comfort_score</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>practicality_score</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>mavt_score</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>raw_kwh</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>raw_cost</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>raw_water_gallons</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Blue Bell, PA</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>low_flow</t>
         </is>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" t="n">
         <v>40</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" t="n">
         <v>120</v>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="I2" t="n">
         <v>195</v>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" t="n">
         <v>75</v>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="M2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="3" t="n">
+      <c r="N2" t="n">
         <v>9.619999999999999</v>
       </c>
-      <c r="O2" s="3" t="n">
+      <c r="O2" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="P2" s="3" t="n">
+      <c r="P2" t="n">
         <v>7.43</v>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="Q2" t="n">
         <v>3.48</v>
       </c>
-      <c r="R2" s="3" t="n">
+      <c r="R2" t="n">
         <v>8.2645</v>
       </c>
-      <c r="S2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T2" s="3" t="n">
+      <c r="S2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T2" t="n">
         <v>1.06147102298792</v>
       </c>
-      <c r="U2" s="3" t="n">
+      <c r="U2" t="n">
         <v>0.2016794943677048</v>
       </c>
-      <c r="V2" s="3" t="n">
+      <c r="V2" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Blue Bell, PA</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>low_flow</t>
         </is>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" t="n">
         <v>40</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" t="n">
         <v>120</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="I3" t="n">
         <v>195</v>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" t="n">
         <v>75</v>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="M3" t="n">
         <v>8</v>
       </c>
-      <c r="N3" s="3" t="n">
+      <c r="N3" t="n">
         <v>8.720000000000001</v>
       </c>
-      <c r="O3" s="3" t="n">
+      <c r="O3" t="n">
         <v>8.74</v>
       </c>
-      <c r="P3" s="3" t="n">
+      <c r="P3" t="n">
         <v>9.960000000000001</v>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="Q3" t="n">
         <v>7.6</v>
       </c>
-      <c r="R3" s="3" t="n">
+      <c r="R3" t="n">
         <v>8.807</v>
       </c>
-      <c r="S3" s="2" t="n">
+      <c r="S3" t="n">
         <v>1</v>
       </c>
-      <c r="T3" s="3" t="n">
+      <c r="T3" t="n">
         <v>1.698353636780672</v>
       </c>
-      <c r="U3" s="3" t="n">
+      <c r="U3" t="n">
         <v>0.3226871909883277</v>
       </c>
-      <c r="V3" s="3" t="n">
+      <c r="V3" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Blue Bell, PA</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>low_flow</t>
         </is>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" t="n">
         <v>40</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" t="n">
         <v>120</v>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="I4" t="n">
         <v>195</v>
       </c>
-      <c r="J4" s="1" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" t="n">
         <v>75</v>
       </c>
-      <c r="L4" s="1" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="M4" t="n">
         <v>12</v>
       </c>
-      <c r="N4" s="3" t="n">
+      <c r="N4" t="n">
         <v>7.53</v>
       </c>
-      <c r="O4" s="3" t="n">
+      <c r="O4" t="n">
         <v>7.56</v>
       </c>
-      <c r="P4" s="3" t="n">
+      <c r="P4" t="n">
         <v>9.210000000000001</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="Q4" t="n">
         <v>6.69</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" t="n">
         <v>7.7505</v>
       </c>
-      <c r="S4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="3" t="n">
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
         <v>2.547530455171008</v>
       </c>
-      <c r="U4" s="3" t="n">
+      <c r="U4" t="n">
         <v>0.4840307864824915</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="V4" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Media, PA</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" s="3" t="n">
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
         <v>2.5</v>
       </c>
-      <c r="F5" s="1" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" t="n">
         <v>50</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" t="n">
         <v>120</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="I5" t="n">
         <v>255</v>
       </c>
-      <c r="J5" s="1" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" t="n">
         <v>85</v>
       </c>
-      <c r="L5" s="1" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="M5" t="n">
         <v>5</v>
       </c>
-      <c r="N5" s="3" t="n">
+      <c r="N5" t="n">
         <v>9.24</v>
       </c>
-      <c r="O5" s="3" t="n">
+      <c r="O5" t="n">
         <v>9.26</v>
       </c>
-      <c r="P5" s="3" t="n">
+      <c r="P5" t="n">
         <v>7.43</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="Q5" t="n">
         <v>3.48</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" t="n">
         <v>8.020999999999999</v>
       </c>
-      <c r="S5" s="2" t="n">
+      <c r="S5" t="n">
         <v>1</v>
       </c>
-      <c r="T5" s="3" t="n">
+      <c r="T5" t="n">
         <v>1.3268387787349</v>
       </c>
-      <c r="U5" s="3" t="n">
+      <c r="U5" t="n">
         <v>0.2520993679596309</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="V5" t="n">
         <v>12.5</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Media, PA</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" s="3" t="n">
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
         <v>2.5</v>
       </c>
-      <c r="F6" s="1" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" t="n">
         <v>50</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" t="n">
         <v>120</v>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="I6" t="n">
         <v>255</v>
       </c>
-      <c r="J6" s="1" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" t="n">
         <v>85</v>
       </c>
-      <c r="L6" s="1" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="M6" t="n">
         <v>8</v>
       </c>
-      <c r="N6" s="3" t="n">
+      <c r="N6" t="n">
         <v>8.119999999999999</v>
       </c>
-      <c r="O6" s="3" t="n">
+      <c r="O6" t="n">
         <v>8.15</v>
       </c>
-      <c r="P6" s="3" t="n">
+      <c r="P6" t="n">
         <v>9.960000000000001</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="Q6" t="n">
         <v>4.64</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" t="n">
         <v>7.976499999999999</v>
       </c>
-      <c r="S6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T6" s="3" t="n">
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="n">
         <v>2.12294204597584</v>
       </c>
-      <c r="U6" s="3" t="n">
+      <c r="U6" t="n">
         <v>0.4033589887354095</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Media, PA</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" s="3" t="n">
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
         <v>2.5</v>
       </c>
-      <c r="F7" s="1" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" t="n">
         <v>50</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" t="n">
         <v>120</v>
       </c>
-      <c r="I7" s="3" t="n">
+      <c r="I7" t="n">
         <v>255</v>
       </c>
-      <c r="J7" s="1" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" t="n">
         <v>85</v>
       </c>
-      <c r="L7" s="1" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="M7" s="2" t="n">
+      <c r="M7" t="n">
         <v>12</v>
       </c>
-      <c r="N7" s="3" t="n">
+      <c r="N7" t="n">
         <v>6.63</v>
       </c>
-      <c r="O7" s="3" t="n">
+      <c r="O7" t="n">
         <v>6.67</v>
       </c>
-      <c r="P7" s="3" t="n">
+      <c r="P7" t="n">
         <v>9.210000000000001</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="Q7" t="n">
         <v>6.69</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" t="n">
         <v>7.169</v>
       </c>
-      <c r="S7" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" s="3" t="n">
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
         <v>3.18441306896376</v>
       </c>
-      <c r="U7" s="3" t="n">
+      <c r="U7" t="n">
         <v>0.6050384831031144</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Indiana, PA</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>low_flow</t>
         </is>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" t="n">
         <v>30</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" t="n">
         <v>110</v>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="I8" t="n">
         <v>155</v>
       </c>
-      <c r="J8" s="1" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" t="n">
         <v>48</v>
       </c>
-      <c r="L8" s="1" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M8" s="2" t="n">
+      <c r="M8" t="n">
         <v>4</v>
       </c>
-      <c r="N8" s="3" t="n">
+      <c r="N8" t="n">
         <v>9.539999999999999</v>
       </c>
-      <c r="O8" s="3" t="n">
+      <c r="O8" t="n">
         <v>9.93</v>
       </c>
-      <c r="P8" s="3" t="n">
+      <c r="P8" t="n">
         <v>6</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q8" t="n">
         <v>2.86</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" t="n">
         <v>7.9665</v>
       </c>
-      <c r="S8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" s="3" t="n">
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
         <v>1.115778842768697</v>
       </c>
-      <c r="U8" s="3" t="n">
+      <c r="U8" t="n">
         <v>0.2119979801260525</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
+      <c r="A9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Indiana, PA</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>low_flow</t>
         </is>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" t="n">
         <v>30</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" t="n">
         <v>110</v>
       </c>
-      <c r="I9" s="3" t="n">
+      <c r="I9" t="n">
         <v>155</v>
       </c>
-      <c r="J9" s="1" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" t="n">
         <v>48</v>
       </c>
-      <c r="L9" s="1" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="M9" s="2" t="n">
+      <c r="M9" t="n">
         <v>6</v>
       </c>
-      <c r="N9" s="3" t="n">
+      <c r="N9" t="n">
         <v>8.76</v>
       </c>
-      <c r="O9" s="3" t="n">
+      <c r="O9" t="n">
         <v>9.33</v>
       </c>
-      <c r="P9" s="3" t="n">
+      <c r="P9" t="n">
         <v>7.56</v>
       </c>
-      <c r="Q9" s="3" t="n">
+      <c r="Q9" t="n">
         <v>5.01</v>
       </c>
-      <c r="R9" s="3" t="n">
+      <c r="R9" t="n">
         <v>8.157</v>
       </c>
-      <c r="S9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" s="3" t="n">
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
         <v>1.673668264153046</v>
       </c>
-      <c r="U9" s="3" t="n">
+      <c r="U9" t="n">
         <v>0.3179969701890787</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
+      <c r="A10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Indiana, PA</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>low_flow</t>
         </is>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" t="n">
         <v>30</v>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="H10" t="n">
         <v>110</v>
       </c>
-      <c r="I10" s="3" t="n">
+      <c r="I10" t="n">
         <v>155</v>
       </c>
-      <c r="J10" s="1" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="K10" t="n">
         <v>48</v>
       </c>
-      <c r="L10" s="1" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M10" s="2" t="n">
+      <c r="M10" t="n">
         <v>10</v>
       </c>
-      <c r="N10" s="3" t="n">
+      <c r="N10" t="n">
         <v>7.19</v>
       </c>
-      <c r="O10" s="3" t="n">
+      <c r="O10" t="n">
         <v>8.15</v>
       </c>
-      <c r="P10" s="3" t="n">
+      <c r="P10" t="n">
         <v>9.94</v>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="Q10" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" t="n">
         <v>8.265000000000001</v>
       </c>
-      <c r="S10" s="2" t="n">
+      <c r="S10" t="n">
         <v>1</v>
       </c>
-      <c r="T10" s="3" t="n">
+      <c r="T10" t="n">
         <v>2.789447106921743</v>
       </c>
-      <c r="U10" s="3" t="n">
+      <c r="U10" t="n">
         <v>0.5299949503151312</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" s="3" t="n">
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="n">
         <v>2.5</v>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="G11" t="n">
         <v>50</v>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="H11" t="n">
         <v>120</v>
       </c>
-      <c r="I11" s="3" t="n">
+      <c r="I11" t="n">
         <v>245</v>
       </c>
-      <c r="J11" s="1" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" t="n">
         <v>62</v>
       </c>
-      <c r="L11" s="1" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M11" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N11" s="3" t="n">
+      <c r="M11" t="n">
+        <v>3</v>
+      </c>
+      <c r="N11" t="n">
         <v>9.82</v>
       </c>
-      <c r="O11" s="3" t="n">
+      <c r="O11" t="n">
         <v>10</v>
       </c>
-      <c r="P11" s="3" t="n">
+      <c r="P11" t="n">
         <v>5.13</v>
       </c>
-      <c r="Q11" s="3" t="n">
+      <c r="Q11" t="n">
         <v>2.2</v>
       </c>
-      <c r="R11" s="3" t="n">
+      <c r="R11" t="n">
         <v>7.802</v>
       </c>
-      <c r="S11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" s="3" t="n">
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
         <v>0.916444458800617</v>
       </c>
-      <c r="U11" s="3" t="n">
+      <c r="U11" t="n">
         <v>0.1741244471721172</v>
       </c>
-      <c r="V11" s="3" t="n">
+      <c r="V11" t="n">
         <v>7.5</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="1" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" s="3" t="n">
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
         <v>2.5</v>
       </c>
-      <c r="F12" s="1" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" t="n">
         <v>50</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" t="n">
         <v>120</v>
       </c>
-      <c r="I12" s="3" t="n">
+      <c r="I12" t="n">
         <v>245</v>
       </c>
-      <c r="J12" s="1" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" t="n">
         <v>62</v>
       </c>
-      <c r="L12" s="1" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M12" s="2" t="n">
+      <c r="M12" t="n">
         <v>5</v>
       </c>
-      <c r="N12" s="3" t="n">
+      <c r="N12" t="n">
         <v>8.960000000000001</v>
       </c>
-      <c r="O12" s="3" t="n">
+      <c r="O12" t="n">
         <v>9.26</v>
       </c>
-      <c r="P12" s="3" t="n">
+      <c r="P12" t="n">
         <v>7.08</v>
       </c>
-      <c r="Q12" s="3" t="n">
+      <c r="Q12" t="n">
         <v>3.48</v>
       </c>
-      <c r="R12" s="3" t="n">
+      <c r="R12" t="n">
         <v>7.867000000000001</v>
       </c>
-      <c r="S12" s="2" t="n">
+      <c r="S12" t="n">
         <v>1</v>
       </c>
-      <c r="T12" s="3" t="n">
+      <c r="T12" t="n">
         <v>1.527407431334362</v>
       </c>
-      <c r="U12" s="3" t="n">
+      <c r="U12" t="n">
         <v>0.2902074119535287</v>
       </c>
-      <c r="V12" s="3" t="n">
+      <c r="V12" t="n">
         <v>12.5</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" t="n">
         <v>4</v>
       </c>
-      <c r="B13" s="1" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E13" s="3" t="n">
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
         <v>2.5</v>
       </c>
-      <c r="F13" s="1" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G13" t="n">
         <v>50</v>
       </c>
-      <c r="H13" s="3" t="n">
+      <c r="H13" t="n">
         <v>120</v>
       </c>
-      <c r="I13" s="3" t="n">
+      <c r="I13" t="n">
         <v>245</v>
       </c>
-      <c r="J13" s="1" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" t="n">
         <v>62</v>
       </c>
-      <c r="L13" s="1" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M13" s="2" t="n">
+      <c r="M13" t="n">
         <v>8</v>
       </c>
-      <c r="N13" s="3" t="n">
+      <c r="N13" t="n">
         <v>7.67</v>
       </c>
-      <c r="O13" s="3" t="n">
+      <c r="O13" t="n">
         <v>8.15</v>
       </c>
-      <c r="P13" s="3" t="n">
+      <c r="P13" t="n">
         <v>9.48</v>
       </c>
-      <c r="Q13" s="3" t="n">
+      <c r="Q13" t="n">
         <v>4.64</v>
       </c>
-      <c r="R13" s="3" t="n">
+      <c r="R13" t="n">
         <v>7.745499999999999</v>
       </c>
-      <c r="S13" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" s="3" t="n">
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
         <v>2.443851890134979</v>
       </c>
-      <c r="U13" s="3" t="n">
+      <c r="U13" t="n">
         <v>0.464331859125646</v>
       </c>
-      <c r="V13" s="3" t="n">
+      <c r="V13" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" t="n">
         <v>5</v>
       </c>
-      <c r="B14" s="1" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>West Mifflin, PA</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" t="n">
         <v>4</v>
       </c>
-      <c r="E14" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" s="1" t="inlineStr">
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" t="n">
         <v>60</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="H14" t="n">
         <v>125</v>
       </c>
-      <c r="I14" s="3" t="n">
+      <c r="I14" t="n">
         <v>295</v>
       </c>
-      <c r="J14" s="1" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" t="n">
         <v>70</v>
       </c>
-      <c r="L14" s="1" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M14" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3" t="n">
+      <c r="M14" t="n">
+        <v>3</v>
+      </c>
+      <c r="N14" t="n">
         <v>9.69</v>
       </c>
-      <c r="O14" s="3" t="n">
+      <c r="O14" t="n">
         <v>9.779999999999999</v>
       </c>
-      <c r="P14" s="3" t="n">
+      <c r="P14" t="n">
         <v>5.13</v>
       </c>
-      <c r="Q14" s="3" t="n">
+      <c r="Q14" t="n">
         <v>2.2</v>
       </c>
-      <c r="R14" s="3" t="n">
+      <c r="R14" t="n">
         <v>7.685999999999999</v>
       </c>
-      <c r="S14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" s="3" t="n">
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
         <v>1.010866009101286</v>
       </c>
-      <c r="U14" s="3" t="n">
+      <c r="U14" t="n">
         <v>0.1920645417292444</v>
       </c>
-      <c r="V14" s="3" t="n">
+      <c r="V14" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" t="n">
         <v>5</v>
       </c>
-      <c r="B15" s="1" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>West Mifflin, PA</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" t="n">
         <v>4</v>
       </c>
-      <c r="E15" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" s="1" t="inlineStr">
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="G15" t="n">
         <v>60</v>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="H15" t="n">
         <v>125</v>
       </c>
-      <c r="I15" s="3" t="n">
+      <c r="I15" t="n">
         <v>295</v>
       </c>
-      <c r="J15" s="1" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" t="n">
         <v>70</v>
       </c>
-      <c r="L15" s="1" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M15" s="2" t="n">
+      <c r="M15" t="n">
         <v>4</v>
       </c>
-      <c r="N15" s="3" t="n">
+      <c r="N15" t="n">
         <v>9.210000000000001</v>
       </c>
-      <c r="O15" s="3" t="n">
+      <c r="O15" t="n">
         <v>9.33</v>
       </c>
-      <c r="P15" s="3" t="n">
+      <c r="P15" t="n">
         <v>6.26</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" t="n">
         <v>2.86</v>
       </c>
-      <c r="R15" s="3" t="n">
+      <c r="R15" t="n">
         <v>7.7095</v>
       </c>
-      <c r="S15" s="2" t="n">
+      <c r="S15" t="n">
         <v>1</v>
       </c>
-      <c r="T15" s="3" t="n">
+      <c r="T15" t="n">
         <v>1.347821345468382</v>
       </c>
-      <c r="U15" s="3" t="n">
+      <c r="U15" t="n">
         <v>0.2560860556389926</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="V15" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" t="n">
         <v>5</v>
       </c>
-      <c r="B16" s="1" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>West Mifflin, PA</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D16" t="n">
         <v>4</v>
       </c>
-      <c r="E16" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" s="1" t="inlineStr">
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" t="n">
         <v>60</v>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="H16" t="n">
         <v>125</v>
       </c>
-      <c r="I16" s="3" t="n">
+      <c r="I16" t="n">
         <v>295</v>
       </c>
-      <c r="J16" s="1" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" t="n">
         <v>70</v>
       </c>
-      <c r="L16" s="1" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="M16" s="2" t="n">
+      <c r="M16" t="n">
         <v>6</v>
       </c>
-      <c r="N16" s="3" t="n">
+      <c r="N16" t="n">
         <v>8.27</v>
       </c>
-      <c r="O16" s="3" t="n">
+      <c r="O16" t="n">
         <v>8.44</v>
       </c>
-      <c r="P16" s="3" t="n">
+      <c r="P16" t="n">
         <v>8.220000000000001</v>
       </c>
-      <c r="Q16" s="3" t="n">
+      <c r="Q16" t="n">
         <v>1.51</v>
       </c>
-      <c r="R16" s="3" t="n">
+      <c r="R16" t="n">
         <v>7.305499999999999</v>
       </c>
-      <c r="S16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" s="3" t="n">
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
         <v>2.021732018202572</v>
       </c>
-      <c r="U16" s="3" t="n">
+      <c r="U16" t="n">
         <v>0.3841290834584888</v>
       </c>
-      <c r="V16" s="3" t="n">
+      <c r="V16" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" t="n">
         <v>6</v>
       </c>
-      <c r="B17" s="1" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F17" s="1" t="inlineStr">
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>low_flow</t>
         </is>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="G17" t="n">
         <v>40</v>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="H17" t="n">
         <v>120</v>
       </c>
-      <c r="I17" s="3" t="n">
+      <c r="I17" t="n">
         <v>185</v>
       </c>
-      <c r="J17" s="1" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="K17" s="3" t="n">
+      <c r="K17" t="n">
         <v>28</v>
       </c>
-      <c r="L17" s="1" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M17" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N17" s="3" t="n">
+      <c r="M17" t="n">
+        <v>3</v>
+      </c>
+      <c r="N17" t="n">
         <v>9.77</v>
       </c>
-      <c r="O17" s="3" t="n">
+      <c r="O17" t="n">
         <v>10</v>
       </c>
-      <c r="P17" s="3" t="n">
+      <c r="P17" t="n">
         <v>5.13</v>
       </c>
-      <c r="Q17" s="3" t="n">
+      <c r="Q17" t="n">
         <v>2.2</v>
       </c>
-      <c r="R17" s="3" t="n">
+      <c r="R17" t="n">
         <v>7.786999999999999</v>
       </c>
-      <c r="S17" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" s="3" t="n">
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
         <v>0.955323920689128</v>
       </c>
-      <c r="U17" s="3" t="n">
+      <c r="U17" t="n">
         <v>0.1815115449309343</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" t="n">
         <v>6</v>
       </c>
-      <c r="B18" s="1" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F18" s="1" t="inlineStr">
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>low_flow</t>
         </is>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="G18" t="n">
         <v>40</v>
       </c>
-      <c r="H18" s="3" t="n">
+      <c r="H18" t="n">
         <v>120</v>
       </c>
-      <c r="I18" s="3" t="n">
+      <c r="I18" t="n">
         <v>185</v>
       </c>
-      <c r="J18" s="1" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" t="n">
         <v>28</v>
       </c>
-      <c r="L18" s="1" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M18" s="2" t="n">
+      <c r="M18" t="n">
         <v>5</v>
       </c>
-      <c r="N18" s="3" t="n">
+      <c r="N18" t="n">
         <v>8.869999999999999</v>
       </c>
-      <c r="O18" s="3" t="n">
+      <c r="O18" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="P18" s="3" t="n">
+      <c r="P18" t="n">
         <v>6.7</v>
       </c>
-      <c r="Q18" s="3" t="n">
+      <c r="Q18" t="n">
         <v>3.48</v>
       </c>
-      <c r="R18" s="3" t="n">
+      <c r="R18" t="n">
         <v>7.8935</v>
       </c>
-      <c r="S18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" s="3" t="n">
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
         <v>1.59220653448188</v>
       </c>
-      <c r="U18" s="3" t="n">
+      <c r="U18" t="n">
         <v>0.3025192415515572</v>
       </c>
-      <c r="V18" s="3" t="n">
+      <c r="V18" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" t="n">
         <v>6</v>
       </c>
-      <c r="B19" s="1" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F19" s="1" t="inlineStr">
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>low_flow</t>
         </is>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="G19" t="n">
         <v>40</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H19" t="n">
         <v>120</v>
       </c>
-      <c r="I19" s="3" t="n">
+      <c r="I19" t="n">
         <v>185</v>
       </c>
-      <c r="J19" s="1" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" t="n">
         <v>28</v>
       </c>
-      <c r="L19" s="1" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M19" s="2" t="n">
+      <c r="M19" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="3" t="n">
+      <c r="N19" t="n">
         <v>7.53</v>
       </c>
-      <c r="O19" s="3" t="n">
+      <c r="O19" t="n">
         <v>8.74</v>
       </c>
-      <c r="P19" s="3" t="n">
+      <c r="P19" t="n">
         <v>8.69</v>
       </c>
-      <c r="Q19" s="3" t="n">
+      <c r="Q19" t="n">
         <v>7.6</v>
       </c>
-      <c r="R19" s="3" t="n">
+      <c r="R19" t="n">
         <v>8.196</v>
       </c>
-      <c r="S19" s="2" t="n">
+      <c r="S19" t="n">
         <v>1</v>
       </c>
-      <c r="T19" s="3" t="n">
+      <c r="T19" t="n">
         <v>2.547530455171008</v>
       </c>
-      <c r="U19" s="3" t="n">
+      <c r="U19" t="n">
         <v>0.4840307864824915</v>
       </c>
-      <c r="V19" s="3" t="n">
+      <c r="V19" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" t="n">
         <v>7</v>
       </c>
-      <c r="B20" s="1" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Exton, PA</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E20" s="3" t="n">
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
         <v>2.5</v>
       </c>
-      <c r="F20" s="1" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" t="n">
         <v>50</v>
       </c>
-      <c r="H20" s="3" t="n">
+      <c r="H20" t="n">
         <v>120</v>
       </c>
-      <c r="I20" s="3" t="n">
+      <c r="I20" t="n">
         <v>260</v>
       </c>
-      <c r="J20" s="1" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" t="n">
         <v>62</v>
       </c>
-      <c r="L20" s="1" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M20" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N20" s="3" t="n">
+      <c r="M20" t="n">
+        <v>3</v>
+      </c>
+      <c r="N20" t="n">
         <v>9.82</v>
       </c>
-      <c r="O20" s="3" t="n">
+      <c r="O20" t="n">
         <v>10</v>
       </c>
-      <c r="P20" s="3" t="n">
+      <c r="P20" t="n">
         <v>5.13</v>
       </c>
-      <c r="Q20" s="3" t="n">
+      <c r="Q20" t="n">
         <v>2.2</v>
       </c>
-      <c r="R20" s="3" t="n">
+      <c r="R20" t="n">
         <v>7.802</v>
       </c>
-      <c r="S20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" s="3" t="n">
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
         <v>0.916444458800617</v>
       </c>
-      <c r="U20" s="3" t="n">
+      <c r="U20" t="n">
         <v>0.1741244471721172</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="V20" t="n">
         <v>7.5</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" t="n">
         <v>7</v>
       </c>
-      <c r="B21" s="1" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Exton, PA</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E21" s="3" t="n">
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
         <v>2.5</v>
       </c>
-      <c r="F21" s="1" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="G21" s="3" t="n">
+      <c r="G21" t="n">
         <v>50</v>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="H21" t="n">
         <v>120</v>
       </c>
-      <c r="I21" s="3" t="n">
+      <c r="I21" t="n">
         <v>260</v>
       </c>
-      <c r="J21" s="1" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" t="n">
         <v>62</v>
       </c>
-      <c r="L21" s="1" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M21" s="2" t="n">
+      <c r="M21" t="n">
         <v>5</v>
       </c>
-      <c r="N21" s="3" t="n">
+      <c r="N21" t="n">
         <v>8.960000000000001</v>
       </c>
-      <c r="O21" s="3" t="n">
+      <c r="O21" t="n">
         <v>9.26</v>
       </c>
-      <c r="P21" s="3" t="n">
+      <c r="P21" t="n">
         <v>7.08</v>
       </c>
-      <c r="Q21" s="3" t="n">
+      <c r="Q21" t="n">
         <v>3.48</v>
       </c>
-      <c r="R21" s="3" t="n">
+      <c r="R21" t="n">
         <v>7.867000000000001</v>
       </c>
-      <c r="S21" s="2" t="n">
+      <c r="S21" t="n">
         <v>1</v>
       </c>
-      <c r="T21" s="3" t="n">
+      <c r="T21" t="n">
         <v>1.527407431334362</v>
       </c>
-      <c r="U21" s="3" t="n">
+      <c r="U21" t="n">
         <v>0.2902074119535287</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="V21" t="n">
         <v>12.5</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" t="n">
         <v>7</v>
       </c>
-      <c r="B22" s="1" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Exton, PA</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E22" s="3" t="n">
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
         <v>2.5</v>
       </c>
-      <c r="F22" s="1" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="G22" s="3" t="n">
+      <c r="G22" t="n">
         <v>50</v>
       </c>
-      <c r="H22" s="3" t="n">
+      <c r="H22" t="n">
         <v>120</v>
       </c>
-      <c r="I22" s="3" t="n">
+      <c r="I22" t="n">
         <v>260</v>
       </c>
-      <c r="J22" s="1" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" t="n">
         <v>62</v>
       </c>
-      <c r="L22" s="1" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M22" s="2" t="n">
+      <c r="M22" t="n">
         <v>8</v>
       </c>
-      <c r="N22" s="3" t="n">
+      <c r="N22" t="n">
         <v>7.67</v>
       </c>
-      <c r="O22" s="3" t="n">
+      <c r="O22" t="n">
         <v>8.15</v>
       </c>
-      <c r="P22" s="3" t="n">
+      <c r="P22" t="n">
         <v>9.48</v>
       </c>
-      <c r="Q22" s="3" t="n">
+      <c r="Q22" t="n">
         <v>4.64</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="R22" t="n">
         <v>7.745499999999999</v>
       </c>
-      <c r="S22" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T22" s="3" t="n">
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="n">
         <v>2.443851890134979</v>
       </c>
-      <c r="U22" s="3" t="n">
+      <c r="U22" t="n">
         <v>0.464331859125646</v>
       </c>
-      <c r="V22" s="3" t="n">
+      <c r="V22" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" t="n">
         <v>8</v>
       </c>
-      <c r="B23" s="1" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Pottstown, PA</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F23" s="1" t="inlineStr">
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>low_flow</t>
         </is>
       </c>
-      <c r="G23" s="3" t="n">
+      <c r="G23" t="n">
         <v>40</v>
       </c>
-      <c r="H23" s="3" t="n">
+      <c r="H23" t="n">
         <v>115</v>
       </c>
-      <c r="I23" s="3" t="n">
+      <c r="I23" t="n">
         <v>195</v>
       </c>
-      <c r="J23" s="1" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" t="n">
         <v>75</v>
       </c>
-      <c r="L23" s="1" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M23" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N23" s="3" t="n">
+      <c r="M23" t="n">
+        <v>3</v>
+      </c>
+      <c r="N23" t="n">
         <v>10</v>
       </c>
-      <c r="O23" s="3" t="n">
+      <c r="O23" t="n">
         <v>10</v>
       </c>
-      <c r="P23" s="3" t="n">
+      <c r="P23" t="n">
         <v>5.13</v>
       </c>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" t="n">
         <v>2.2</v>
       </c>
-      <c r="R23" s="3" t="n">
+      <c r="R23" t="n">
         <v>7.856</v>
       </c>
-      <c r="S23" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" s="3" t="n">
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
         <v>0.636882613792752</v>
       </c>
-      <c r="U23" s="3" t="n">
+      <c r="U23" t="n">
         <v>0.1210076966206229</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="V23" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" t="n">
         <v>8</v>
       </c>
-      <c r="B24" s="1" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Pottstown, PA</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F24" s="1" t="inlineStr">
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>low_flow</t>
         </is>
       </c>
-      <c r="G24" s="3" t="n">
+      <c r="G24" t="n">
         <v>40</v>
       </c>
-      <c r="H24" s="3" t="n">
+      <c r="H24" t="n">
         <v>115</v>
       </c>
-      <c r="I24" s="3" t="n">
+      <c r="I24" t="n">
         <v>195</v>
       </c>
-      <c r="J24" s="1" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="K24" s="3" t="n">
+      <c r="K24" t="n">
         <v>75</v>
       </c>
-      <c r="L24" s="1" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M24" s="2" t="n">
+      <c r="M24" t="n">
         <v>5</v>
       </c>
-      <c r="N24" s="3" t="n">
+      <c r="N24" t="n">
         <v>9.619999999999999</v>
       </c>
-      <c r="O24" s="3" t="n">
+      <c r="O24" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="P24" s="3" t="n">
+      <c r="P24" t="n">
         <v>7.43</v>
       </c>
-      <c r="Q24" s="3" t="n">
+      <c r="Q24" t="n">
         <v>3.48</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" t="n">
         <v>8.2645</v>
       </c>
-      <c r="S24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T24" s="3" t="n">
+      <c r="S24" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" t="n">
         <v>1.06147102298792</v>
       </c>
-      <c r="U24" s="3" t="n">
+      <c r="U24" t="n">
         <v>0.2016794943677048</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" t="n">
         <v>8</v>
       </c>
-      <c r="B25" s="1" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Pottstown, PA</t>
         </is>
       </c>
-      <c r="D25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F25" s="1" t="inlineStr">
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>low_flow</t>
         </is>
       </c>
-      <c r="G25" s="3" t="n">
+      <c r="G25" t="n">
         <v>40</v>
       </c>
-      <c r="H25" s="3" t="n">
+      <c r="H25" t="n">
         <v>115</v>
       </c>
-      <c r="I25" s="3" t="n">
+      <c r="I25" t="n">
         <v>195</v>
       </c>
-      <c r="J25" s="1" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" t="n">
         <v>75</v>
       </c>
-      <c r="L25" s="1" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M25" s="2" t="n">
+      <c r="M25" t="n">
         <v>8</v>
       </c>
-      <c r="N25" s="3" t="n">
+      <c r="N25" t="n">
         <v>8.720000000000001</v>
       </c>
-      <c r="O25" s="3" t="n">
+      <c r="O25" t="n">
         <v>8.74</v>
       </c>
-      <c r="P25" s="3" t="n">
+      <c r="P25" t="n">
         <v>9.960000000000001</v>
       </c>
-      <c r="Q25" s="3" t="n">
+      <c r="Q25" t="n">
         <v>7.6</v>
       </c>
-      <c r="R25" s="3" t="n">
+      <c r="R25" t="n">
         <v>8.807</v>
       </c>
-      <c r="S25" s="2" t="n">
+      <c r="S25" t="n">
         <v>1</v>
       </c>
-      <c r="T25" s="3" t="n">
+      <c r="T25" t="n">
         <v>1.698353636780672</v>
       </c>
-      <c r="U25" s="3" t="n">
+      <c r="U25" t="n">
         <v>0.3226871909883277</v>
       </c>
-      <c r="V25" s="3" t="n">
+      <c r="V25" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" t="n">
         <v>9</v>
       </c>
-      <c r="B26" s="1" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Phoenixville, PA</t>
         </is>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="D26" t="n">
         <v>4</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="E26" t="n">
         <v>2.5</v>
       </c>
-      <c r="F26" s="1" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="G26" s="3" t="n">
+      <c r="G26" t="n">
         <v>60</v>
       </c>
-      <c r="H26" s="3" t="n">
+      <c r="H26" t="n">
         <v>120</v>
       </c>
-      <c r="I26" s="3" t="n">
+      <c r="I26" t="n">
         <v>310</v>
       </c>
-      <c r="J26" s="1" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="K26" t="n">
         <v>55</v>
       </c>
-      <c r="L26" s="1" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M26" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N26" s="3" t="n">
+      <c r="M26" t="n">
+        <v>3</v>
+      </c>
+      <c r="N26" t="n">
         <v>9.73</v>
       </c>
-      <c r="O26" s="3" t="n">
+      <c r="O26" t="n">
         <v>10</v>
       </c>
-      <c r="P26" s="3" t="n">
+      <c r="P26" t="n">
         <v>5.13</v>
       </c>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" t="n">
         <v>2.2</v>
       </c>
-      <c r="R26" s="3" t="n">
+      <c r="R26" t="n">
         <v>7.775</v>
       </c>
-      <c r="S26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T26" s="3" t="n">
+      <c r="S26" t="n">
+        <v>2</v>
+      </c>
+      <c r="T26" t="n">
         <v>0.9812435619481353</v>
       </c>
-      <c r="U26" s="3" t="n">
+      <c r="U26" t="n">
         <v>0.1864362767701457</v>
       </c>
-      <c r="V26" s="3" t="n">
+      <c r="V26" t="n">
         <v>7.5</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" t="n">
         <v>9</v>
       </c>
-      <c r="B27" s="1" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Phoenixville, PA</t>
         </is>
       </c>
-      <c r="D27" s="2" t="n">
+      <c r="D27" t="n">
         <v>4</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="E27" t="n">
         <v>2.5</v>
       </c>
-      <c r="F27" s="1" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="G27" s="3" t="n">
+      <c r="G27" t="n">
         <v>60</v>
       </c>
-      <c r="H27" s="3" t="n">
+      <c r="H27" t="n">
         <v>120</v>
       </c>
-      <c r="I27" s="3" t="n">
+      <c r="I27" t="n">
         <v>310</v>
       </c>
-      <c r="J27" s="1" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" t="n">
         <v>55</v>
       </c>
-      <c r="L27" s="1" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M27" s="2" t="n">
+      <c r="M27" t="n">
         <v>5</v>
       </c>
-      <c r="N27" s="3" t="n">
+      <c r="N27" t="n">
         <v>8.81</v>
       </c>
-      <c r="O27" s="3" t="n">
+      <c r="O27" t="n">
         <v>9.26</v>
       </c>
-      <c r="P27" s="3" t="n">
+      <c r="P27" t="n">
         <v>6.94</v>
       </c>
-      <c r="Q27" s="3" t="n">
+      <c r="Q27" t="n">
         <v>3.48</v>
       </c>
-      <c r="R27" s="3" t="n">
+      <c r="R27" t="n">
         <v>7.794</v>
       </c>
-      <c r="S27" s="2" t="n">
+      <c r="S27" t="n">
         <v>1</v>
       </c>
-      <c r="T27" s="3" t="n">
+      <c r="T27" t="n">
         <v>1.635405936580226</v>
       </c>
-      <c r="U27" s="3" t="n">
+      <c r="U27" t="n">
         <v>0.3107271279502429</v>
       </c>
-      <c r="V27" s="3" t="n">
+      <c r="V27" t="n">
         <v>12.5</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" t="n">
         <v>9</v>
       </c>
-      <c r="B28" s="1" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Phoenixville, PA</t>
         </is>
       </c>
-      <c r="D28" s="2" t="n">
+      <c r="D28" t="n">
         <v>4</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="E28" t="n">
         <v>2.5</v>
       </c>
-      <c r="F28" s="1" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="G28" s="3" t="n">
+      <c r="G28" t="n">
         <v>60</v>
       </c>
-      <c r="H28" s="3" t="n">
+      <c r="H28" t="n">
         <v>120</v>
       </c>
-      <c r="I28" s="3" t="n">
+      <c r="I28" t="n">
         <v>310</v>
       </c>
-      <c r="J28" s="1" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" t="n">
         <v>55</v>
       </c>
-      <c r="L28" s="1" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="M28" s="2" t="n">
+      <c r="M28" t="n">
         <v>7</v>
       </c>
-      <c r="N28" s="3" t="n">
+      <c r="N28" t="n">
         <v>7.89</v>
       </c>
-      <c r="O28" s="3" t="n">
+      <c r="O28" t="n">
         <v>8.52</v>
       </c>
-      <c r="P28" s="3" t="n">
+      <c r="P28" t="n">
         <v>8.49</v>
       </c>
-      <c r="Q28" s="3" t="n">
+      <c r="Q28" t="n">
         <v>3.07</v>
       </c>
-      <c r="R28" s="3" t="n">
+      <c r="R28" t="n">
         <v>7.5075</v>
       </c>
-      <c r="S28" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T28" s="3" t="n">
+      <c r="S28" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" t="n">
         <v>2.289568311212316</v>
       </c>
-      <c r="U28" s="3" t="n">
+      <c r="U28" t="n">
         <v>0.43501797913034</v>
       </c>
-      <c r="V28" s="3" t="n">
+      <c r="V28" t="n">
         <v>17.5</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" t="n">
         <v>10</v>
       </c>
-      <c r="B29" s="1" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Bethlehem, PA</t>
         </is>
       </c>
-      <c r="D29" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F29" s="1" t="inlineStr">
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>low_flow</t>
         </is>
       </c>
-      <c r="G29" s="3" t="n">
+      <c r="G29" t="n">
         <v>40</v>
       </c>
-      <c r="H29" s="3" t="n">
+      <c r="H29" t="n">
         <v>115</v>
       </c>
-      <c r="I29" s="3" t="n">
+      <c r="I29" t="n">
         <v>200</v>
       </c>
-      <c r="J29" s="1" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" t="n">
         <v>62</v>
       </c>
-      <c r="L29" s="1" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M29" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N29" s="3" t="n">
+      <c r="M29" t="n">
+        <v>3</v>
+      </c>
+      <c r="N29" t="n">
         <v>10</v>
       </c>
-      <c r="O29" s="3" t="n">
+      <c r="O29" t="n">
         <v>10</v>
       </c>
-      <c r="P29" s="3" t="n">
+      <c r="P29" t="n">
         <v>5.13</v>
       </c>
-      <c r="Q29" s="3" t="n">
+      <c r="Q29" t="n">
         <v>2.2</v>
       </c>
-      <c r="R29" s="3" t="n">
+      <c r="R29" t="n">
         <v>7.856</v>
       </c>
-      <c r="S29" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T29" s="3" t="n">
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="n">
         <v>0.7331555670404936</v>
       </c>
-      <c r="U29" s="3" t="n">
+      <c r="U29" t="n">
         <v>0.1392995577376938</v>
       </c>
-      <c r="V29" s="3" t="n">
+      <c r="V29" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" t="n">
         <v>10</v>
       </c>
-      <c r="B30" s="1" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Bethlehem, PA</t>
         </is>
       </c>
-      <c r="D30" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F30" s="1" t="inlineStr">
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>low_flow</t>
         </is>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="G30" t="n">
         <v>40</v>
       </c>
-      <c r="H30" s="3" t="n">
+      <c r="H30" t="n">
         <v>115</v>
       </c>
-      <c r="I30" s="3" t="n">
+      <c r="I30" t="n">
         <v>200</v>
       </c>
-      <c r="J30" s="1" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" t="n">
         <v>62</v>
       </c>
-      <c r="L30" s="1" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M30" s="2" t="n">
+      <c r="M30" t="n">
         <v>5</v>
       </c>
-      <c r="N30" s="3" t="n">
+      <c r="N30" t="n">
         <v>9.390000000000001</v>
       </c>
-      <c r="O30" s="3" t="n">
+      <c r="O30" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="P30" s="3" t="n">
+      <c r="P30" t="n">
         <v>7.08</v>
       </c>
-      <c r="Q30" s="3" t="n">
+      <c r="Q30" t="n">
         <v>3.48</v>
       </c>
-      <c r="R30" s="3" t="n">
+      <c r="R30" t="n">
         <v>8.125500000000001</v>
       </c>
-      <c r="S30" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T30" s="3" t="n">
+      <c r="S30" t="n">
+        <v>2</v>
+      </c>
+      <c r="T30" t="n">
         <v>1.221925945067489</v>
       </c>
-      <c r="U30" s="3" t="n">
+      <c r="U30" t="n">
         <v>0.232165929562823</v>
       </c>
-      <c r="V30" s="3" t="n">
+      <c r="V30" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" t="n">
         <v>10</v>
       </c>
-      <c r="B31" s="1" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Bethlehem, PA</t>
         </is>
       </c>
-      <c r="D31" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F31" s="1" t="inlineStr">
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>low_flow</t>
         </is>
       </c>
-      <c r="G31" s="3" t="n">
+      <c r="G31" t="n">
         <v>40</v>
       </c>
-      <c r="H31" s="3" t="n">
+      <c r="H31" t="n">
         <v>115</v>
       </c>
-      <c r="I31" s="3" t="n">
+      <c r="I31" t="n">
         <v>200</v>
       </c>
-      <c r="J31" s="1" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="K31" s="3" t="n">
+      <c r="K31" t="n">
         <v>62</v>
       </c>
-      <c r="L31" s="1" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M31" s="2" t="n">
+      <c r="M31" t="n">
         <v>8</v>
       </c>
-      <c r="N31" s="3" t="n">
+      <c r="N31" t="n">
         <v>8.359999999999999</v>
       </c>
-      <c r="O31" s="3" t="n">
+      <c r="O31" t="n">
         <v>8.74</v>
       </c>
-      <c r="P31" s="3" t="n">
+      <c r="P31" t="n">
         <v>9.48</v>
       </c>
-      <c r="Q31" s="3" t="n">
+      <c r="Q31" t="n">
         <v>7.6</v>
       </c>
-      <c r="R31" s="3" t="n">
+      <c r="R31" t="n">
         <v>8.603</v>
       </c>
-      <c r="S31" s="2" t="n">
+      <c r="S31" t="n">
         <v>1</v>
       </c>
-      <c r="T31" s="3" t="n">
+      <c r="T31" t="n">
         <v>1.955081512107983</v>
       </c>
-      <c r="U31" s="3" t="n">
+      <c r="U31" t="n">
         <v>0.3714654873005167</v>
       </c>
-      <c r="V31" s="3" t="n">
+      <c r="V31" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" t="n">
         <v>11</v>
       </c>
-      <c r="B32" s="1" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Hazleton, PA</t>
         </is>
       </c>
-      <c r="D32" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E32" s="3" t="n">
+      <c r="D32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" t="n">
         <v>2.5</v>
       </c>
-      <c r="F32" s="1" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="G32" s="3" t="n">
+      <c r="G32" t="n">
         <v>50</v>
       </c>
-      <c r="H32" s="3" t="n">
+      <c r="H32" t="n">
         <v>120</v>
       </c>
-      <c r="I32" s="3" t="n">
+      <c r="I32" t="n">
         <v>250</v>
       </c>
-      <c r="J32" s="1" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="K32" s="3" t="n">
+      <c r="K32" t="n">
         <v>48</v>
       </c>
-      <c r="L32" s="1" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M32" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N32" s="3" t="n">
+      <c r="M32" t="n">
+        <v>3</v>
+      </c>
+      <c r="N32" t="n">
         <v>9.640000000000001</v>
       </c>
-      <c r="O32" s="3" t="n">
+      <c r="O32" t="n">
         <v>10</v>
       </c>
-      <c r="P32" s="3" t="n">
+      <c r="P32" t="n">
         <v>5.13</v>
       </c>
-      <c r="Q32" s="3" t="n">
+      <c r="Q32" t="n">
         <v>2.2</v>
       </c>
-      <c r="R32" s="3" t="n">
+      <c r="R32" t="n">
         <v>7.747999999999999</v>
       </c>
-      <c r="S32" s="2" t="n">
+      <c r="S32" t="n">
         <v>1</v>
       </c>
-      <c r="T32" s="3" t="n">
+      <c r="T32" t="n">
         <v>1.046042665095654</v>
       </c>
-      <c r="U32" s="3" t="n">
+      <c r="U32" t="n">
         <v>0.1987481063681742</v>
       </c>
-      <c r="V32" s="3" t="n">
+      <c r="V32" t="n">
         <v>7.5</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" t="n">
         <v>11</v>
       </c>
-      <c r="B33" s="1" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Hazleton, PA</t>
         </is>
       </c>
-      <c r="D33" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E33" s="3" t="n">
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="n">
         <v>2.5</v>
       </c>
-      <c r="F33" s="1" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="G33" s="3" t="n">
+      <c r="G33" t="n">
         <v>50</v>
       </c>
-      <c r="H33" s="3" t="n">
+      <c r="H33" t="n">
         <v>120</v>
       </c>
-      <c r="I33" s="3" t="n">
+      <c r="I33" t="n">
         <v>250</v>
       </c>
-      <c r="J33" s="1" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="K33" t="n">
         <v>48</v>
       </c>
-      <c r="L33" s="1" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M33" s="2" t="n">
+      <c r="M33" t="n">
         <v>5</v>
       </c>
-      <c r="N33" s="3" t="n">
+      <c r="N33" t="n">
         <v>8.66</v>
       </c>
-      <c r="O33" s="3" t="n">
+      <c r="O33" t="n">
         <v>9.26</v>
       </c>
-      <c r="P33" s="3" t="n">
+      <c r="P33" t="n">
         <v>6.81</v>
       </c>
-      <c r="Q33" s="3" t="n">
+      <c r="Q33" t="n">
         <v>3.48</v>
       </c>
-      <c r="R33" s="3" t="n">
+      <c r="R33" t="n">
         <v>7.723</v>
       </c>
-      <c r="S33" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T33" s="3" t="n">
+      <c r="S33" t="n">
+        <v>2</v>
+      </c>
+      <c r="T33" t="n">
         <v>1.743404441826089</v>
       </c>
-      <c r="U33" s="3" t="n">
+      <c r="U33" t="n">
         <v>0.331246843946957</v>
       </c>
-      <c r="V33" s="3" t="n">
+      <c r="V33" t="n">
         <v>12.5</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" t="n">
         <v>11</v>
       </c>
-      <c r="B34" s="1" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Hazleton, PA</t>
         </is>
       </c>
-      <c r="D34" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E34" s="3" t="n">
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="n">
         <v>2.5</v>
       </c>
-      <c r="F34" s="1" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="G34" t="n">
         <v>50</v>
       </c>
-      <c r="H34" s="3" t="n">
+      <c r="H34" t="n">
         <v>120</v>
       </c>
-      <c r="I34" s="3" t="n">
+      <c r="I34" t="n">
         <v>250</v>
       </c>
-      <c r="J34" s="1" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="K34" t="n">
         <v>48</v>
       </c>
-      <c r="L34" s="1" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M34" s="2" t="n">
+      <c r="M34" t="n">
         <v>8</v>
       </c>
-      <c r="N34" s="3" t="n">
+      <c r="N34" t="n">
         <v>7.19</v>
       </c>
-      <c r="O34" s="3" t="n">
+      <c r="O34" t="n">
         <v>8.15</v>
       </c>
-      <c r="P34" s="3" t="n">
+      <c r="P34" t="n">
         <v>8.93</v>
       </c>
-      <c r="Q34" s="3" t="n">
+      <c r="Q34" t="n">
         <v>4.64</v>
       </c>
-      <c r="R34" s="3" t="n">
+      <c r="R34" t="n">
         <v>7.4915</v>
       </c>
-      <c r="S34" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T34" s="3" t="n">
+      <c r="S34" t="n">
+        <v>3</v>
+      </c>
+      <c r="T34" t="n">
         <v>2.789447106921743</v>
       </c>
-      <c r="U34" s="3" t="n">
+      <c r="U34" t="n">
         <v>0.5299949503151312</v>
       </c>
-      <c r="V34" s="3" t="n">
+      <c r="V34" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" t="n">
         <v>12</v>
       </c>
-      <c r="B35" s="1" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Wilkes-Barre, PA</t>
         </is>
       </c>
-      <c r="D35" s="2" t="n">
+      <c r="D35" t="n">
         <v>4</v>
       </c>
-      <c r="E35" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F35" s="1" t="inlineStr">
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>low_flow</t>
         </is>
       </c>
-      <c r="G35" s="3" t="n">
+      <c r="G35" t="n">
         <v>60</v>
       </c>
-      <c r="H35" s="3" t="n">
+      <c r="H35" t="n">
         <v>120</v>
       </c>
-      <c r="I35" s="3" t="n">
+      <c r="I35" t="n">
         <v>280</v>
       </c>
-      <c r="J35" s="1" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" t="n">
         <v>70</v>
       </c>
-      <c r="L35" s="1" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M35" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N35" s="3" t="n">
+      <c r="M35" t="n">
+        <v>3</v>
+      </c>
+      <c r="N35" t="n">
         <v>10</v>
       </c>
-      <c r="O35" s="3" t="n">
+      <c r="O35" t="n">
         <v>10</v>
       </c>
-      <c r="P35" s="3" t="n">
+      <c r="P35" t="n">
         <v>5.13</v>
       </c>
-      <c r="Q35" s="3" t="n">
+      <c r="Q35" t="n">
         <v>2.2</v>
       </c>
-      <c r="R35" s="3" t="n">
+      <c r="R35" t="n">
         <v>7.856</v>
       </c>
-      <c r="S35" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T35" s="3" t="n">
+      <c r="S35" t="n">
+        <v>3</v>
+      </c>
+      <c r="T35" t="n">
         <v>0.6739106727341909</v>
       </c>
-      <c r="U35" s="3" t="n">
+      <c r="U35" t="n">
         <v>0.1280430278194963</v>
       </c>
-      <c r="V35" s="3" t="n">
+      <c r="V35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" t="n">
         <v>12</v>
       </c>
-      <c r="B36" s="1" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Wilkes-Barre, PA</t>
         </is>
       </c>
-      <c r="D36" s="2" t="n">
+      <c r="D36" t="n">
         <v>4</v>
       </c>
-      <c r="E36" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F36" s="1" t="inlineStr">
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>low_flow</t>
         </is>
       </c>
-      <c r="G36" s="3" t="n">
+      <c r="G36" t="n">
         <v>60</v>
       </c>
-      <c r="H36" s="3" t="n">
+      <c r="H36" t="n">
         <v>120</v>
       </c>
-      <c r="I36" s="3" t="n">
+      <c r="I36" t="n">
         <v>280</v>
       </c>
-      <c r="J36" s="1" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" t="n">
         <v>70</v>
       </c>
-      <c r="L36" s="1" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M36" s="2" t="n">
+      <c r="M36" t="n">
         <v>5</v>
       </c>
-      <c r="N36" s="3" t="n">
+      <c r="N36" t="n">
         <v>9.529999999999999</v>
       </c>
-      <c r="O36" s="3" t="n">
+      <c r="O36" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="P36" s="3" t="n">
+      <c r="P36" t="n">
         <v>7.28</v>
       </c>
-      <c r="Q36" s="3" t="n">
+      <c r="Q36" t="n">
         <v>3.48</v>
       </c>
-      <c r="R36" s="3" t="n">
+      <c r="R36" t="n">
         <v>8.2075</v>
       </c>
-      <c r="S36" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T36" s="3" t="n">
+      <c r="S36" t="n">
+        <v>2</v>
+      </c>
+      <c r="T36" t="n">
         <v>1.123184454556985</v>
       </c>
-      <c r="U36" s="3" t="n">
+      <c r="U36" t="n">
         <v>0.2134050463658271</v>
       </c>
-      <c r="V36" s="3" t="n">
+      <c r="V36" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" t="n">
         <v>12</v>
       </c>
-      <c r="B37" s="1" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Wilkes-Barre, PA</t>
         </is>
       </c>
-      <c r="D37" s="2" t="n">
+      <c r="D37" t="n">
         <v>4</v>
       </c>
-      <c r="E37" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F37" s="1" t="inlineStr">
+      <c r="E37" t="n">
+        <v>2</v>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>low_flow</t>
         </is>
       </c>
-      <c r="G37" s="3" t="n">
+      <c r="G37" t="n">
         <v>60</v>
       </c>
-      <c r="H37" s="3" t="n">
+      <c r="H37" t="n">
         <v>120</v>
       </c>
-      <c r="I37" s="3" t="n">
+      <c r="I37" t="n">
         <v>280</v>
       </c>
-      <c r="J37" s="1" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" t="n">
         <v>70</v>
       </c>
-      <c r="L37" s="1" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="M37" s="2" t="n">
+      <c r="M37" t="n">
         <v>7</v>
       </c>
-      <c r="N37" s="3" t="n">
+      <c r="N37" t="n">
         <v>8.9</v>
       </c>
-      <c r="O37" s="3" t="n">
+      <c r="O37" t="n">
         <v>9.039999999999999</v>
       </c>
-      <c r="P37" s="3" t="n">
+      <c r="P37" t="n">
         <v>9.08</v>
       </c>
-      <c r="Q37" s="3" t="n">
+      <c r="Q37" t="n">
         <v>6.37</v>
       </c>
-      <c r="R37" s="3" t="n">
+      <c r="R37" t="n">
         <v>8.605499999999999</v>
       </c>
-      <c r="S37" s="2" t="n">
+      <c r="S37" t="n">
         <v>1</v>
       </c>
-      <c r="T37" s="3" t="n">
+      <c r="T37" t="n">
         <v>1.572458236379779</v>
       </c>
-      <c r="U37" s="3" t="n">
+      <c r="U37" t="n">
         <v>0.298767064912158</v>
       </c>
-      <c r="V37" s="3" t="n">
+      <c r="V37" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" t="n">
         <v>13</v>
       </c>
-      <c r="B38" s="1" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Meadville, PA</t>
         </is>
       </c>
-      <c r="D38" s="2" t="n">
+      <c r="D38" t="n">
         <v>1</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="E38" t="n">
         <v>1.5</v>
       </c>
-      <c r="F38" s="1" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>low_flow</t>
         </is>
       </c>
-      <c r="G38" s="3" t="n">
+      <c r="G38" t="n">
         <v>30</v>
       </c>
-      <c r="H38" s="3" t="n">
+      <c r="H38" t="n">
         <v>105</v>
       </c>
-      <c r="I38" s="3" t="n">
+      <c r="I38" t="n">
         <v>140</v>
       </c>
-      <c r="J38" s="1" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="K38" s="3" t="n">
+      <c r="K38" t="n">
         <v>38</v>
       </c>
-      <c r="L38" s="1" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M38" s="2" t="n">
+      <c r="M38" t="n">
         <v>4</v>
       </c>
-      <c r="N38" s="3" t="n">
+      <c r="N38" t="n">
         <v>9.83</v>
       </c>
-      <c r="O38" s="3" t="n">
+      <c r="O38" t="n">
         <v>10</v>
       </c>
-      <c r="P38" s="3" t="n">
+      <c r="P38" t="n">
         <v>3.85</v>
       </c>
-      <c r="Q38" s="3" t="n">
+      <c r="Q38" t="n">
         <v>2.86</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" t="n">
         <v>7.648</v>
       </c>
-      <c r="S38" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T38" s="3" t="n">
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="n">
         <v>0.9108902499594012</v>
       </c>
-      <c r="U38" s="3" t="n">
+      <c r="U38" t="n">
         <v>0.1730691474922862</v>
       </c>
-      <c r="V38" s="3" t="n">
+      <c r="V38" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" t="n">
         <v>13</v>
       </c>
-      <c r="B39" s="1" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Meadville, PA</t>
         </is>
       </c>
-      <c r="D39" s="2" t="n">
+      <c r="D39" t="n">
         <v>1</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" t="n">
         <v>1.5</v>
       </c>
-      <c r="F39" s="1" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>low_flow</t>
         </is>
       </c>
-      <c r="G39" s="3" t="n">
+      <c r="G39" t="n">
         <v>30</v>
       </c>
-      <c r="H39" s="3" t="n">
+      <c r="H39" t="n">
         <v>105</v>
       </c>
-      <c r="I39" s="3" t="n">
+      <c r="I39" t="n">
         <v>140</v>
       </c>
-      <c r="J39" s="1" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="K39" t="n">
         <v>38</v>
       </c>
-      <c r="L39" s="1" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="M39" s="2" t="n">
+      <c r="M39" t="n">
         <v>6</v>
       </c>
-      <c r="N39" s="3" t="n">
+      <c r="N39" t="n">
         <v>9.19</v>
       </c>
-      <c r="O39" s="3" t="n">
+      <c r="O39" t="n">
         <v>9.779999999999999</v>
       </c>
-      <c r="P39" s="3" t="n">
+      <c r="P39" t="n">
         <v>5.6</v>
       </c>
-      <c r="Q39" s="3" t="n">
+      <c r="Q39" t="n">
         <v>5.01</v>
       </c>
-      <c r="R39" s="3" t="n">
+      <c r="R39" t="n">
         <v>8.051499999999999</v>
       </c>
-      <c r="S39" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T39" s="3" t="n">
+      <c r="S39" t="n">
+        <v>2</v>
+      </c>
+      <c r="T39" t="n">
         <v>1.366335374939102</v>
       </c>
-      <c r="U39" s="3" t="n">
+      <c r="U39" t="n">
         <v>0.2596037212384293</v>
       </c>
-      <c r="V39" s="3" t="n">
+      <c r="V39" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" t="n">
         <v>13</v>
       </c>
-      <c r="B40" s="1" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Meadville, PA</t>
         </is>
       </c>
-      <c r="D40" s="2" t="n">
+      <c r="D40" t="n">
         <v>1</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="E40" t="n">
         <v>1.5</v>
       </c>
-      <c r="F40" s="1" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>low_flow</t>
         </is>
       </c>
-      <c r="G40" s="3" t="n">
+      <c r="G40" t="n">
         <v>30</v>
       </c>
-      <c r="H40" s="3" t="n">
+      <c r="H40" t="n">
         <v>105</v>
       </c>
-      <c r="I40" s="3" t="n">
+      <c r="I40" t="n">
         <v>140</v>
       </c>
-      <c r="J40" s="1" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="K40" s="3" t="n">
+      <c r="K40" t="n">
         <v>38</v>
       </c>
-      <c r="L40" s="1" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M40" s="2" t="n">
+      <c r="M40" t="n">
         <v>10</v>
       </c>
-      <c r="N40" s="3" t="n">
+      <c r="N40" t="n">
         <v>7.91</v>
       </c>
-      <c r="O40" s="3" t="n">
+      <c r="O40" t="n">
         <v>8.890000000000001</v>
       </c>
-      <c r="P40" s="3" t="n">
+      <c r="P40" t="n">
         <v>8.43</v>
       </c>
-      <c r="Q40" s="3" t="n">
+      <c r="Q40" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="R40" s="3" t="n">
+      <c r="R40" t="n">
         <v>8.437999999999999</v>
       </c>
-      <c r="S40" s="2" t="n">
+      <c r="S40" t="n">
         <v>1</v>
       </c>
-      <c r="T40" s="3" t="n">
+      <c r="T40" t="n">
         <v>2.277225624898503</v>
       </c>
-      <c r="U40" s="3" t="n">
+      <c r="U40" t="n">
         <v>0.4326728687307156</v>
       </c>
-      <c r="V40" s="3" t="n">
+      <c r="V40" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" t="n">
         <v>14</v>
       </c>
-      <c r="B41" s="1" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Uniontown, PA</t>
         </is>
       </c>
-      <c r="D41" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F41" s="1" t="inlineStr">
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>low_flow</t>
         </is>
       </c>
-      <c r="G41" s="3" t="n">
+      <c r="G41" t="n">
         <v>40</v>
       </c>
-      <c r="H41" s="3" t="n">
+      <c r="H41" t="n">
         <v>115</v>
       </c>
-      <c r="I41" s="3" t="n">
+      <c r="I41" t="n">
         <v>160</v>
       </c>
-      <c r="J41" s="1" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="K41" t="n">
         <v>52</v>
       </c>
-      <c r="L41" s="1" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M41" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N41" s="3" t="n">
+      <c r="M41" t="n">
+        <v>3</v>
+      </c>
+      <c r="N41" t="n">
         <v>9.98</v>
       </c>
-      <c r="O41" s="3" t="n">
+      <c r="O41" t="n">
         <v>10</v>
       </c>
-      <c r="P41" s="3" t="n">
+      <c r="P41" t="n">
         <v>5.13</v>
       </c>
-      <c r="Q41" s="3" t="n">
+      <c r="Q41" t="n">
         <v>2.2</v>
       </c>
-      <c r="R41" s="3" t="n">
+      <c r="R41" t="n">
         <v>7.85</v>
       </c>
-      <c r="S41" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T41" s="3" t="n">
+      <c r="S41" t="n">
+        <v>3</v>
+      </c>
+      <c r="T41" t="n">
         <v>0.8072116849233715</v>
       </c>
-      <c r="U41" s="3" t="n">
+      <c r="U41" t="n">
         <v>0.1533702201354406</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="V41" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" t="n">
         <v>14</v>
       </c>
-      <c r="B42" s="1" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Uniontown, PA</t>
         </is>
       </c>
-      <c r="D42" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F42" s="1" t="inlineStr">
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>low_flow</t>
         </is>
       </c>
-      <c r="G42" s="3" t="n">
+      <c r="G42" t="n">
         <v>40</v>
       </c>
-      <c r="H42" s="3" t="n">
+      <c r="H42" t="n">
         <v>115</v>
       </c>
-      <c r="I42" s="3" t="n">
+      <c r="I42" t="n">
         <v>160</v>
       </c>
-      <c r="J42" s="1" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="K42" t="n">
         <v>52</v>
       </c>
-      <c r="L42" s="1" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M42" s="2" t="n">
+      <c r="M42" t="n">
         <v>5</v>
       </c>
-      <c r="N42" s="3" t="n">
+      <c r="N42" t="n">
         <v>9.220000000000001</v>
       </c>
-      <c r="O42" s="3" t="n">
+      <c r="O42" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="P42" s="3" t="n">
+      <c r="P42" t="n">
         <v>6.88</v>
       </c>
-      <c r="Q42" s="3" t="n">
+      <c r="Q42" t="n">
         <v>3.48</v>
       </c>
-      <c r="R42" s="3" t="n">
+      <c r="R42" t="n">
         <v>8.0345</v>
       </c>
-      <c r="S42" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T42" s="3" t="n">
+      <c r="S42" t="n">
+        <v>2</v>
+      </c>
+      <c r="T42" t="n">
         <v>1.345352808205619</v>
       </c>
-      <c r="U42" s="3" t="n">
+      <c r="U42" t="n">
         <v>0.2556170335590677</v>
       </c>
-      <c r="V42" s="3" t="n">
+      <c r="V42" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" t="n">
         <v>14</v>
       </c>
-      <c r="B43" s="1" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Uniontown, PA</t>
         </is>
       </c>
-      <c r="D43" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F43" s="1" t="inlineStr">
+      <c r="D43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>low_flow</t>
         </is>
       </c>
-      <c r="G43" s="3" t="n">
+      <c r="G43" t="n">
         <v>40</v>
       </c>
-      <c r="H43" s="3" t="n">
+      <c r="H43" t="n">
         <v>115</v>
       </c>
-      <c r="I43" s="3" t="n">
+      <c r="I43" t="n">
         <v>160</v>
       </c>
-      <c r="J43" s="1" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="K43" s="3" t="n">
+      <c r="K43" t="n">
         <v>52</v>
       </c>
-      <c r="L43" s="1" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M43" s="2" t="n">
+      <c r="M43" t="n">
         <v>8</v>
       </c>
-      <c r="N43" s="3" t="n">
+      <c r="N43" t="n">
         <v>8.08</v>
       </c>
-      <c r="O43" s="3" t="n">
+      <c r="O43" t="n">
         <v>8.74</v>
       </c>
-      <c r="P43" s="3" t="n">
+      <c r="P43" t="n">
         <v>9.07</v>
       </c>
-      <c r="Q43" s="3" t="n">
+      <c r="Q43" t="n">
         <v>7.6</v>
       </c>
-      <c r="R43" s="3" t="n">
+      <c r="R43" t="n">
         <v>8.436999999999999</v>
       </c>
-      <c r="S43" s="2" t="n">
+      <c r="S43" t="n">
         <v>1</v>
       </c>
-      <c r="T43" s="3" t="n">
+      <c r="T43" t="n">
         <v>2.152564493128991</v>
       </c>
-      <c r="U43" s="3" t="n">
+      <c r="U43" t="n">
         <v>0.4089872536945083</v>
       </c>
-      <c r="V43" s="3" t="n">
+      <c r="V43" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" t="n">
         <v>15</v>
       </c>
-      <c r="B44" s="1" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Williamsport, PA</t>
         </is>
       </c>
-      <c r="D44" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E44" s="3" t="n">
+      <c r="D44" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" t="n">
         <v>2.5</v>
       </c>
-      <c r="F44" s="1" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="G44" s="3" t="n">
+      <c r="G44" t="n">
         <v>50</v>
       </c>
-      <c r="H44" s="3" t="n">
+      <c r="H44" t="n">
         <v>120</v>
       </c>
-      <c r="I44" s="3" t="n">
+      <c r="I44" t="n">
         <v>255</v>
       </c>
-      <c r="J44" s="1" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="K44" s="3" t="n">
+      <c r="K44" t="n">
         <v>48</v>
       </c>
-      <c r="L44" s="1" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M44" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N44" s="3" t="n">
+      <c r="M44" t="n">
+        <v>3</v>
+      </c>
+      <c r="N44" t="n">
         <v>9.640000000000001</v>
       </c>
-      <c r="O44" s="3" t="n">
+      <c r="O44" t="n">
         <v>10</v>
       </c>
-      <c r="P44" s="3" t="n">
+      <c r="P44" t="n">
         <v>5.13</v>
       </c>
-      <c r="Q44" s="3" t="n">
+      <c r="Q44" t="n">
         <v>2.2</v>
       </c>
-      <c r="R44" s="3" t="n">
+      <c r="R44" t="n">
         <v>7.747999999999999</v>
       </c>
-      <c r="S44" s="2" t="n">
+      <c r="S44" t="n">
         <v>1</v>
       </c>
-      <c r="T44" s="3" t="n">
+      <c r="T44" t="n">
         <v>1.046042665095654</v>
       </c>
-      <c r="U44" s="3" t="n">
+      <c r="U44" t="n">
         <v>0.1987481063681742</v>
       </c>
-      <c r="V44" s="3" t="n">
+      <c r="V44" t="n">
         <v>7.5</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" t="n">
         <v>15</v>
       </c>
-      <c r="B45" s="1" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Williamsport, PA</t>
         </is>
       </c>
-      <c r="D45" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E45" s="3" t="n">
+      <c r="D45" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" t="n">
         <v>2.5</v>
       </c>
-      <c r="F45" s="1" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="G45" s="3" t="n">
+      <c r="G45" t="n">
         <v>50</v>
       </c>
-      <c r="H45" s="3" t="n">
+      <c r="H45" t="n">
         <v>120</v>
       </c>
-      <c r="I45" s="3" t="n">
+      <c r="I45" t="n">
         <v>255</v>
       </c>
-      <c r="J45" s="1" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" t="n">
         <v>48</v>
       </c>
-      <c r="L45" s="1" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M45" s="2" t="n">
+      <c r="M45" t="n">
         <v>5</v>
       </c>
-      <c r="N45" s="3" t="n">
+      <c r="N45" t="n">
         <v>8.66</v>
       </c>
-      <c r="O45" s="3" t="n">
+      <c r="O45" t="n">
         <v>9.26</v>
       </c>
-      <c r="P45" s="3" t="n">
+      <c r="P45" t="n">
         <v>6.81</v>
       </c>
-      <c r="Q45" s="3" t="n">
+      <c r="Q45" t="n">
         <v>3.48</v>
       </c>
-      <c r="R45" s="3" t="n">
+      <c r="R45" t="n">
         <v>7.723</v>
       </c>
-      <c r="S45" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T45" s="3" t="n">
+      <c r="S45" t="n">
+        <v>2</v>
+      </c>
+      <c r="T45" t="n">
         <v>1.743404441826089</v>
       </c>
-      <c r="U45" s="3" t="n">
+      <c r="U45" t="n">
         <v>0.331246843946957</v>
       </c>
-      <c r="V45" s="3" t="n">
+      <c r="V45" t="n">
         <v>12.5</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" t="n">
         <v>15</v>
       </c>
-      <c r="B46" s="1" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Williamsport, PA</t>
         </is>
       </c>
-      <c r="D46" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E46" s="3" t="n">
+      <c r="D46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" t="n">
         <v>2.5</v>
       </c>
-      <c r="F46" s="1" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="G46" s="3" t="n">
+      <c r="G46" t="n">
         <v>50</v>
       </c>
-      <c r="H46" s="3" t="n">
+      <c r="H46" t="n">
         <v>120</v>
       </c>
-      <c r="I46" s="3" t="n">
+      <c r="I46" t="n">
         <v>255</v>
       </c>
-      <c r="J46" s="1" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="K46" s="3" t="n">
+      <c r="K46" t="n">
         <v>48</v>
       </c>
-      <c r="L46" s="1" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M46" s="2" t="n">
+      <c r="M46" t="n">
         <v>8</v>
       </c>
-      <c r="N46" s="3" t="n">
+      <c r="N46" t="n">
         <v>7.19</v>
       </c>
-      <c r="O46" s="3" t="n">
+      <c r="O46" t="n">
         <v>8.15</v>
       </c>
-      <c r="P46" s="3" t="n">
+      <c r="P46" t="n">
         <v>8.93</v>
       </c>
-      <c r="Q46" s="3" t="n">
+      <c r="Q46" t="n">
         <v>4.64</v>
       </c>
-      <c r="R46" s="3" t="n">
+      <c r="R46" t="n">
         <v>7.4915</v>
       </c>
-      <c r="S46" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T46" s="3" t="n">
+      <c r="S46" t="n">
+        <v>3</v>
+      </c>
+      <c r="T46" t="n">
         <v>2.789447106921743</v>
       </c>
-      <c r="U46" s="3" t="n">
+      <c r="U46" t="n">
         <v>0.5299949503151312</v>
       </c>
-      <c r="V46" s="3" t="n">
+      <c r="V46" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" t="n">
         <v>16</v>
       </c>
-      <c r="B47" s="1" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Williamsport, PA</t>
         </is>
       </c>
-      <c r="D47" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F47" s="1" t="inlineStr">
+      <c r="D47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>low_flow</t>
         </is>
       </c>
-      <c r="G47" s="3" t="n">
+      <c r="G47" t="n">
         <v>40</v>
       </c>
-      <c r="H47" s="3" t="n">
+      <c r="H47" t="n">
         <v>120</v>
       </c>
-      <c r="I47" s="3" t="n">
+      <c r="I47" t="n">
         <v>195</v>
       </c>
-      <c r="J47" s="1" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="K47" s="3" t="n">
+      <c r="K47" t="n">
         <v>35</v>
       </c>
-      <c r="L47" s="1" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M47" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N47" s="3" t="n">
+      <c r="M47" t="n">
+        <v>3</v>
+      </c>
+      <c r="N47" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="O47" s="3" t="n">
+      <c r="O47" t="n">
         <v>10</v>
       </c>
-      <c r="P47" s="3" t="n">
+      <c r="P47" t="n">
         <v>5.13</v>
       </c>
-      <c r="Q47" s="3" t="n">
+      <c r="Q47" t="n">
         <v>2.2</v>
       </c>
-      <c r="R47" s="3" t="n">
+      <c r="R47" t="n">
         <v>7.795999999999999</v>
       </c>
-      <c r="S47" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T47" s="3" t="n">
+      <c r="S47" t="n">
+        <v>3</v>
+      </c>
+      <c r="T47" t="n">
         <v>0.9331070853242645</v>
       </c>
-      <c r="U47" s="3" t="n">
+      <c r="U47" t="n">
         <v>0.1772903462116102</v>
       </c>
-      <c r="V47" s="3" t="n">
+      <c r="V47" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" t="n">
         <v>16</v>
       </c>
-      <c r="B48" s="1" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Williamsport, PA</t>
         </is>
       </c>
-      <c r="D48" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F48" s="1" t="inlineStr">
+      <c r="D48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2</v>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>low_flow</t>
         </is>
       </c>
-      <c r="G48" s="3" t="n">
+      <c r="G48" t="n">
         <v>40</v>
       </c>
-      <c r="H48" s="3" t="n">
+      <c r="H48" t="n">
         <v>120</v>
       </c>
-      <c r="I48" s="3" t="n">
+      <c r="I48" t="n">
         <v>195</v>
       </c>
-      <c r="J48" s="1" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="K48" s="3" t="n">
+      <c r="K48" t="n">
         <v>35</v>
       </c>
-      <c r="L48" s="1" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M48" s="2" t="n">
+      <c r="M48" t="n">
         <v>5</v>
       </c>
-      <c r="N48" s="3" t="n">
+      <c r="N48" t="n">
         <v>8.92</v>
       </c>
-      <c r="O48" s="3" t="n">
+      <c r="O48" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="P48" s="3" t="n">
+      <c r="P48" t="n">
         <v>6.7</v>
       </c>
-      <c r="Q48" s="3" t="n">
+      <c r="Q48" t="n">
         <v>3.48</v>
       </c>
-      <c r="R48" s="3" t="n">
+      <c r="R48" t="n">
         <v>7.9085</v>
       </c>
-      <c r="S48" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T48" s="3" t="n">
+      <c r="S48" t="n">
+        <v>2</v>
+      </c>
+      <c r="T48" t="n">
         <v>1.555178475540441</v>
       </c>
-      <c r="U48" s="3" t="n">
+      <c r="U48" t="n">
         <v>0.2954839103526837</v>
       </c>
-      <c r="V48" s="3" t="n">
+      <c r="V48" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" t="n">
         <v>16</v>
       </c>
-      <c r="B49" s="1" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Williamsport, PA</t>
         </is>
       </c>
-      <c r="D49" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F49" s="1" t="inlineStr">
+      <c r="D49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>low_flow</t>
         </is>
       </c>
-      <c r="G49" s="3" t="n">
+      <c r="G49" t="n">
         <v>40</v>
       </c>
-      <c r="H49" s="3" t="n">
+      <c r="H49" t="n">
         <v>120</v>
       </c>
-      <c r="I49" s="3" t="n">
+      <c r="I49" t="n">
         <v>195</v>
       </c>
-      <c r="J49" s="1" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="K49" s="3" t="n">
+      <c r="K49" t="n">
         <v>35</v>
       </c>
-      <c r="L49" s="1" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M49" s="2" t="n">
+      <c r="M49" t="n">
         <v>8</v>
       </c>
-      <c r="N49" s="3" t="n">
+      <c r="N49" t="n">
         <v>7.61</v>
       </c>
-      <c r="O49" s="3" t="n">
+      <c r="O49" t="n">
         <v>8.74</v>
       </c>
-      <c r="P49" s="3" t="n">
+      <c r="P49" t="n">
         <v>8.69</v>
       </c>
-      <c r="Q49" s="3" t="n">
+      <c r="Q49" t="n">
         <v>7.6</v>
       </c>
-      <c r="R49" s="3" t="n">
+      <c r="R49" t="n">
         <v>8.220000000000001</v>
       </c>
-      <c r="S49" s="2" t="n">
+      <c r="S49" t="n">
         <v>1</v>
       </c>
-      <c r="T49" s="3" t="n">
+      <c r="T49" t="n">
         <v>2.488285560864705</v>
       </c>
-      <c r="U49" s="3" t="n">
+      <c r="U49" t="n">
         <v>0.472774256564294</v>
       </c>
-      <c r="V49" s="3" t="n">
+      <c r="V49" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" t="n">
         <v>17</v>
       </c>
-      <c r="B50" s="1" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>West Mifflin, PA</t>
         </is>
       </c>
-      <c r="D50" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E50" s="3" t="n">
+      <c r="D50" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" t="n">
         <v>2.5</v>
       </c>
-      <c r="F50" s="1" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="G50" s="3" t="n">
+      <c r="G50" t="n">
         <v>50</v>
       </c>
-      <c r="H50" s="3" t="n">
+      <c r="H50" t="n">
         <v>120</v>
       </c>
-      <c r="I50" s="3" t="n">
+      <c r="I50" t="n">
         <v>250</v>
       </c>
-      <c r="J50" s="1" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="K50" s="3" t="n">
+      <c r="K50" t="n">
         <v>60</v>
       </c>
-      <c r="L50" s="1" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M50" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N50" s="3" t="n">
+      <c r="M50" t="n">
+        <v>3</v>
+      </c>
+      <c r="N50" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="O50" s="3" t="n">
+      <c r="O50" t="n">
         <v>10</v>
       </c>
-      <c r="P50" s="3" t="n">
+      <c r="P50" t="n">
         <v>5.13</v>
       </c>
-      <c r="Q50" s="3" t="n">
+      <c r="Q50" t="n">
         <v>2.2</v>
       </c>
-      <c r="R50" s="3" t="n">
+      <c r="R50" t="n">
         <v>7.795999999999999</v>
       </c>
-      <c r="S50" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T50" s="3" t="n">
+      <c r="S50" t="n">
+        <v>2</v>
+      </c>
+      <c r="T50" t="n">
         <v>0.9349584882713364</v>
       </c>
-      <c r="U50" s="3" t="n">
+      <c r="U50" t="n">
         <v>0.1776421127715539</v>
       </c>
-      <c r="V50" s="3" t="n">
+      <c r="V50" t="n">
         <v>7.5</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" t="n">
         <v>17</v>
       </c>
-      <c r="B51" s="1" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>West Mifflin, PA</t>
         </is>
       </c>
-      <c r="D51" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E51" s="3" t="n">
+      <c r="D51" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" t="n">
         <v>2.5</v>
       </c>
-      <c r="F51" s="1" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="G51" s="3" t="n">
+      <c r="G51" t="n">
         <v>50</v>
       </c>
-      <c r="H51" s="3" t="n">
+      <c r="H51" t="n">
         <v>120</v>
       </c>
-      <c r="I51" s="3" t="n">
+      <c r="I51" t="n">
         <v>250</v>
       </c>
-      <c r="J51" s="1" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="K51" s="3" t="n">
+      <c r="K51" t="n">
         <v>60</v>
       </c>
-      <c r="L51" s="1" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M51" s="2" t="n">
+      <c r="M51" t="n">
         <v>5</v>
       </c>
-      <c r="N51" s="3" t="n">
+      <c r="N51" t="n">
         <v>8.92</v>
       </c>
-      <c r="O51" s="3" t="n">
+      <c r="O51" t="n">
         <v>9.26</v>
       </c>
-      <c r="P51" s="3" t="n">
+      <c r="P51" t="n">
         <v>7.04</v>
       </c>
-      <c r="Q51" s="3" t="n">
+      <c r="Q51" t="n">
         <v>3.48</v>
       </c>
-      <c r="R51" s="3" t="n">
+      <c r="R51" t="n">
         <v>7.847</v>
       </c>
-      <c r="S51" s="2" t="n">
+      <c r="S51" t="n">
         <v>1</v>
       </c>
-      <c r="T51" s="3" t="n">
+      <c r="T51" t="n">
         <v>1.558264147118894</v>
       </c>
-      <c r="U51" s="3" t="n">
+      <c r="U51" t="n">
         <v>0.2960701879525898</v>
       </c>
-      <c r="V51" s="3" t="n">
+      <c r="V51" t="n">
         <v>12.5</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" t="n">
         <v>17</v>
       </c>
-      <c r="B52" s="1" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>How long should I shower?</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>West Mifflin, PA</t>
         </is>
       </c>
-      <c r="D52" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E52" s="3" t="n">
+      <c r="D52" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" t="n">
         <v>2.5</v>
       </c>
-      <c r="F52" s="1" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="G52" s="3" t="n">
+      <c r="G52" t="n">
         <v>50</v>
       </c>
-      <c r="H52" s="3" t="n">
+      <c r="H52" t="n">
         <v>120</v>
       </c>
-      <c r="I52" s="3" t="n">
+      <c r="I52" t="n">
         <v>250</v>
       </c>
-      <c r="J52" s="1" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="K52" s="3" t="n">
+      <c r="K52" t="n">
         <v>60</v>
       </c>
-      <c r="L52" s="1" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M52" s="2" t="n">
+      <c r="M52" t="n">
         <v>8</v>
       </c>
-      <c r="N52" s="3" t="n">
+      <c r="N52" t="n">
         <v>7.6</v>
       </c>
-      <c r="O52" s="3" t="n">
+      <c r="O52" t="n">
         <v>8.15</v>
       </c>
-      <c r="P52" s="3" t="n">
+      <c r="P52" t="n">
         <v>9.390000000000001</v>
       </c>
-      <c r="Q52" s="3" t="n">
+      <c r="Q52" t="n">
         <v>4.64</v>
       </c>
-      <c r="R52" s="3" t="n">
+      <c r="R52" t="n">
         <v>7.7065</v>
       </c>
-      <c r="S52" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T52" s="3" t="n">
+      <c r="S52" t="n">
+        <v>3</v>
+      </c>
+      <c r="T52" t="n">
         <v>2.49322263539023</v>
       </c>
-      <c r="U52" s="3" t="n">
+      <c r="U52" t="n">
         <v>0.4737123007241438</v>
       </c>
-      <c r="V52" s="3" t="n">
+      <c r="V52" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" t="n">
         <v>18</v>
       </c>
-      <c r="B53" s="1" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>With a high-flow showerhead and small tank on a cold morning, how long should I shower?</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Altoona, PA</t>
         </is>
       </c>
-      <c r="D53" s="2" t="n">
+      <c r="D53" t="n">
         <v>4</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="E53" t="n">
         <v>3.5</v>
       </c>
-      <c r="F53" s="1" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>high_flow</t>
         </is>
       </c>
-      <c r="G53" s="3" t="n">
+      <c r="G53" t="n">
         <v>40</v>
       </c>
-      <c r="H53" s="3" t="n">
+      <c r="H53" t="n">
         <v>120</v>
       </c>
-      <c r="I53" s="3" t="n">
+      <c r="I53" t="n">
         <v>240</v>
       </c>
-      <c r="J53" s="1" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="K53" s="3" t="n">
+      <c r="K53" t="n">
         <v>18</v>
       </c>
-      <c r="L53" s="1" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M53" s="2" t="n">
+      <c r="M53" t="n">
         <v>4</v>
       </c>
-      <c r="N53" s="3" t="n">
+      <c r="N53" t="n">
         <v>7.97</v>
       </c>
-      <c r="O53" s="3" t="n">
+      <c r="O53" t="n">
         <v>9.039999999999999</v>
       </c>
-      <c r="P53" s="3" t="n">
+      <c r="P53" t="n">
         <v>5.94</v>
       </c>
-      <c r="Q53" s="3" t="n">
+      <c r="Q53" t="n">
         <v>1.51</v>
       </c>
-      <c r="R53" s="3" t="n">
+      <c r="R53" t="n">
         <v>6.9695</v>
       </c>
-      <c r="S53" s="2" t="n">
+      <c r="S53" t="n">
         <v>1</v>
       </c>
-      <c r="T53" s="3" t="n">
+      <c r="T53" t="n">
         <v>2.229089148274632</v>
       </c>
-      <c r="U53" s="3" t="n">
+      <c r="U53" t="n">
         <v>0.4235269381721801</v>
       </c>
-      <c r="V53" s="3" t="n">
+      <c r="V53" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" t="n">
         <v>18</v>
       </c>
-      <c r="B54" s="1" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>With a high-flow showerhead and small tank on a cold morning, how long should I shower?</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Altoona, PA</t>
         </is>
       </c>
-      <c r="D54" s="2" t="n">
+      <c r="D54" t="n">
         <v>4</v>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="E54" t="n">
         <v>3.5</v>
       </c>
-      <c r="F54" s="1" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>high_flow</t>
         </is>
       </c>
-      <c r="G54" s="3" t="n">
+      <c r="G54" t="n">
         <v>40</v>
       </c>
-      <c r="H54" s="3" t="n">
+      <c r="H54" t="n">
         <v>120</v>
       </c>
-      <c r="I54" s="3" t="n">
+      <c r="I54" t="n">
         <v>240</v>
       </c>
-      <c r="J54" s="1" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="K54" s="3" t="n">
+      <c r="K54" t="n">
         <v>18</v>
       </c>
-      <c r="L54" s="1" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="M54" s="2" t="n">
+      <c r="M54" t="n">
         <v>6</v>
       </c>
-      <c r="N54" s="3" t="n">
+      <c r="N54" t="n">
         <v>6.41</v>
       </c>
-      <c r="O54" s="3" t="n">
+      <c r="O54" t="n">
         <v>8</v>
       </c>
-      <c r="P54" s="3" t="n">
+      <c r="P54" t="n">
         <v>7.4</v>
       </c>
-      <c r="Q54" s="3" t="n">
+      <c r="Q54" t="n">
         <v>1.51</v>
       </c>
-      <c r="R54" s="3" t="n">
+      <c r="R54" t="n">
         <v>6.4295</v>
       </c>
-      <c r="S54" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T54" s="3" t="n">
+      <c r="S54" t="n">
+        <v>2</v>
+      </c>
+      <c r="T54" t="n">
         <v>3.343633722411948</v>
       </c>
-      <c r="U54" s="3" t="n">
+      <c r="U54" t="n">
         <v>0.6352904072582701</v>
       </c>
-      <c r="V54" s="3" t="n">
+      <c r="V54" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" t="n">
         <v>18</v>
       </c>
-      <c r="B55" s="1" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>With a high-flow showerhead and small tank on a cold morning, how long should I shower?</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Altoona, PA</t>
         </is>
       </c>
-      <c r="D55" s="2" t="n">
+      <c r="D55" t="n">
         <v>4</v>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="E55" t="n">
         <v>3.5</v>
       </c>
-      <c r="F55" s="1" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>high_flow</t>
         </is>
       </c>
-      <c r="G55" s="3" t="n">
+      <c r="G55" t="n">
         <v>40</v>
       </c>
-      <c r="H55" s="3" t="n">
+      <c r="H55" t="n">
         <v>120</v>
       </c>
-      <c r="I55" s="3" t="n">
+      <c r="I55" t="n">
         <v>240</v>
       </c>
-      <c r="J55" s="1" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="K55" s="3" t="n">
+      <c r="K55" t="n">
         <v>18</v>
       </c>
-      <c r="L55" s="1" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M55" s="2" t="n">
+      <c r="M55" t="n">
         <v>8</v>
       </c>
-      <c r="N55" s="3" t="n">
+      <c r="N55" t="n">
         <v>4.84</v>
       </c>
-      <c r="O55" s="3" t="n">
+      <c r="O55" t="n">
         <v>6.96</v>
       </c>
-      <c r="P55" s="3" t="n">
+      <c r="P55" t="n">
         <v>8.619999999999999</v>
       </c>
-      <c r="Q55" s="3" t="n">
+      <c r="Q55" t="n">
         <v>4.64</v>
       </c>
-      <c r="R55" s="3" t="n">
+      <c r="R55" t="n">
         <v>6.308</v>
       </c>
-      <c r="S55" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T55" s="3" t="n">
+      <c r="S55" t="n">
+        <v>3</v>
+      </c>
+      <c r="T55" t="n">
         <v>4.458178296549264</v>
       </c>
-      <c r="U55" s="3" t="n">
+      <c r="U55" t="n">
         <v>0.8470538763443601</v>
       </c>
-      <c r="V55" s="3" t="n">
+      <c r="V55" t="n">
         <v>28</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" t="n">
         <v>19</v>
       </c>
-      <c r="B56" s="1" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>On a hot day with a low-flow showerhead, what shower duration makes sense?</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Chester, PA</t>
         </is>
       </c>
-      <c r="D56" s="2" t="n">
+      <c r="D56" t="n">
         <v>1</v>
       </c>
-      <c r="E56" s="3" t="n">
+      <c r="E56" t="n">
         <v>1.5</v>
       </c>
-      <c r="F56" s="1" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>low_flow</t>
         </is>
       </c>
-      <c r="G56" s="3" t="n">
+      <c r="G56" t="n">
         <v>30</v>
       </c>
-      <c r="H56" s="3" t="n">
+      <c r="H56" t="n">
         <v>115</v>
       </c>
-      <c r="I56" s="3" t="n">
+      <c r="I56" t="n">
         <v>150</v>
       </c>
-      <c r="J56" s="1" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="K56" s="3" t="n">
+      <c r="K56" t="n">
         <v>90</v>
       </c>
-      <c r="L56" s="1" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M56" s="2" t="n">
+      <c r="M56" t="n">
         <v>4</v>
       </c>
-      <c r="N56" s="3" t="n">
+      <c r="N56" t="n">
         <v>10</v>
       </c>
-      <c r="O56" s="3" t="n">
+      <c r="O56" t="n">
         <v>10</v>
       </c>
-      <c r="P56" s="3" t="n">
+      <c r="P56" t="n">
         <v>6.34</v>
       </c>
-      <c r="Q56" s="3" t="n">
+      <c r="Q56" t="n">
         <v>2.86</v>
       </c>
-      <c r="R56" s="3" t="n">
+      <c r="R56" t="n">
         <v>8.196999999999999</v>
       </c>
-      <c r="S56" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T56" s="3" t="n">
+      <c r="S56" t="n">
+        <v>3</v>
+      </c>
+      <c r="T56" t="n">
         <v>0.6368826137927521</v>
       </c>
-      <c r="U56" s="3" t="n">
+      <c r="U56" t="n">
         <v>0.1210076966206229</v>
       </c>
-      <c r="V56" s="3" t="n">
+      <c r="V56" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" t="n">
         <v>19</v>
       </c>
-      <c r="B57" s="1" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>On a hot day with a low-flow showerhead, what shower duration makes sense?</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Chester, PA</t>
         </is>
       </c>
-      <c r="D57" s="2" t="n">
+      <c r="D57" t="n">
         <v>1</v>
       </c>
-      <c r="E57" s="3" t="n">
+      <c r="E57" t="n">
         <v>1.5</v>
       </c>
-      <c r="F57" s="1" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>low_flow</t>
         </is>
       </c>
-      <c r="G57" s="3" t="n">
+      <c r="G57" t="n">
         <v>30</v>
       </c>
-      <c r="H57" s="3" t="n">
+      <c r="H57" t="n">
         <v>115</v>
       </c>
-      <c r="I57" s="3" t="n">
+      <c r="I57" t="n">
         <v>150</v>
       </c>
-      <c r="J57" s="1" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="K57" s="3" t="n">
+      <c r="K57" t="n">
         <v>90</v>
       </c>
-      <c r="L57" s="1" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="M57" s="2" t="n">
+      <c r="M57" t="n">
         <v>7</v>
       </c>
-      <c r="N57" s="3" t="n">
+      <c r="N57" t="n">
         <v>9.539999999999999</v>
       </c>
-      <c r="O57" s="3" t="n">
+      <c r="O57" t="n">
         <v>9.56</v>
       </c>
-      <c r="P57" s="3" t="n">
+      <c r="P57" t="n">
         <v>9.32</v>
       </c>
-      <c r="Q57" s="3" t="n">
+      <c r="Q57" t="n">
         <v>6.37</v>
       </c>
-      <c r="R57" s="3" t="n">
+      <c r="R57" t="n">
         <v>9.027500000000002</v>
       </c>
-      <c r="S57" s="2" t="n">
+      <c r="S57" t="n">
         <v>1</v>
       </c>
-      <c r="T57" s="3" t="n">
+      <c r="T57" t="n">
         <v>1.114544574137316</v>
       </c>
-      <c r="U57" s="3" t="n">
+      <c r="U57" t="n">
         <v>0.2117634690860901</v>
       </c>
-      <c r="V57" s="3" t="n">
+      <c r="V57" t="n">
         <v>10.5</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" t="n">
         <v>19</v>
       </c>
-      <c r="B58" s="1" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>On a hot day with a low-flow showerhead, what shower duration makes sense?</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Chester, PA</t>
         </is>
       </c>
-      <c r="D58" s="2" t="n">
+      <c r="D58" t="n">
         <v>1</v>
       </c>
-      <c r="E58" s="3" t="n">
+      <c r="E58" t="n">
         <v>1.5</v>
       </c>
-      <c r="F58" s="1" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>low_flow</t>
         </is>
       </c>
-      <c r="G58" s="3" t="n">
+      <c r="G58" t="n">
         <v>30</v>
       </c>
-      <c r="H58" s="3" t="n">
+      <c r="H58" t="n">
         <v>115</v>
       </c>
-      <c r="I58" s="3" t="n">
+      <c r="I58" t="n">
         <v>150</v>
       </c>
-      <c r="J58" s="1" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="K58" s="3" t="n">
+      <c r="K58" t="n">
         <v>90</v>
       </c>
-      <c r="L58" s="1" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M58" s="2" t="n">
+      <c r="M58" t="n">
         <v>10</v>
       </c>
-      <c r="N58" s="3" t="n">
+      <c r="N58" t="n">
         <v>8.869999999999999</v>
       </c>
-      <c r="O58" s="3" t="n">
+      <c r="O58" t="n">
         <v>8.890000000000001</v>
       </c>
-      <c r="P58" s="3" t="n">
+      <c r="P58" t="n">
         <v>9.59</v>
       </c>
-      <c r="Q58" s="3" t="n">
+      <c r="Q58" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="R58" s="3" t="n">
+      <c r="R58" t="n">
         <v>8.957999999999998</v>
       </c>
-      <c r="S58" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T58" s="3" t="n">
+      <c r="S58" t="n">
+        <v>2</v>
+      </c>
+      <c r="T58" t="n">
         <v>1.59220653448188</v>
       </c>
-      <c r="U58" s="3" t="n">
+      <c r="U58" t="n">
         <v>0.3025192415515572</v>
       </c>
-      <c r="V58" s="3" t="n">
+      <c r="V58" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" t="n">
         <v>20</v>
       </c>
-      <c r="B59" s="1" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>With six people sharing a tank tonight, how long should showers be?</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Johnstown, PA</t>
         </is>
       </c>
-      <c r="D59" s="2" t="n">
+      <c r="D59" t="n">
         <v>6</v>
       </c>
-      <c r="E59" s="3" t="n">
+      <c r="E59" t="n">
         <v>2.5</v>
       </c>
-      <c r="F59" s="1" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="G59" s="3" t="n">
+      <c r="G59" t="n">
         <v>50</v>
       </c>
-      <c r="H59" s="3" t="n">
+      <c r="H59" t="n">
         <v>120</v>
       </c>
-      <c r="I59" s="3" t="n">
+      <c r="I59" t="n">
         <v>340</v>
       </c>
-      <c r="J59" s="1" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="K59" s="3" t="n">
+      <c r="K59" t="n">
         <v>40</v>
       </c>
-      <c r="L59" s="1" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M59" s="2" t="n">
+      <c r="M59" t="n">
         <v>5</v>
       </c>
-      <c r="N59" s="3" t="n">
+      <c r="N59" t="n">
         <v>8.48</v>
       </c>
-      <c r="O59" s="3" t="n">
+      <c r="O59" t="n">
         <v>9.26</v>
       </c>
-      <c r="P59" s="3" t="n">
+      <c r="P59" t="n">
         <v>6.7</v>
       </c>
-      <c r="Q59" s="3" t="n">
+      <c r="Q59" t="n">
         <v>1.51</v>
       </c>
-      <c r="R59" s="3" t="n">
+      <c r="R59" t="n">
         <v>7.3515</v>
       </c>
-      <c r="S59" s="2" t="n">
+      <c r="S59" t="n">
         <v>1</v>
       </c>
-      <c r="T59" s="3" t="n">
+      <c r="T59" t="n">
         <v>1.86683130496422</v>
       </c>
-      <c r="U59" s="3" t="n">
+      <c r="U59" t="n">
         <v>0.3546979479432018</v>
       </c>
-      <c r="V59" s="3" t="n">
+      <c r="V59" t="n">
         <v>12.5</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" t="n">
         <v>20</v>
       </c>
-      <c r="B60" s="1" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>With six people sharing a tank tonight, how long should showers be?</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Johnstown, PA</t>
         </is>
       </c>
-      <c r="D60" s="2" t="n">
+      <c r="D60" t="n">
         <v>6</v>
       </c>
-      <c r="E60" s="3" t="n">
+      <c r="E60" t="n">
         <v>2.5</v>
       </c>
-      <c r="F60" s="1" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="G60" s="3" t="n">
+      <c r="G60" t="n">
         <v>50</v>
       </c>
-      <c r="H60" s="3" t="n">
+      <c r="H60" t="n">
         <v>120</v>
       </c>
-      <c r="I60" s="3" t="n">
+      <c r="I60" t="n">
         <v>340</v>
       </c>
-      <c r="J60" s="1" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="K60" s="3" t="n">
+      <c r="K60" t="n">
         <v>40</v>
       </c>
-      <c r="L60" s="1" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M60" s="2" t="n">
+      <c r="M60" t="n">
         <v>8</v>
       </c>
-      <c r="N60" s="3" t="n">
+      <c r="N60" t="n">
         <v>6.91</v>
       </c>
-      <c r="O60" s="3" t="n">
+      <c r="O60" t="n">
         <v>8.15</v>
       </c>
-      <c r="P60" s="3" t="n">
+      <c r="P60" t="n">
         <v>8.619999999999999</v>
       </c>
-      <c r="Q60" s="3" t="n">
+      <c r="Q60" t="n">
         <v>4.64</v>
       </c>
-      <c r="R60" s="3" t="n">
+      <c r="R60" t="n">
         <v>7.345499999999999</v>
       </c>
-      <c r="S60" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T60" s="3" t="n">
+      <c r="S60" t="n">
+        <v>2</v>
+      </c>
+      <c r="T60" t="n">
         <v>2.986930087942751</v>
       </c>
-      <c r="U60" s="3" t="n">
+      <c r="U60" t="n">
         <v>0.5675167167091227</v>
       </c>
-      <c r="V60" s="3" t="n">
+      <c r="V60" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" t="n">
         <v>20</v>
       </c>
-      <c r="B61" s="1" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>With six people sharing a tank tonight, how long should showers be?</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Johnstown, PA</t>
         </is>
       </c>
-      <c r="D61" s="2" t="n">
+      <c r="D61" t="n">
         <v>6</v>
       </c>
-      <c r="E61" s="3" t="n">
+      <c r="E61" t="n">
         <v>2.5</v>
       </c>
-      <c r="F61" s="1" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="G61" s="3" t="n">
+      <c r="G61" t="n">
         <v>50</v>
       </c>
-      <c r="H61" s="3" t="n">
+      <c r="H61" t="n">
         <v>120</v>
       </c>
-      <c r="I61" s="3" t="n">
+      <c r="I61" t="n">
         <v>340</v>
       </c>
-      <c r="J61" s="1" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="K61" s="3" t="n">
+      <c r="K61" t="n">
         <v>40</v>
       </c>
-      <c r="L61" s="1" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="M61" s="2" t="n">
+      <c r="M61" t="n">
         <v>12</v>
       </c>
-      <c r="N61" s="3" t="n">
+      <c r="N61" t="n">
         <v>4.81</v>
       </c>
-      <c r="O61" s="3" t="n">
+      <c r="O61" t="n">
         <v>6.67</v>
       </c>
-      <c r="P61" s="3" t="n">
+      <c r="P61" t="n">
         <v>7.97</v>
       </c>
-      <c r="Q61" s="3" t="n">
+      <c r="Q61" t="n">
         <v>6.69</v>
       </c>
-      <c r="R61" s="3" t="n">
+      <c r="R61" t="n">
         <v>6.375</v>
       </c>
-      <c r="S61" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T61" s="3" t="n">
+      <c r="S61" t="n">
+        <v>3</v>
+      </c>
+      <c r="T61" t="n">
         <v>4.480395131914127</v>
       </c>
-      <c r="U61" s="3" t="n">
+      <c r="U61" t="n">
         <v>0.8512750750636842</v>
       </c>
-      <c r="V61" s="3" t="n">
+      <c r="V61" t="n">
         <v>30</v>
       </c>
     </row>

--- a/workbooks/scenarios/ShowerRAGScenarios.xlsx
+++ b/workbooks/scenarios/ShowerRAGScenarios.xlsx
@@ -585,13 +585,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>7.43</v>
+        <v>7.37</v>
       </c>
       <c r="Q2" t="n">
         <v>3.48</v>
       </c>
       <c r="R2" t="n">
-        <v>8.2645</v>
+        <v>8.2525</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -663,13 +663,13 @@
         <v>8.74</v>
       </c>
       <c r="P3" t="n">
-        <v>9.960000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="Q3" t="n">
         <v>7.6</v>
       </c>
       <c r="R3" t="n">
-        <v>8.807</v>
+        <v>8.813000000000001</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,13 +741,13 @@
         <v>7.56</v>
       </c>
       <c r="P4" t="n">
-        <v>9.210000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="Q4" t="n">
         <v>6.69</v>
       </c>
       <c r="R4" t="n">
-        <v>7.7505</v>
+        <v>7.7525</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -1053,13 +1053,13 @@
         <v>9.93</v>
       </c>
       <c r="P8" t="n">
-        <v>6</v>
+        <v>5.99</v>
       </c>
       <c r="Q8" t="n">
         <v>2.86</v>
       </c>
       <c r="R8" t="n">
-        <v>7.9665</v>
+        <v>7.9645</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1131,13 +1131,13 @@
         <v>9.33</v>
       </c>
       <c r="P9" t="n">
-        <v>7.56</v>
+        <v>7.52</v>
       </c>
       <c r="Q9" t="n">
         <v>5.01</v>
       </c>
       <c r="R9" t="n">
-        <v>8.157</v>
+        <v>8.148999999999999</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
@@ -1209,13 +1209,13 @@
         <v>8.15</v>
       </c>
       <c r="P10" t="n">
-        <v>9.94</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="Q10" t="n">
         <v>8.449999999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>8.265000000000001</v>
+        <v>8.271000000000001</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1365,13 +1365,13 @@
         <v>9.26</v>
       </c>
       <c r="P12" t="n">
-        <v>7.08</v>
+        <v>7.04</v>
       </c>
       <c r="Q12" t="n">
         <v>3.48</v>
       </c>
       <c r="R12" t="n">
-        <v>7.867000000000001</v>
+        <v>7.859000000000001</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1443,13 +1443,13 @@
         <v>8.15</v>
       </c>
       <c r="P13" t="n">
-        <v>9.48</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>4.64</v>
       </c>
       <c r="R13" t="n">
-        <v>7.745499999999999</v>
+        <v>7.727499999999999</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -1599,13 +1599,13 @@
         <v>9.33</v>
       </c>
       <c r="P15" t="n">
-        <v>6.26</v>
+        <v>6.23</v>
       </c>
       <c r="Q15" t="n">
         <v>2.86</v>
       </c>
       <c r="R15" t="n">
-        <v>7.7095</v>
+        <v>7.703500000000001</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -1677,13 +1677,13 @@
         <v>8.44</v>
       </c>
       <c r="P16" t="n">
-        <v>8.220000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="Q16" t="n">
         <v>1.51</v>
       </c>
       <c r="R16" t="n">
-        <v>7.305499999999999</v>
+        <v>7.289499999999999</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2067,13 +2067,13 @@
         <v>9.26</v>
       </c>
       <c r="P21" t="n">
-        <v>7.08</v>
+        <v>7.04</v>
       </c>
       <c r="Q21" t="n">
         <v>3.48</v>
       </c>
       <c r="R21" t="n">
-        <v>7.867000000000001</v>
+        <v>7.859000000000001</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2145,13 +2145,13 @@
         <v>8.15</v>
       </c>
       <c r="P22" t="n">
-        <v>9.48</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="Q22" t="n">
         <v>4.64</v>
       </c>
       <c r="R22" t="n">
-        <v>7.745499999999999</v>
+        <v>7.727499999999999</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2301,13 +2301,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>7.43</v>
+        <v>7.37</v>
       </c>
       <c r="Q24" t="n">
         <v>3.48</v>
       </c>
       <c r="R24" t="n">
-        <v>8.2645</v>
+        <v>8.2525</v>
       </c>
       <c r="S24" t="n">
         <v>2</v>
@@ -2379,13 +2379,13 @@
         <v>8.74</v>
       </c>
       <c r="P25" t="n">
-        <v>9.960000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="Q25" t="n">
         <v>7.6</v>
       </c>
       <c r="R25" t="n">
-        <v>8.807</v>
+        <v>8.813000000000001</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -2535,13 +2535,13 @@
         <v>9.26</v>
       </c>
       <c r="P27" t="n">
-        <v>6.94</v>
+        <v>6.9</v>
       </c>
       <c r="Q27" t="n">
         <v>3.48</v>
       </c>
       <c r="R27" t="n">
-        <v>7.794</v>
+        <v>7.786</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -2613,13 +2613,13 @@
         <v>8.52</v>
       </c>
       <c r="P28" t="n">
-        <v>8.49</v>
+        <v>8.42</v>
       </c>
       <c r="Q28" t="n">
         <v>3.07</v>
       </c>
       <c r="R28" t="n">
-        <v>7.5075</v>
+        <v>7.4935</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -2769,13 +2769,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="P30" t="n">
-        <v>7.08</v>
+        <v>7.04</v>
       </c>
       <c r="Q30" t="n">
         <v>3.48</v>
       </c>
       <c r="R30" t="n">
-        <v>8.125500000000001</v>
+        <v>8.1175</v>
       </c>
       <c r="S30" t="n">
         <v>2</v>
@@ -2847,13 +2847,13 @@
         <v>8.74</v>
       </c>
       <c r="P31" t="n">
-        <v>9.48</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="Q31" t="n">
         <v>7.6</v>
       </c>
       <c r="R31" t="n">
-        <v>8.603</v>
+        <v>8.584999999999999</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3003,13 +3003,13 @@
         <v>9.26</v>
       </c>
       <c r="P33" t="n">
-        <v>6.81</v>
+        <v>6.78</v>
       </c>
       <c r="Q33" t="n">
         <v>3.48</v>
       </c>
       <c r="R33" t="n">
-        <v>7.723</v>
+        <v>7.717</v>
       </c>
       <c r="S33" t="n">
         <v>2</v>
@@ -3081,13 +3081,13 @@
         <v>8.15</v>
       </c>
       <c r="P34" t="n">
-        <v>8.93</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="Q34" t="n">
         <v>4.64</v>
       </c>
       <c r="R34" t="n">
-        <v>7.4915</v>
+        <v>7.4775</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -3237,13 +3237,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="P36" t="n">
-        <v>7.28</v>
+        <v>7.23</v>
       </c>
       <c r="Q36" t="n">
         <v>3.48</v>
       </c>
       <c r="R36" t="n">
-        <v>8.2075</v>
+        <v>8.1975</v>
       </c>
       <c r="S36" t="n">
         <v>2</v>
@@ -3315,13 +3315,13 @@
         <v>9.039999999999999</v>
       </c>
       <c r="P37" t="n">
-        <v>9.08</v>
+        <v>8.99</v>
       </c>
       <c r="Q37" t="n">
         <v>6.37</v>
       </c>
       <c r="R37" t="n">
-        <v>8.605499999999999</v>
+        <v>8.5875</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -3705,13 +3705,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="P42" t="n">
-        <v>6.88</v>
+        <v>6.85</v>
       </c>
       <c r="Q42" t="n">
         <v>3.48</v>
       </c>
       <c r="R42" t="n">
-        <v>8.0345</v>
+        <v>8.028499999999999</v>
       </c>
       <c r="S42" t="n">
         <v>2</v>
@@ -3783,13 +3783,13 @@
         <v>8.74</v>
       </c>
       <c r="P43" t="n">
-        <v>9.07</v>
+        <v>9</v>
       </c>
       <c r="Q43" t="n">
         <v>7.6</v>
       </c>
       <c r="R43" t="n">
-        <v>8.436999999999999</v>
+        <v>8.423</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -3939,13 +3939,13 @@
         <v>9.26</v>
       </c>
       <c r="P45" t="n">
-        <v>6.81</v>
+        <v>6.78</v>
       </c>
       <c r="Q45" t="n">
         <v>3.48</v>
       </c>
       <c r="R45" t="n">
-        <v>7.723</v>
+        <v>7.717</v>
       </c>
       <c r="S45" t="n">
         <v>2</v>
@@ -4017,13 +4017,13 @@
         <v>8.15</v>
       </c>
       <c r="P46" t="n">
-        <v>8.93</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="Q46" t="n">
         <v>4.64</v>
       </c>
       <c r="R46" t="n">
-        <v>7.4915</v>
+        <v>7.4775</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
@@ -4407,13 +4407,13 @@
         <v>9.26</v>
       </c>
       <c r="P51" t="n">
-        <v>7.04</v>
+        <v>7</v>
       </c>
       <c r="Q51" t="n">
         <v>3.48</v>
       </c>
       <c r="R51" t="n">
-        <v>7.847</v>
+        <v>7.839</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -4485,13 +4485,13 @@
         <v>8.15</v>
       </c>
       <c r="P52" t="n">
-        <v>9.390000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="Q52" t="n">
         <v>4.64</v>
       </c>
       <c r="R52" t="n">
-        <v>7.7065</v>
+        <v>7.6905</v>
       </c>
       <c r="S52" t="n">
         <v>3</v>

--- a/workbooks/scenarios/ShowerRAGScenarios.xlsx
+++ b/workbooks/scenarios/ShowerRAGScenarios.xlsx
@@ -579,10 +579,10 @@
         <v>5</v>
       </c>
       <c r="N2" t="n">
-        <v>9.619999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>9.630000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="P2" t="n">
         <v>7.37</v>
@@ -591,7 +591,7 @@
         <v>3.48</v>
       </c>
       <c r="R2" t="n">
-        <v>8.2525</v>
+        <v>7.9495</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -657,10 +657,10 @@
         <v>8</v>
       </c>
       <c r="N3" t="n">
-        <v>8.720000000000001</v>
+        <v>8.17</v>
       </c>
       <c r="O3" t="n">
-        <v>8.74</v>
+        <v>7.44</v>
       </c>
       <c r="P3" t="n">
         <v>9.99</v>
@@ -669,7 +669,7 @@
         <v>7.6</v>
       </c>
       <c r="R3" t="n">
-        <v>8.813000000000001</v>
+        <v>8.193</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -735,10 +735,10 @@
         <v>12</v>
       </c>
       <c r="N4" t="n">
-        <v>7.53</v>
+        <v>6.56</v>
       </c>
       <c r="O4" t="n">
-        <v>7.56</v>
+        <v>5.38</v>
       </c>
       <c r="P4" t="n">
         <v>9.220000000000001</v>
@@ -747,7 +747,7 @@
         <v>6.69</v>
       </c>
       <c r="R4" t="n">
-        <v>7.7525</v>
+        <v>6.6985</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -813,10 +813,10 @@
         <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>9.24</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>9.26</v>
+        <v>8.33</v>
       </c>
       <c r="P5" t="n">
         <v>7.43</v>
@@ -825,7 +825,7 @@
         <v>3.48</v>
       </c>
       <c r="R5" t="n">
-        <v>8.020999999999999</v>
+        <v>7.587499999999999</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -891,10 +891,10 @@
         <v>8</v>
       </c>
       <c r="N6" t="n">
-        <v>8.119999999999999</v>
+        <v>7.37</v>
       </c>
       <c r="O6" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="P6" t="n">
         <v>9.960000000000001</v>
@@ -903,7 +903,7 @@
         <v>4.64</v>
       </c>
       <c r="R6" t="n">
-        <v>7.976499999999999</v>
+        <v>7.142499999999999</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
@@ -969,10 +969,10 @@
         <v>12</v>
       </c>
       <c r="N7" t="n">
-        <v>6.63</v>
+        <v>5.35</v>
       </c>
       <c r="O7" t="n">
-        <v>6.67</v>
+        <v>3.85</v>
       </c>
       <c r="P7" t="n">
         <v>9.210000000000001</v>
@@ -981,7 +981,7 @@
         <v>6.69</v>
       </c>
       <c r="R7" t="n">
-        <v>7.169</v>
+        <v>5.798</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1047,10 +1047,10 @@
         <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>9.539999999999999</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>9.93</v>
+        <v>9.49</v>
       </c>
       <c r="P8" t="n">
         <v>5.99</v>
@@ -1059,10 +1059,10 @@
         <v>2.86</v>
       </c>
       <c r="R8" t="n">
-        <v>7.9645</v>
+        <v>7.7325</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>1.115778842768697</v>
@@ -1125,10 +1125,10 @@
         <v>6</v>
       </c>
       <c r="N9" t="n">
-        <v>8.76</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>9.33</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="P9" t="n">
         <v>7.52</v>
@@ -1137,7 +1137,7 @@
         <v>5.01</v>
       </c>
       <c r="R9" t="n">
-        <v>8.148999999999999</v>
+        <v>7.682500000000001</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
@@ -1203,10 +1203,10 @@
         <v>10</v>
       </c>
       <c r="N10" t="n">
-        <v>7.19</v>
+        <v>6.1</v>
       </c>
       <c r="O10" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="P10" t="n">
         <v>9.970000000000001</v>
@@ -1215,10 +1215,10 @@
         <v>8.449999999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>8.271000000000001</v>
+        <v>7.335000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
         <v>2.789447106921743</v>
@@ -1281,10 +1281,10 @@
         <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>9.82</v>
+        <v>9.66</v>
       </c>
       <c r="O11" t="n">
-        <v>10</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="P11" t="n">
         <v>5.13</v>
@@ -1293,10 +1293,10 @@
         <v>2.2</v>
       </c>
       <c r="R11" t="n">
-        <v>7.802</v>
+        <v>7.621</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T11" t="n">
         <v>0.916444458800617</v>
@@ -1359,10 +1359,10 @@
         <v>5</v>
       </c>
       <c r="N12" t="n">
-        <v>8.960000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="O12" t="n">
-        <v>9.26</v>
+        <v>8.33</v>
       </c>
       <c r="P12" t="n">
         <v>7.04</v>
@@ -1371,10 +1371,10 @@
         <v>3.48</v>
       </c>
       <c r="R12" t="n">
-        <v>7.859000000000001</v>
+        <v>7.3955</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T12" t="n">
         <v>1.527407431334362</v>
@@ -1437,10 +1437,10 @@
         <v>8</v>
       </c>
       <c r="N13" t="n">
-        <v>7.67</v>
+        <v>6.76</v>
       </c>
       <c r="O13" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="P13" t="n">
         <v>9.390000000000001</v>
@@ -1449,7 +1449,7 @@
         <v>4.64</v>
       </c>
       <c r="R13" t="n">
-        <v>7.727499999999999</v>
+        <v>6.845499999999999</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -1515,10 +1515,10 @@
         <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>9.69</v>
+        <v>9.48</v>
       </c>
       <c r="O14" t="n">
-        <v>9.779999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="P14" t="n">
         <v>5.13</v>
@@ -1527,10 +1527,10 @@
         <v>2.2</v>
       </c>
       <c r="R14" t="n">
-        <v>7.685999999999999</v>
+        <v>7.4305</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
         <v>1.010866009101286</v>
@@ -1593,10 +1593,10 @@
         <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>9.210000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="O15" t="n">
-        <v>9.33</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="P15" t="n">
         <v>6.23</v>
@@ -1605,10 +1605,10 @@
         <v>2.86</v>
       </c>
       <c r="R15" t="n">
-        <v>7.703500000000001</v>
+        <v>7.288</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T15" t="n">
         <v>1.347821345468382</v>
@@ -1671,10 +1671,10 @@
         <v>6</v>
       </c>
       <c r="N16" t="n">
-        <v>8.27</v>
+        <v>7.56</v>
       </c>
       <c r="O16" t="n">
-        <v>8.44</v>
+        <v>6.92</v>
       </c>
       <c r="P16" t="n">
         <v>8.140000000000001</v>
@@ -1683,7 +1683,7 @@
         <v>1.51</v>
       </c>
       <c r="R16" t="n">
-        <v>7.289499999999999</v>
+        <v>6.544499999999999</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -1749,7 +1749,7 @@
         <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>9.77</v>
+        <v>9.58</v>
       </c>
       <c r="O17" t="n">
         <v>10</v>
@@ -1761,10 +1761,10 @@
         <v>2.2</v>
       </c>
       <c r="R17" t="n">
-        <v>7.786999999999999</v>
+        <v>7.73</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
         <v>0.955323920689128</v>
@@ -1827,10 +1827,10 @@
         <v>5</v>
       </c>
       <c r="N18" t="n">
-        <v>8.869999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>9.630000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="P18" t="n">
         <v>6.7</v>
@@ -1839,7 +1839,7 @@
         <v>3.48</v>
       </c>
       <c r="R18" t="n">
-        <v>7.8935</v>
+        <v>7.512499999999999</v>
       </c>
       <c r="S18" t="n">
         <v>2</v>
@@ -1905,10 +1905,10 @@
         <v>8</v>
       </c>
       <c r="N19" t="n">
-        <v>7.53</v>
+        <v>6.56</v>
       </c>
       <c r="O19" t="n">
-        <v>8.74</v>
+        <v>7.44</v>
       </c>
       <c r="P19" t="n">
         <v>8.69</v>
@@ -1917,10 +1917,10 @@
         <v>7.6</v>
       </c>
       <c r="R19" t="n">
-        <v>8.196</v>
+        <v>7.45</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
         <v>2.547530455171008</v>
@@ -1983,10 +1983,10 @@
         <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>9.82</v>
+        <v>9.66</v>
       </c>
       <c r="O20" t="n">
-        <v>10</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="P20" t="n">
         <v>5.13</v>
@@ -1995,10 +1995,10 @@
         <v>2.2</v>
       </c>
       <c r="R20" t="n">
-        <v>7.802</v>
+        <v>7.621</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
         <v>0.916444458800617</v>
@@ -2061,10 +2061,10 @@
         <v>5</v>
       </c>
       <c r="N21" t="n">
-        <v>8.960000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="O21" t="n">
-        <v>9.26</v>
+        <v>8.33</v>
       </c>
       <c r="P21" t="n">
         <v>7.04</v>
@@ -2073,10 +2073,10 @@
         <v>3.48</v>
       </c>
       <c r="R21" t="n">
-        <v>7.859000000000001</v>
+        <v>7.3955</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T21" t="n">
         <v>1.527407431334362</v>
@@ -2139,10 +2139,10 @@
         <v>8</v>
       </c>
       <c r="N22" t="n">
-        <v>7.67</v>
+        <v>6.76</v>
       </c>
       <c r="O22" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="P22" t="n">
         <v>9.390000000000001</v>
@@ -2151,7 +2151,7 @@
         <v>4.64</v>
       </c>
       <c r="R22" t="n">
-        <v>7.727499999999999</v>
+        <v>6.845499999999999</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2295,10 +2295,10 @@
         <v>5</v>
       </c>
       <c r="N24" t="n">
-        <v>9.619999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>9.630000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="P24" t="n">
         <v>7.37</v>
@@ -2307,7 +2307,7 @@
         <v>3.48</v>
       </c>
       <c r="R24" t="n">
-        <v>8.2525</v>
+        <v>7.9495</v>
       </c>
       <c r="S24" t="n">
         <v>2</v>
@@ -2373,10 +2373,10 @@
         <v>8</v>
       </c>
       <c r="N25" t="n">
-        <v>8.720000000000001</v>
+        <v>8.17</v>
       </c>
       <c r="O25" t="n">
-        <v>8.74</v>
+        <v>7.44</v>
       </c>
       <c r="P25" t="n">
         <v>9.99</v>
@@ -2385,7 +2385,7 @@
         <v>7.6</v>
       </c>
       <c r="R25" t="n">
-        <v>8.813000000000001</v>
+        <v>8.193</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -2451,10 +2451,10 @@
         <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>9.73</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>10</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="P26" t="n">
         <v>5.13</v>
@@ -2463,10 +2463,10 @@
         <v>2.2</v>
       </c>
       <c r="R26" t="n">
-        <v>7.775</v>
+        <v>7.584999999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T26" t="n">
         <v>0.9812435619481353</v>
@@ -2529,10 +2529,10 @@
         <v>5</v>
       </c>
       <c r="N27" t="n">
-        <v>8.81</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>9.26</v>
+        <v>8.33</v>
       </c>
       <c r="P27" t="n">
         <v>6.9</v>
@@ -2541,10 +2541,10 @@
         <v>3.48</v>
       </c>
       <c r="R27" t="n">
-        <v>7.786</v>
+        <v>7.3045</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T27" t="n">
         <v>1.635405936580226</v>
@@ -2607,10 +2607,10 @@
         <v>7</v>
       </c>
       <c r="N28" t="n">
-        <v>7.89</v>
+        <v>7.05</v>
       </c>
       <c r="O28" t="n">
-        <v>8.52</v>
+        <v>7.05</v>
       </c>
       <c r="P28" t="n">
         <v>8.42</v>
@@ -2619,7 +2619,7 @@
         <v>3.07</v>
       </c>
       <c r="R28" t="n">
-        <v>7.4935</v>
+        <v>6.726999999999999</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -2700,7 +2700,7 @@
         <v>7.856</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T29" t="n">
         <v>0.7331555670404936</v>
@@ -2763,10 +2763,10 @@
         <v>5</v>
       </c>
       <c r="N30" t="n">
-        <v>9.390000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="O30" t="n">
-        <v>9.630000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="P30" t="n">
         <v>7.04</v>
@@ -2775,10 +2775,10 @@
         <v>3.48</v>
       </c>
       <c r="R30" t="n">
-        <v>8.1175</v>
+        <v>7.793500000000001</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
         <v>1.221925945067489</v>
@@ -2841,10 +2841,10 @@
         <v>8</v>
       </c>
       <c r="N31" t="n">
-        <v>8.359999999999999</v>
+        <v>7.69</v>
       </c>
       <c r="O31" t="n">
-        <v>8.74</v>
+        <v>7.44</v>
       </c>
       <c r="P31" t="n">
         <v>9.390000000000001</v>
@@ -2853,7 +2853,7 @@
         <v>7.6</v>
       </c>
       <c r="R31" t="n">
-        <v>8.584999999999999</v>
+        <v>7.928999999999999</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -2919,10 +2919,10 @@
         <v>3</v>
       </c>
       <c r="N32" t="n">
-        <v>9.640000000000001</v>
+        <v>9.41</v>
       </c>
       <c r="O32" t="n">
-        <v>10</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="P32" t="n">
         <v>5.13</v>
@@ -2931,7 +2931,7 @@
         <v>2.2</v>
       </c>
       <c r="R32" t="n">
-        <v>7.747999999999999</v>
+        <v>7.545999999999999</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -2997,10 +2997,10 @@
         <v>5</v>
       </c>
       <c r="N33" t="n">
-        <v>8.66</v>
+        <v>8.09</v>
       </c>
       <c r="O33" t="n">
-        <v>9.26</v>
+        <v>8.33</v>
       </c>
       <c r="P33" t="n">
         <v>6.78</v>
@@ -3009,7 +3009,7 @@
         <v>3.48</v>
       </c>
       <c r="R33" t="n">
-        <v>7.717</v>
+        <v>7.220499999999999</v>
       </c>
       <c r="S33" t="n">
         <v>2</v>
@@ -3075,10 +3075,10 @@
         <v>8</v>
       </c>
       <c r="N34" t="n">
-        <v>7.19</v>
+        <v>6.1</v>
       </c>
       <c r="O34" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="P34" t="n">
         <v>8.859999999999999</v>
@@ -3087,7 +3087,7 @@
         <v>4.64</v>
       </c>
       <c r="R34" t="n">
-        <v>7.4775</v>
+        <v>6.5415</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -3231,10 +3231,10 @@
         <v>5</v>
       </c>
       <c r="N36" t="n">
-        <v>9.529999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="O36" t="n">
-        <v>9.630000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="P36" t="n">
         <v>7.23</v>
@@ -3243,7 +3243,7 @@
         <v>3.48</v>
       </c>
       <c r="R36" t="n">
-        <v>8.1975</v>
+        <v>7.888500000000001</v>
       </c>
       <c r="S36" t="n">
         <v>2</v>
@@ -3309,10 +3309,10 @@
         <v>7</v>
       </c>
       <c r="N37" t="n">
-        <v>8.9</v>
+        <v>8.41</v>
       </c>
       <c r="O37" t="n">
-        <v>9.039999999999999</v>
+        <v>7.95</v>
       </c>
       <c r="P37" t="n">
         <v>8.99</v>
@@ -3321,7 +3321,7 @@
         <v>6.37</v>
       </c>
       <c r="R37" t="n">
-        <v>8.5875</v>
+        <v>8.059000000000001</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -3387,7 +3387,7 @@
         <v>4</v>
       </c>
       <c r="N38" t="n">
-        <v>9.83</v>
+        <v>9.67</v>
       </c>
       <c r="O38" t="n">
         <v>10</v>
@@ -3399,7 +3399,7 @@
         <v>2.86</v>
       </c>
       <c r="R38" t="n">
-        <v>7.648</v>
+        <v>7.6</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -3465,10 +3465,10 @@
         <v>6</v>
       </c>
       <c r="N39" t="n">
-        <v>9.19</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O39" t="n">
-        <v>9.779999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="P39" t="n">
         <v>5.6</v>
@@ -3477,7 +3477,7 @@
         <v>5.01</v>
       </c>
       <c r="R39" t="n">
-        <v>8.051499999999999</v>
+        <v>7.742</v>
       </c>
       <c r="S39" t="n">
         <v>2</v>
@@ -3543,10 +3543,10 @@
         <v>10</v>
       </c>
       <c r="N40" t="n">
-        <v>7.91</v>
+        <v>7.07</v>
       </c>
       <c r="O40" t="n">
-        <v>8.890000000000001</v>
+        <v>7.69</v>
       </c>
       <c r="P40" t="n">
         <v>8.43</v>
@@ -3555,7 +3555,7 @@
         <v>8.449999999999999</v>
       </c>
       <c r="R40" t="n">
-        <v>8.437999999999999</v>
+        <v>7.766</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -3621,7 +3621,7 @@
         <v>3</v>
       </c>
       <c r="N41" t="n">
-        <v>9.98</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="O41" t="n">
         <v>10</v>
@@ -3633,10 +3633,10 @@
         <v>2.2</v>
       </c>
       <c r="R41" t="n">
-        <v>7.85</v>
+        <v>7.817</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T41" t="n">
         <v>0.8072116849233715</v>
@@ -3699,10 +3699,10 @@
         <v>5</v>
       </c>
       <c r="N42" t="n">
-        <v>9.220000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="O42" t="n">
-        <v>9.630000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="P42" t="n">
         <v>6.85</v>
@@ -3711,10 +3711,10 @@
         <v>3.48</v>
       </c>
       <c r="R42" t="n">
-        <v>8.028499999999999</v>
+        <v>7.6835</v>
       </c>
       <c r="S42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T42" t="n">
         <v>1.345352808205619</v>
@@ -3777,10 +3777,10 @@
         <v>8</v>
       </c>
       <c r="N43" t="n">
-        <v>8.08</v>
+        <v>7.31</v>
       </c>
       <c r="O43" t="n">
-        <v>8.74</v>
+        <v>7.44</v>
       </c>
       <c r="P43" t="n">
         <v>9</v>
@@ -3789,10 +3789,10 @@
         <v>7.6</v>
       </c>
       <c r="R43" t="n">
-        <v>8.423</v>
+        <v>7.736999999999999</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T43" t="n">
         <v>2.152564493128991</v>
@@ -3855,10 +3855,10 @@
         <v>3</v>
       </c>
       <c r="N44" t="n">
-        <v>9.640000000000001</v>
+        <v>9.41</v>
       </c>
       <c r="O44" t="n">
-        <v>10</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="P44" t="n">
         <v>5.13</v>
@@ -3867,7 +3867,7 @@
         <v>2.2</v>
       </c>
       <c r="R44" t="n">
-        <v>7.747999999999999</v>
+        <v>7.545999999999999</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -3933,10 +3933,10 @@
         <v>5</v>
       </c>
       <c r="N45" t="n">
-        <v>8.66</v>
+        <v>8.09</v>
       </c>
       <c r="O45" t="n">
-        <v>9.26</v>
+        <v>8.33</v>
       </c>
       <c r="P45" t="n">
         <v>6.78</v>
@@ -3945,7 +3945,7 @@
         <v>3.48</v>
       </c>
       <c r="R45" t="n">
-        <v>7.717</v>
+        <v>7.220499999999999</v>
       </c>
       <c r="S45" t="n">
         <v>2</v>
@@ -4011,10 +4011,10 @@
         <v>8</v>
       </c>
       <c r="N46" t="n">
-        <v>7.19</v>
+        <v>6.1</v>
       </c>
       <c r="O46" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="P46" t="n">
         <v>8.859999999999999</v>
@@ -4023,7 +4023,7 @@
         <v>4.64</v>
       </c>
       <c r="R46" t="n">
-        <v>7.4775</v>
+        <v>6.5415</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
@@ -4089,7 +4089,7 @@
         <v>3</v>
       </c>
       <c r="N47" t="n">
-        <v>9.800000000000001</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
@@ -4101,10 +4101,10 @@
         <v>2.2</v>
       </c>
       <c r="R47" t="n">
-        <v>7.795999999999999</v>
+        <v>7.745</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T47" t="n">
         <v>0.9331070853242645</v>
@@ -4167,10 +4167,10 @@
         <v>5</v>
       </c>
       <c r="N48" t="n">
-        <v>8.92</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O48" t="n">
-        <v>9.630000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="P48" t="n">
         <v>6.7</v>
@@ -4179,7 +4179,7 @@
         <v>3.48</v>
       </c>
       <c r="R48" t="n">
-        <v>7.9085</v>
+        <v>7.5365</v>
       </c>
       <c r="S48" t="n">
         <v>2</v>
@@ -4245,10 +4245,10 @@
         <v>8</v>
       </c>
       <c r="N49" t="n">
-        <v>7.61</v>
+        <v>6.67</v>
       </c>
       <c r="O49" t="n">
-        <v>8.74</v>
+        <v>7.44</v>
       </c>
       <c r="P49" t="n">
         <v>8.69</v>
@@ -4257,10 +4257,10 @@
         <v>7.6</v>
       </c>
       <c r="R49" t="n">
-        <v>8.220000000000001</v>
+        <v>7.483</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T49" t="n">
         <v>2.488285560864705</v>
@@ -4323,10 +4323,10 @@
         <v>3</v>
       </c>
       <c r="N50" t="n">
-        <v>9.800000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="O50" t="n">
-        <v>10</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="P50" t="n">
         <v>5.13</v>
@@ -4335,10 +4335,10 @@
         <v>2.2</v>
       </c>
       <c r="R50" t="n">
-        <v>7.795999999999999</v>
+        <v>7.608999999999999</v>
       </c>
       <c r="S50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T50" t="n">
         <v>0.9349584882713364</v>
@@ -4401,10 +4401,10 @@
         <v>5</v>
       </c>
       <c r="N51" t="n">
-        <v>8.92</v>
+        <v>8.44</v>
       </c>
       <c r="O51" t="n">
-        <v>9.26</v>
+        <v>8.33</v>
       </c>
       <c r="P51" t="n">
         <v>7</v>
@@ -4413,10 +4413,10 @@
         <v>3.48</v>
       </c>
       <c r="R51" t="n">
-        <v>7.839</v>
+        <v>7.3695</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T51" t="n">
         <v>1.558264147118894</v>
@@ -4479,10 +4479,10 @@
         <v>8</v>
       </c>
       <c r="N52" t="n">
-        <v>7.6</v>
+        <v>6.66</v>
       </c>
       <c r="O52" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="P52" t="n">
         <v>9.31</v>
@@ -4491,7 +4491,7 @@
         <v>4.64</v>
       </c>
       <c r="R52" t="n">
-        <v>7.6905</v>
+        <v>6.7995</v>
       </c>
       <c r="S52" t="n">
         <v>3</v>
@@ -4557,10 +4557,10 @@
         <v>4</v>
       </c>
       <c r="N53" t="n">
-        <v>7.97</v>
+        <v>7.16</v>
       </c>
       <c r="O53" t="n">
-        <v>9.039999999999999</v>
+        <v>7.95</v>
       </c>
       <c r="P53" t="n">
         <v>5.94</v>
@@ -4569,7 +4569,7 @@
         <v>1.51</v>
       </c>
       <c r="R53" t="n">
-        <v>6.9695</v>
+        <v>6.345000000000001</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -4635,10 +4635,10 @@
         <v>6</v>
       </c>
       <c r="N54" t="n">
-        <v>6.41</v>
+        <v>5.05</v>
       </c>
       <c r="O54" t="n">
-        <v>8</v>
+        <v>6.15</v>
       </c>
       <c r="P54" t="n">
         <v>7.4</v>
@@ -4647,7 +4647,7 @@
         <v>1.51</v>
       </c>
       <c r="R54" t="n">
-        <v>6.4295</v>
+        <v>5.374</v>
       </c>
       <c r="S54" t="n">
         <v>2</v>
@@ -4713,10 +4713,10 @@
         <v>8</v>
       </c>
       <c r="N55" t="n">
-        <v>4.84</v>
+        <v>2.93</v>
       </c>
       <c r="O55" t="n">
-        <v>6.96</v>
+        <v>4.36</v>
       </c>
       <c r="P55" t="n">
         <v>8.619999999999999</v>
@@ -4725,7 +4725,7 @@
         <v>4.64</v>
       </c>
       <c r="R55" t="n">
-        <v>6.308</v>
+        <v>4.825</v>
       </c>
       <c r="S55" t="n">
         <v>3</v>
@@ -4869,10 +4869,10 @@
         <v>7</v>
       </c>
       <c r="N57" t="n">
-        <v>9.539999999999999</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="O57" t="n">
-        <v>9.56</v>
+        <v>8.85</v>
       </c>
       <c r="P57" t="n">
         <v>9.32</v>
@@ -4881,7 +4881,7 @@
         <v>6.37</v>
       </c>
       <c r="R57" t="n">
-        <v>9.027500000000002</v>
+        <v>8.700999999999999</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
@@ -4947,10 +4947,10 @@
         <v>10</v>
       </c>
       <c r="N58" t="n">
-        <v>8.869999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="O58" t="n">
-        <v>8.890000000000001</v>
+        <v>7.69</v>
       </c>
       <c r="P58" t="n">
         <v>9.59</v>
@@ -4959,7 +4959,7 @@
         <v>8.449999999999999</v>
       </c>
       <c r="R58" t="n">
-        <v>8.957999999999998</v>
+        <v>8.388</v>
       </c>
       <c r="S58" t="n">
         <v>2</v>
@@ -5025,10 +5025,10 @@
         <v>5</v>
       </c>
       <c r="N59" t="n">
-        <v>8.48</v>
+        <v>7.85</v>
       </c>
       <c r="O59" t="n">
-        <v>9.26</v>
+        <v>8.33</v>
       </c>
       <c r="P59" t="n">
         <v>6.7</v>
@@ -5037,7 +5037,7 @@
         <v>1.51</v>
       </c>
       <c r="R59" t="n">
-        <v>7.3515</v>
+        <v>6.837</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -5103,10 +5103,10 @@
         <v>8</v>
       </c>
       <c r="N60" t="n">
-        <v>6.91</v>
+        <v>5.72</v>
       </c>
       <c r="O60" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="P60" t="n">
         <v>8.619999999999999</v>
@@ -5115,7 +5115,7 @@
         <v>4.64</v>
       </c>
       <c r="R60" t="n">
-        <v>7.345499999999999</v>
+        <v>6.3795</v>
       </c>
       <c r="S60" t="n">
         <v>2</v>
@@ -5181,10 +5181,10 @@
         <v>12</v>
       </c>
       <c r="N61" t="n">
-        <v>4.81</v>
+        <v>2.89</v>
       </c>
       <c r="O61" t="n">
-        <v>6.67</v>
+        <v>3.85</v>
       </c>
       <c r="P61" t="n">
         <v>7.97</v>
@@ -5193,7 +5193,7 @@
         <v>6.69</v>
       </c>
       <c r="R61" t="n">
-        <v>6.375</v>
+        <v>4.812</v>
       </c>
       <c r="S61" t="n">
         <v>3</v>

--- a/workbooks/scenarios/ShowerRAGScenarios.xlsx
+++ b/workbooks/scenarios/ShowerRAGScenarios.xlsx
@@ -579,19 +579,19 @@
         <v>5</v>
       </c>
       <c r="N2" t="n">
-        <v>9.380000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>8.970000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="P2" t="n">
-        <v>7.37</v>
+        <v>0.74</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="R2" t="n">
-        <v>7.9495</v>
+        <v>0.7975</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -657,19 +657,19 @@
         <v>8</v>
       </c>
       <c r="N3" t="n">
-        <v>8.17</v>
+        <v>0.82</v>
       </c>
       <c r="O3" t="n">
-        <v>7.44</v>
+        <v>0.74</v>
       </c>
       <c r="P3" t="n">
-        <v>9.99</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.6</v>
+        <v>0.76</v>
       </c>
       <c r="R3" t="n">
-        <v>8.193</v>
+        <v>0.8190000000000001</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -735,19 +735,19 @@
         <v>12</v>
       </c>
       <c r="N4" t="n">
-        <v>6.56</v>
+        <v>0.66</v>
       </c>
       <c r="O4" t="n">
-        <v>5.38</v>
+        <v>0.54</v>
       </c>
       <c r="P4" t="n">
-        <v>9.220000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="R4" t="n">
-        <v>6.6985</v>
+        <v>0.6715000000000001</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -813,19 +813,19 @@
         <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>8.880000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="O5" t="n">
-        <v>8.33</v>
+        <v>0.83</v>
       </c>
       <c r="P5" t="n">
-        <v>7.43</v>
+        <v>0.74</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="R5" t="n">
-        <v>7.587499999999999</v>
+        <v>0.758</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -891,19 +891,19 @@
         <v>8</v>
       </c>
       <c r="N6" t="n">
-        <v>7.37</v>
+        <v>0.74</v>
       </c>
       <c r="O6" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="P6" t="n">
-        <v>9.960000000000001</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="R6" t="n">
-        <v>7.142499999999999</v>
+        <v>0.7149999999999999</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
@@ -969,19 +969,19 @@
         <v>12</v>
       </c>
       <c r="N7" t="n">
-        <v>5.35</v>
+        <v>0.53</v>
       </c>
       <c r="O7" t="n">
-        <v>3.85</v>
+        <v>0.38</v>
       </c>
       <c r="P7" t="n">
-        <v>9.210000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="R7" t="n">
-        <v>5.798</v>
+        <v>0.5765</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1047,19 +1047,19 @@
         <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>9.279999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="O8" t="n">
-        <v>9.49</v>
+        <v>0.95</v>
       </c>
       <c r="P8" t="n">
-        <v>5.99</v>
+        <v>0.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="R8" t="n">
-        <v>7.7325</v>
+        <v>0.7749999999999999</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1125,19 +1125,19 @@
         <v>6</v>
       </c>
       <c r="N9" t="n">
-        <v>8.220000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="O9" t="n">
-        <v>8.460000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="P9" t="n">
-        <v>7.52</v>
+        <v>0.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.01</v>
+        <v>0.5</v>
       </c>
       <c r="R9" t="n">
-        <v>7.682500000000001</v>
+        <v>0.7685</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
@@ -1203,19 +1203,19 @@
         <v>10</v>
       </c>
       <c r="N10" t="n">
-        <v>6.1</v>
+        <v>0.61</v>
       </c>
       <c r="O10" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="P10" t="n">
-        <v>9.970000000000001</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.449999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="R10" t="n">
-        <v>7.335000000000001</v>
+        <v>0.7344999999999999</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1281,19 +1281,19 @@
         <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>9.66</v>
+        <v>0.97</v>
       </c>
       <c r="O11" t="n">
-        <v>9.619999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="P11" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="R11" t="n">
-        <v>7.621</v>
+        <v>0.762</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1359,19 +1359,19 @@
         <v>5</v>
       </c>
       <c r="N12" t="n">
-        <v>8.5</v>
+        <v>0.85</v>
       </c>
       <c r="O12" t="n">
-        <v>8.33</v>
+        <v>0.83</v>
       </c>
       <c r="P12" t="n">
-        <v>7.04</v>
+        <v>0.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="R12" t="n">
-        <v>7.3955</v>
+        <v>0.738</v>
       </c>
       <c r="S12" t="n">
         <v>2</v>
@@ -1437,19 +1437,19 @@
         <v>8</v>
       </c>
       <c r="N13" t="n">
-        <v>6.76</v>
+        <v>0.68</v>
       </c>
       <c r="O13" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="P13" t="n">
-        <v>9.390000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="R13" t="n">
-        <v>6.845499999999999</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -1515,19 +1515,19 @@
         <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>9.48</v>
+        <v>0.95</v>
       </c>
       <c r="O14" t="n">
-        <v>9.23</v>
+        <v>0.92</v>
       </c>
       <c r="P14" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="R14" t="n">
-        <v>7.4305</v>
+        <v>0.742</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1593,19 +1593,19 @@
         <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>8.84</v>
+        <v>0.88</v>
       </c>
       <c r="O15" t="n">
-        <v>8.460000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="P15" t="n">
-        <v>6.23</v>
+        <v>0.62</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="R15" t="n">
-        <v>7.288</v>
+        <v>0.729</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
@@ -1671,19 +1671,19 @@
         <v>6</v>
       </c>
       <c r="N16" t="n">
-        <v>7.56</v>
+        <v>0.76</v>
       </c>
       <c r="O16" t="n">
-        <v>6.92</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>8.140000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.51</v>
+        <v>0.15</v>
       </c>
       <c r="R16" t="n">
-        <v>6.544499999999999</v>
+        <v>0.6539999999999999</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -1749,19 +1749,19 @@
         <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>9.58</v>
+        <v>0.96</v>
       </c>
       <c r="O17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P17" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="R17" t="n">
-        <v>7.73</v>
+        <v>0.7729999999999999</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -1827,19 +1827,19 @@
         <v>5</v>
       </c>
       <c r="N18" t="n">
-        <v>8.369999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="O18" t="n">
-        <v>8.970000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="P18" t="n">
-        <v>6.7</v>
+        <v>0.67</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="R18" t="n">
-        <v>7.512499999999999</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="S18" t="n">
         <v>2</v>
@@ -1905,19 +1905,19 @@
         <v>8</v>
       </c>
       <c r="N19" t="n">
-        <v>6.56</v>
+        <v>0.66</v>
       </c>
       <c r="O19" t="n">
-        <v>7.44</v>
+        <v>0.74</v>
       </c>
       <c r="P19" t="n">
-        <v>8.69</v>
+        <v>0.87</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.6</v>
+        <v>0.76</v>
       </c>
       <c r="R19" t="n">
-        <v>7.45</v>
+        <v>0.745</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -1983,19 +1983,19 @@
         <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>9.66</v>
+        <v>0.97</v>
       </c>
       <c r="O20" t="n">
-        <v>9.619999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="P20" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="R20" t="n">
-        <v>7.621</v>
+        <v>0.762</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2061,19 +2061,19 @@
         <v>5</v>
       </c>
       <c r="N21" t="n">
-        <v>8.5</v>
+        <v>0.85</v>
       </c>
       <c r="O21" t="n">
-        <v>8.33</v>
+        <v>0.83</v>
       </c>
       <c r="P21" t="n">
-        <v>7.04</v>
+        <v>0.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="R21" t="n">
-        <v>7.3955</v>
+        <v>0.738</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
@@ -2139,19 +2139,19 @@
         <v>8</v>
       </c>
       <c r="N22" t="n">
-        <v>6.76</v>
+        <v>0.68</v>
       </c>
       <c r="O22" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="P22" t="n">
-        <v>9.390000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="R22" t="n">
-        <v>6.845499999999999</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2217,19 +2217,19 @@
         <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P23" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="R23" t="n">
-        <v>7.856</v>
+        <v>0.7849999999999999</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -2295,19 +2295,19 @@
         <v>5</v>
       </c>
       <c r="N24" t="n">
-        <v>9.380000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>8.970000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="P24" t="n">
-        <v>7.37</v>
+        <v>0.74</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="R24" t="n">
-        <v>7.9495</v>
+        <v>0.7975</v>
       </c>
       <c r="S24" t="n">
         <v>2</v>
@@ -2373,19 +2373,19 @@
         <v>8</v>
       </c>
       <c r="N25" t="n">
-        <v>8.17</v>
+        <v>0.82</v>
       </c>
       <c r="O25" t="n">
-        <v>7.44</v>
+        <v>0.74</v>
       </c>
       <c r="P25" t="n">
-        <v>9.99</v>
+        <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>7.6</v>
+        <v>0.76</v>
       </c>
       <c r="R25" t="n">
-        <v>8.193</v>
+        <v>0.8190000000000001</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -2451,19 +2451,19 @@
         <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>9.539999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="O26" t="n">
-        <v>9.619999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="P26" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="R26" t="n">
-        <v>7.584999999999999</v>
+        <v>0.756</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -2529,19 +2529,19 @@
         <v>5</v>
       </c>
       <c r="N27" t="n">
-        <v>8.289999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="O27" t="n">
-        <v>8.33</v>
+        <v>0.83</v>
       </c>
       <c r="P27" t="n">
-        <v>6.9</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="R27" t="n">
-        <v>7.3045</v>
+        <v>0.73</v>
       </c>
       <c r="S27" t="n">
         <v>2</v>
@@ -2607,19 +2607,19 @@
         <v>7</v>
       </c>
       <c r="N28" t="n">
-        <v>7.05</v>
+        <v>0.7</v>
       </c>
       <c r="O28" t="n">
-        <v>7.05</v>
+        <v>0.71</v>
       </c>
       <c r="P28" t="n">
-        <v>8.42</v>
+        <v>0.84</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.07</v>
+        <v>0.31</v>
       </c>
       <c r="R28" t="n">
-        <v>6.726999999999999</v>
+        <v>0.6729999999999999</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -2685,19 +2685,19 @@
         <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P29" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="R29" t="n">
-        <v>7.856</v>
+        <v>0.7849999999999999</v>
       </c>
       <c r="S29" t="n">
         <v>2</v>
@@ -2763,19 +2763,19 @@
         <v>5</v>
       </c>
       <c r="N30" t="n">
-        <v>9.08</v>
+        <v>0.91</v>
       </c>
       <c r="O30" t="n">
-        <v>8.970000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="P30" t="n">
-        <v>7.04</v>
+        <v>0.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="R30" t="n">
-        <v>7.793500000000001</v>
+        <v>0.7805000000000001</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -2841,19 +2841,19 @@
         <v>8</v>
       </c>
       <c r="N31" t="n">
-        <v>7.69</v>
+        <v>0.77</v>
       </c>
       <c r="O31" t="n">
-        <v>7.44</v>
+        <v>0.74</v>
       </c>
       <c r="P31" t="n">
-        <v>9.390000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q31" t="n">
-        <v>7.6</v>
+        <v>0.76</v>
       </c>
       <c r="R31" t="n">
-        <v>7.928999999999999</v>
+        <v>0.7919999999999999</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -2919,19 +2919,19 @@
         <v>3</v>
       </c>
       <c r="N32" t="n">
-        <v>9.41</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>9.619999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="P32" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="R32" t="n">
-        <v>7.545999999999999</v>
+        <v>0.7529999999999999</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -2997,19 +2997,19 @@
         <v>5</v>
       </c>
       <c r="N33" t="n">
-        <v>8.09</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="O33" t="n">
-        <v>8.33</v>
+        <v>0.83</v>
       </c>
       <c r="P33" t="n">
-        <v>6.78</v>
+        <v>0.68</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="R33" t="n">
-        <v>7.220499999999999</v>
+        <v>0.722</v>
       </c>
       <c r="S33" t="n">
         <v>2</v>
@@ -3075,19 +3075,19 @@
         <v>8</v>
       </c>
       <c r="N34" t="n">
-        <v>6.1</v>
+        <v>0.61</v>
       </c>
       <c r="O34" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="P34" t="n">
-        <v>8.859999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="R34" t="n">
-        <v>6.5415</v>
+        <v>0.6539999999999999</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -3153,19 +3153,19 @@
         <v>3</v>
       </c>
       <c r="N35" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P35" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="R35" t="n">
-        <v>7.856</v>
+        <v>0.7849999999999999</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -3231,19 +3231,19 @@
         <v>5</v>
       </c>
       <c r="N36" t="n">
-        <v>9.27</v>
+        <v>0.93</v>
       </c>
       <c r="O36" t="n">
-        <v>8.970000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="P36" t="n">
-        <v>7.23</v>
+        <v>0.72</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="R36" t="n">
-        <v>7.888500000000001</v>
+        <v>0.7905000000000001</v>
       </c>
       <c r="S36" t="n">
         <v>2</v>
@@ -3309,19 +3309,19 @@
         <v>7</v>
       </c>
       <c r="N37" t="n">
-        <v>8.41</v>
+        <v>0.84</v>
       </c>
       <c r="O37" t="n">
-        <v>7.95</v>
+        <v>0.79</v>
       </c>
       <c r="P37" t="n">
-        <v>8.99</v>
+        <v>0.9</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.37</v>
+        <v>0.64</v>
       </c>
       <c r="R37" t="n">
-        <v>8.059000000000001</v>
+        <v>0.8045</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -3387,19 +3387,19 @@
         <v>4</v>
       </c>
       <c r="N38" t="n">
-        <v>9.67</v>
+        <v>0.97</v>
       </c>
       <c r="O38" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P38" t="n">
-        <v>3.85</v>
+        <v>0.39</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="R38" t="n">
-        <v>7.6</v>
+        <v>0.7625000000000001</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -3465,19 +3465,19 @@
         <v>6</v>
       </c>
       <c r="N39" t="n">
-        <v>8.800000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="O39" t="n">
-        <v>9.23</v>
+        <v>0.92</v>
       </c>
       <c r="P39" t="n">
-        <v>5.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.01</v>
+        <v>0.5</v>
       </c>
       <c r="R39" t="n">
-        <v>7.742</v>
+        <v>0.773</v>
       </c>
       <c r="S39" t="n">
         <v>2</v>
@@ -3543,19 +3543,19 @@
         <v>10</v>
       </c>
       <c r="N40" t="n">
-        <v>7.07</v>
+        <v>0.71</v>
       </c>
       <c r="O40" t="n">
-        <v>7.69</v>
+        <v>0.77</v>
       </c>
       <c r="P40" t="n">
-        <v>8.43</v>
+        <v>0.84</v>
       </c>
       <c r="Q40" t="n">
-        <v>8.449999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="R40" t="n">
-        <v>7.766</v>
+        <v>0.778</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -3621,19 +3621,19 @@
         <v>3</v>
       </c>
       <c r="N41" t="n">
-        <v>9.869999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="O41" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P41" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="R41" t="n">
-        <v>7.817</v>
+        <v>0.782</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -3699,19 +3699,19 @@
         <v>5</v>
       </c>
       <c r="N42" t="n">
-        <v>8.84</v>
+        <v>0.88</v>
       </c>
       <c r="O42" t="n">
-        <v>8.970000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="P42" t="n">
-        <v>6.85</v>
+        <v>0.68</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="R42" t="n">
-        <v>7.6835</v>
+        <v>0.7675</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -3777,19 +3777,19 @@
         <v>8</v>
       </c>
       <c r="N43" t="n">
-        <v>7.31</v>
+        <v>0.73</v>
       </c>
       <c r="O43" t="n">
-        <v>7.44</v>
+        <v>0.74</v>
       </c>
       <c r="P43" t="n">
-        <v>9</v>
+        <v>0.9</v>
       </c>
       <c r="Q43" t="n">
-        <v>7.6</v>
+        <v>0.76</v>
       </c>
       <c r="R43" t="n">
-        <v>7.736999999999999</v>
+        <v>0.772</v>
       </c>
       <c r="S43" t="n">
         <v>2</v>
@@ -3855,19 +3855,19 @@
         <v>3</v>
       </c>
       <c r="N44" t="n">
-        <v>9.41</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O44" t="n">
-        <v>9.619999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="P44" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="R44" t="n">
-        <v>7.545999999999999</v>
+        <v>0.7529999999999999</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -3933,19 +3933,19 @@
         <v>5</v>
       </c>
       <c r="N45" t="n">
-        <v>8.09</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="O45" t="n">
-        <v>8.33</v>
+        <v>0.83</v>
       </c>
       <c r="P45" t="n">
-        <v>6.78</v>
+        <v>0.68</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="R45" t="n">
-        <v>7.220499999999999</v>
+        <v>0.722</v>
       </c>
       <c r="S45" t="n">
         <v>2</v>
@@ -4011,19 +4011,19 @@
         <v>8</v>
       </c>
       <c r="N46" t="n">
-        <v>6.1</v>
+        <v>0.61</v>
       </c>
       <c r="O46" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="P46" t="n">
-        <v>8.859999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="R46" t="n">
-        <v>6.5415</v>
+        <v>0.6539999999999999</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
@@ -4089,19 +4089,19 @@
         <v>3</v>
       </c>
       <c r="N47" t="n">
-        <v>9.630000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="O47" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P47" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="R47" t="n">
-        <v>7.745</v>
+        <v>0.7729999999999999</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -4167,19 +4167,19 @@
         <v>5</v>
       </c>
       <c r="N48" t="n">
-        <v>8.449999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="O48" t="n">
-        <v>8.970000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="P48" t="n">
-        <v>6.7</v>
+        <v>0.67</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="R48" t="n">
-        <v>7.5365</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="S48" t="n">
         <v>2</v>
@@ -4245,19 +4245,19 @@
         <v>8</v>
       </c>
       <c r="N49" t="n">
-        <v>6.67</v>
+        <v>0.67</v>
       </c>
       <c r="O49" t="n">
-        <v>7.44</v>
+        <v>0.74</v>
       </c>
       <c r="P49" t="n">
-        <v>8.69</v>
+        <v>0.87</v>
       </c>
       <c r="Q49" t="n">
-        <v>7.6</v>
+        <v>0.76</v>
       </c>
       <c r="R49" t="n">
-        <v>7.483</v>
+        <v>0.748</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -4323,19 +4323,19 @@
         <v>3</v>
       </c>
       <c r="N50" t="n">
-        <v>9.619999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="O50" t="n">
-        <v>9.619999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="P50" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="R50" t="n">
-        <v>7.608999999999999</v>
+        <v>0.7589999999999999</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -4401,19 +4401,19 @@
         <v>5</v>
       </c>
       <c r="N51" t="n">
-        <v>8.44</v>
+        <v>0.84</v>
       </c>
       <c r="O51" t="n">
-        <v>8.33</v>
+        <v>0.83</v>
       </c>
       <c r="P51" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="R51" t="n">
-        <v>7.3695</v>
+        <v>0.735</v>
       </c>
       <c r="S51" t="n">
         <v>2</v>
@@ -4479,19 +4479,19 @@
         <v>8</v>
       </c>
       <c r="N52" t="n">
-        <v>6.66</v>
+        <v>0.67</v>
       </c>
       <c r="O52" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="P52" t="n">
-        <v>9.31</v>
+        <v>0.93</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="R52" t="n">
-        <v>6.7995</v>
+        <v>0.6799999999999999</v>
       </c>
       <c r="S52" t="n">
         <v>3</v>
@@ -4557,19 +4557,19 @@
         <v>4</v>
       </c>
       <c r="N53" t="n">
-        <v>7.16</v>
+        <v>0.72</v>
       </c>
       <c r="O53" t="n">
-        <v>7.95</v>
+        <v>0.79</v>
       </c>
       <c r="P53" t="n">
-        <v>5.94</v>
+        <v>0.59</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.51</v>
+        <v>0.15</v>
       </c>
       <c r="R53" t="n">
-        <v>6.345000000000001</v>
+        <v>0.6329999999999999</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -4635,19 +4635,19 @@
         <v>6</v>
       </c>
       <c r="N54" t="n">
-        <v>5.05</v>
+        <v>0.5</v>
       </c>
       <c r="O54" t="n">
-        <v>6.15</v>
+        <v>0.62</v>
       </c>
       <c r="P54" t="n">
-        <v>7.4</v>
+        <v>0.74</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.51</v>
+        <v>0.15</v>
       </c>
       <c r="R54" t="n">
-        <v>5.374</v>
+        <v>0.5375</v>
       </c>
       <c r="S54" t="n">
         <v>2</v>
@@ -4713,19 +4713,19 @@
         <v>8</v>
       </c>
       <c r="N55" t="n">
-        <v>2.93</v>
+        <v>0.29</v>
       </c>
       <c r="O55" t="n">
-        <v>4.36</v>
+        <v>0.44</v>
       </c>
       <c r="P55" t="n">
-        <v>8.619999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="R55" t="n">
-        <v>4.825</v>
+        <v>0.482</v>
       </c>
       <c r="S55" t="n">
         <v>3</v>
@@ -4791,19 +4791,19 @@
         <v>4</v>
       </c>
       <c r="N56" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P56" t="n">
-        <v>6.34</v>
+        <v>0.63</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="R56" t="n">
-        <v>8.196999999999999</v>
+        <v>0.8194999999999999</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
@@ -4869,19 +4869,19 @@
         <v>7</v>
       </c>
       <c r="N57" t="n">
-        <v>9.279999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="O57" t="n">
-        <v>8.85</v>
+        <v>0.88</v>
       </c>
       <c r="P57" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="Q57" t="n">
-        <v>6.37</v>
+        <v>0.64</v>
       </c>
       <c r="R57" t="n">
-        <v>8.700999999999999</v>
+        <v>0.869</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
@@ -4947,19 +4947,19 @@
         <v>10</v>
       </c>
       <c r="N58" t="n">
-        <v>8.369999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="O58" t="n">
-        <v>7.69</v>
+        <v>0.77</v>
       </c>
       <c r="P58" t="n">
-        <v>9.59</v>
+        <v>0.96</v>
       </c>
       <c r="Q58" t="n">
-        <v>8.449999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="R58" t="n">
-        <v>8.388</v>
+        <v>0.841</v>
       </c>
       <c r="S58" t="n">
         <v>2</v>
@@ -5025,19 +5025,19 @@
         <v>5</v>
       </c>
       <c r="N59" t="n">
-        <v>7.85</v>
+        <v>0.79</v>
       </c>
       <c r="O59" t="n">
-        <v>8.33</v>
+        <v>0.83</v>
       </c>
       <c r="P59" t="n">
-        <v>6.7</v>
+        <v>0.67</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.51</v>
+        <v>0.15</v>
       </c>
       <c r="R59" t="n">
-        <v>6.837</v>
+        <v>0.6839999999999999</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -5103,19 +5103,19 @@
         <v>8</v>
       </c>
       <c r="N60" t="n">
-        <v>5.72</v>
+        <v>0.57</v>
       </c>
       <c r="O60" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="P60" t="n">
-        <v>8.619999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="R60" t="n">
-        <v>6.3795</v>
+        <v>0.6359999999999999</v>
       </c>
       <c r="S60" t="n">
         <v>2</v>
@@ -5181,19 +5181,19 @@
         <v>12</v>
       </c>
       <c r="N61" t="n">
-        <v>2.89</v>
+        <v>0.29</v>
       </c>
       <c r="O61" t="n">
-        <v>3.85</v>
+        <v>0.38</v>
       </c>
       <c r="P61" t="n">
-        <v>7.97</v>
+        <v>0.8</v>
       </c>
       <c r="Q61" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="R61" t="n">
-        <v>4.812</v>
+        <v>0.4805</v>
       </c>
       <c r="S61" t="n">
         <v>3</v>

--- a/workbooks/scenarios/ShowerRAGScenarios.xlsx
+++ b/workbooks/scenarios/ShowerRAGScenarios.xlsx
@@ -4719,13 +4719,13 @@
         <v>0.44</v>
       </c>
       <c r="P55" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="Q55" t="n">
         <v>0.46</v>
       </c>
       <c r="R55" t="n">
-        <v>0.482</v>
+        <v>0.484</v>
       </c>
       <c r="S55" t="n">
         <v>3</v>
@@ -5109,13 +5109,13 @@
         <v>0.64</v>
       </c>
       <c r="P60" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="Q60" t="n">
         <v>0.46</v>
       </c>
       <c r="R60" t="n">
-        <v>0.6359999999999999</v>
+        <v>0.6379999999999999</v>
       </c>
       <c r="S60" t="n">
         <v>2</v>
@@ -5187,13 +5187,13 @@
         <v>0.38</v>
       </c>
       <c r="P61" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="Q61" t="n">
         <v>0.67</v>
       </c>
       <c r="R61" t="n">
-        <v>0.4805</v>
+        <v>0.4985000000000001</v>
       </c>
       <c r="S61" t="n">
         <v>3</v>

--- a/workbooks/scenarios/ShowerRAGScenarios.xlsx
+++ b/workbooks/scenarios/ShowerRAGScenarios.xlsx
@@ -1053,13 +1053,13 @@
         <v>0.95</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6</v>
+        <v>0.39</v>
       </c>
       <c r="Q8" t="n">
         <v>0.29</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7749999999999999</v>
+        <v>0.733</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1131,13 +1131,13 @@
         <v>0.85</v>
       </c>
       <c r="P9" t="n">
-        <v>0.75</v>
+        <v>0.57</v>
       </c>
       <c r="Q9" t="n">
         <v>0.5</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7685</v>
+        <v>0.7324999999999999</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
@@ -1209,13 +1209,13 @@
         <v>0.64</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="Q10" t="n">
         <v>0.85</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7344999999999999</v>
+        <v>0.7064999999999999</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -2223,13 +2223,13 @@
         <v>1</v>
       </c>
       <c r="P23" t="n">
-        <v>0.51</v>
+        <v>0.29</v>
       </c>
       <c r="Q23" t="n">
         <v>0.22</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.741</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -2301,13 +2301,13 @@
         <v>0.9</v>
       </c>
       <c r="P24" t="n">
-        <v>0.74</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q24" t="n">
         <v>0.35</v>
       </c>
       <c r="R24" t="n">
-        <v>0.7975</v>
+        <v>0.7615</v>
       </c>
       <c r="S24" t="n">
         <v>2</v>
@@ -2379,13 +2379,13 @@
         <v>0.74</v>
       </c>
       <c r="P25" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="Q25" t="n">
         <v>0.76</v>
       </c>
       <c r="R25" t="n">
-        <v>0.8190000000000001</v>
+        <v>0.791</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -2691,16 +2691,16 @@
         <v>1</v>
       </c>
       <c r="P29" t="n">
-        <v>0.51</v>
+        <v>0.29</v>
       </c>
       <c r="Q29" t="n">
         <v>0.22</v>
       </c>
       <c r="R29" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.741</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T29" t="n">
         <v>0.7331555670404936</v>
@@ -2769,16 +2769,16 @@
         <v>0.9</v>
       </c>
       <c r="P30" t="n">
-        <v>0.7</v>
+        <v>0.52</v>
       </c>
       <c r="Q30" t="n">
         <v>0.35</v>
       </c>
       <c r="R30" t="n">
-        <v>0.7805000000000001</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T30" t="n">
         <v>1.221925945067489</v>
@@ -2847,13 +2847,13 @@
         <v>0.74</v>
       </c>
       <c r="P31" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="Q31" t="n">
         <v>0.76</v>
       </c>
       <c r="R31" t="n">
-        <v>0.7919999999999999</v>
+        <v>0.762</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3627,16 +3627,16 @@
         <v>1</v>
       </c>
       <c r="P41" t="n">
-        <v>0.51</v>
+        <v>0.29</v>
       </c>
       <c r="Q41" t="n">
         <v>0.22</v>
       </c>
       <c r="R41" t="n">
-        <v>0.782</v>
+        <v>0.7380000000000001</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T41" t="n">
         <v>0.8072116849233715</v>
@@ -3705,13 +3705,13 @@
         <v>0.9</v>
       </c>
       <c r="P42" t="n">
-        <v>0.68</v>
+        <v>0.49</v>
       </c>
       <c r="Q42" t="n">
         <v>0.35</v>
       </c>
       <c r="R42" t="n">
-        <v>0.7675</v>
+        <v>0.7294999999999999</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -3783,16 +3783,16 @@
         <v>0.74</v>
       </c>
       <c r="P43" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="Q43" t="n">
         <v>0.76</v>
       </c>
       <c r="R43" t="n">
-        <v>0.772</v>
+        <v>0.742</v>
       </c>
       <c r="S43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T43" t="n">
         <v>2.152564493128991</v>
@@ -4797,13 +4797,13 @@
         <v>1</v>
       </c>
       <c r="P56" t="n">
-        <v>0.63</v>
+        <v>0.43</v>
       </c>
       <c r="Q56" t="n">
         <v>0.29</v>
       </c>
       <c r="R56" t="n">
-        <v>0.8194999999999999</v>
+        <v>0.7794999999999999</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
@@ -4875,13 +4875,13 @@
         <v>0.88</v>
       </c>
       <c r="P57" t="n">
-        <v>0.93</v>
+        <v>0.78</v>
       </c>
       <c r="Q57" t="n">
         <v>0.64</v>
       </c>
       <c r="R57" t="n">
-        <v>0.869</v>
+        <v>0.839</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
@@ -4953,13 +4953,13 @@
         <v>0.77</v>
       </c>
       <c r="P58" t="n">
-        <v>0.96</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q58" t="n">
         <v>0.85</v>
       </c>
       <c r="R58" t="n">
-        <v>0.841</v>
+        <v>0.8109999999999999</v>
       </c>
       <c r="S58" t="n">
         <v>2</v>

--- a/workbooks/scenarios/ShowerRAGScenarios.xlsx
+++ b/workbooks/scenarios/ShowerRAGScenarios.xlsx
@@ -669,7 +669,7 @@
         <v>0.76</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8190000000000001</v>
+        <v>0.819</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -747,7 +747,7 @@
         <v>0.67</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6715000000000001</v>
+        <v>0.6715</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -903,7 +903,7 @@
         <v>0.46</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7149999999999999</v>
+        <v>0.715</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
@@ -1137,7 +1137,7 @@
         <v>0.5</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7324999999999999</v>
+        <v>0.7325</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
@@ -1215,7 +1215,7 @@
         <v>0.85</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7064999999999999</v>
+        <v>0.7065</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1683,7 +1683,7 @@
         <v>0.15</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6539999999999999</v>
+        <v>0.654</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -1761,7 +1761,7 @@
         <v>0.22</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7729999999999999</v>
+        <v>0.773</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2619,7 +2619,7 @@
         <v>0.31</v>
       </c>
       <c r="R28" t="n">
-        <v>0.6729999999999999</v>
+        <v>0.673</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -2931,7 +2931,7 @@
         <v>0.22</v>
       </c>
       <c r="R32" t="n">
-        <v>0.7529999999999999</v>
+        <v>0.753</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3087,7 +3087,7 @@
         <v>0.46</v>
       </c>
       <c r="R34" t="n">
-        <v>0.6539999999999999</v>
+        <v>0.654</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -3165,7 +3165,7 @@
         <v>0.22</v>
       </c>
       <c r="R35" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -3243,7 +3243,7 @@
         <v>0.35</v>
       </c>
       <c r="R36" t="n">
-        <v>0.7905000000000001</v>
+        <v>0.7905</v>
       </c>
       <c r="S36" t="n">
         <v>2</v>
@@ -3399,7 +3399,7 @@
         <v>0.29</v>
       </c>
       <c r="R38" t="n">
-        <v>0.7625000000000001</v>
+        <v>0.7625</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -3633,7 +3633,7 @@
         <v>0.22</v>
       </c>
       <c r="R41" t="n">
-        <v>0.7380000000000001</v>
+        <v>0.738</v>
       </c>
       <c r="S41" t="n">
         <v>2</v>
@@ -3711,7 +3711,7 @@
         <v>0.35</v>
       </c>
       <c r="R42" t="n">
-        <v>0.7294999999999999</v>
+        <v>0.7295</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -3867,7 +3867,7 @@
         <v>0.22</v>
       </c>
       <c r="R44" t="n">
-        <v>0.7529999999999999</v>
+        <v>0.753</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -4023,7 +4023,7 @@
         <v>0.46</v>
       </c>
       <c r="R46" t="n">
-        <v>0.6539999999999999</v>
+        <v>0.654</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
@@ -4101,7 +4101,7 @@
         <v>0.22</v>
       </c>
       <c r="R47" t="n">
-        <v>0.7729999999999999</v>
+        <v>0.773</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -4335,7 +4335,7 @@
         <v>0.22</v>
       </c>
       <c r="R50" t="n">
-        <v>0.7589999999999999</v>
+        <v>0.759</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -4491,7 +4491,7 @@
         <v>0.46</v>
       </c>
       <c r="R52" t="n">
-        <v>0.6799999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="S52" t="n">
         <v>3</v>
@@ -4569,7 +4569,7 @@
         <v>0.15</v>
       </c>
       <c r="R53" t="n">
-        <v>0.6329999999999999</v>
+        <v>0.633</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -4803,7 +4803,7 @@
         <v>0.29</v>
       </c>
       <c r="R56" t="n">
-        <v>0.7794999999999999</v>
+        <v>0.7795</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
@@ -4959,7 +4959,7 @@
         <v>0.85</v>
       </c>
       <c r="R58" t="n">
-        <v>0.8109999999999999</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="S58" t="n">
         <v>2</v>
@@ -5037,7 +5037,7 @@
         <v>0.15</v>
       </c>
       <c r="R59" t="n">
-        <v>0.6839999999999999</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -5115,7 +5115,7 @@
         <v>0.46</v>
       </c>
       <c r="R60" t="n">
-        <v>0.6379999999999999</v>
+        <v>0.638</v>
       </c>
       <c r="S60" t="n">
         <v>2</v>
@@ -5193,7 +5193,7 @@
         <v>0.67</v>
       </c>
       <c r="R61" t="n">
-        <v>0.4985000000000001</v>
+        <v>0.4985</v>
       </c>
       <c r="S61" t="n">
         <v>3</v>

--- a/workbooks/scenarios/ShowerRAGScenarios.xlsx
+++ b/workbooks/scenarios/ShowerRAGScenarios.xlsx
@@ -597,10 +597,10 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.06147102298792</v>
+        <v>0.9765533411488861</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2016794943677048</v>
+        <v>0.1855451348182884</v>
       </c>
       <c r="V2" t="n">
         <v>10</v>
@@ -675,10 +675,10 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.698353636780672</v>
+        <v>1.562485345838218</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3226871909883277</v>
+        <v>0.2968722157092614</v>
       </c>
       <c r="V3" t="n">
         <v>16</v>
@@ -753,10 +753,10 @@
         <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.547530455171008</v>
+        <v>2.343728018757327</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4840307864824915</v>
+        <v>0.4453083235638921</v>
       </c>
       <c r="V4" t="n">
         <v>24</v>
@@ -831,10 +831,10 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3268387787349</v>
+        <v>1.220691676436108</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2520993679596309</v>
+        <v>0.2319314185228604</v>
       </c>
       <c r="V5" t="n">
         <v>12.5</v>
@@ -909,10 +909,10 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>2.12294204597584</v>
+        <v>1.953106682297772</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4033589887354095</v>
+        <v>0.3710902696365768</v>
       </c>
       <c r="V6" t="n">
         <v>20</v>
@@ -969,7 +969,7 @@
         <v>12</v>
       </c>
       <c r="N7" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="O7" t="n">
         <v>0.38</v>
@@ -981,16 +981,16 @@
         <v>0.67</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5765</v>
+        <v>0.5825</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>3.18441306896376</v>
+        <v>2.929660023446659</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6050384831031144</v>
+        <v>0.5566354044548653</v>
       </c>
       <c r="V7" t="n">
         <v>30</v>
@@ -1065,10 +1065,10 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1.115778842768697</v>
+        <v>1.043845666931795</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2119979801260525</v>
+        <v>0.198330676717041</v>
       </c>
       <c r="V8" t="n">
         <v>8</v>
@@ -1143,10 +1143,10 @@
         <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.673668264153046</v>
+        <v>1.565768500397692</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3179969701890787</v>
+        <v>0.2974960150755615</v>
       </c>
       <c r="V9" t="n">
         <v>12</v>
@@ -1221,10 +1221,10 @@
         <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.789447106921743</v>
+        <v>2.609614167329487</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5299949503151312</v>
+        <v>0.4958266917926026</v>
       </c>
       <c r="V10" t="n">
         <v>20</v>
@@ -1299,10 +1299,10 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.916444458800617</v>
+        <v>0.8509510795479465</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1741244471721172</v>
+        <v>0.1616807051141098</v>
       </c>
       <c r="V11" t="n">
         <v>7.5</v>
@@ -1377,10 +1377,10 @@
         <v>2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.527407431334362</v>
+        <v>1.418251799246577</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2902074119535287</v>
+        <v>0.2694678418568497</v>
       </c>
       <c r="V12" t="n">
         <v>12.5</v>
@@ -1455,10 +1455,10 @@
         <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.443851890134979</v>
+        <v>2.269202878794524</v>
       </c>
       <c r="U13" t="n">
-        <v>0.464331859125646</v>
+        <v>0.4311485469709595</v>
       </c>
       <c r="V13" t="n">
         <v>20</v>
@@ -1533,10 +1533,10 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1.010866009101286</v>
+        <v>0.9336069641199739</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1920645417292444</v>
+        <v>0.177385323182795</v>
       </c>
       <c r="V14" t="n">
         <v>9</v>
@@ -1593,7 +1593,7 @@
         <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="O15" t="n">
         <v>0.85</v>
@@ -1605,16 +1605,16 @@
         <v>0.29</v>
       </c>
       <c r="R15" t="n">
-        <v>0.729</v>
+        <v>0.732</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>1.347821345468382</v>
+        <v>1.244809285493299</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2560860556389926</v>
+        <v>0.2365137642437267</v>
       </c>
       <c r="V15" t="n">
         <v>12</v>
@@ -1680,19 +1680,19 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="R16" t="n">
-        <v>0.654</v>
+        <v>0.7065</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.021732018202572</v>
+        <v>1.867213928239948</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3841290834584888</v>
+        <v>0.3547706463655901</v>
       </c>
       <c r="V16" t="n">
         <v>18</v>
@@ -1767,10 +1767,10 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>0.955323920689128</v>
+        <v>0.8995966919822622</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1815115449309343</v>
+        <v>0.1709233714766298</v>
       </c>
       <c r="V17" t="n">
         <v>6</v>
@@ -1845,10 +1845,10 @@
         <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>1.59220653448188</v>
+        <v>1.499327819970437</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3025192415515572</v>
+        <v>0.2848722857943831</v>
       </c>
       <c r="V18" t="n">
         <v>10</v>
@@ -1905,7 +1905,7 @@
         <v>8</v>
       </c>
       <c r="N19" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="O19" t="n">
         <v>0.74</v>
@@ -1917,16 +1917,16 @@
         <v>0.76</v>
       </c>
       <c r="R19" t="n">
-        <v>0.745</v>
+        <v>0.742</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.547530455171008</v>
+        <v>2.398924511952699</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4840307864824915</v>
+        <v>0.4557956572710128</v>
       </c>
       <c r="V19" t="n">
         <v>16</v>
@@ -2001,10 +2001,10 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>0.916444458800617</v>
+        <v>0.8509510795479465</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1741244471721172</v>
+        <v>0.1616807051141098</v>
       </c>
       <c r="V20" t="n">
         <v>7.5</v>
@@ -2079,10 +2079,10 @@
         <v>2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.527407431334362</v>
+        <v>1.418251799246577</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2902074119535287</v>
+        <v>0.2694678418568497</v>
       </c>
       <c r="V21" t="n">
         <v>12.5</v>
@@ -2157,10 +2157,10 @@
         <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>2.443851890134979</v>
+        <v>2.269202878794524</v>
       </c>
       <c r="U22" t="n">
-        <v>0.464331859125646</v>
+        <v>0.4311485469709595</v>
       </c>
       <c r="V22" t="n">
         <v>20</v>
@@ -2235,10 +2235,10 @@
         <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>0.636882613792752</v>
+        <v>0.5859320046893317</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1210076966206229</v>
+        <v>0.111327080890973</v>
       </c>
       <c r="V23" t="n">
         <v>6</v>
@@ -2313,10 +2313,10 @@
         <v>2</v>
       </c>
       <c r="T24" t="n">
-        <v>1.06147102298792</v>
+        <v>0.9765533411488861</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2016794943677048</v>
+        <v>0.1855451348182884</v>
       </c>
       <c r="V24" t="n">
         <v>10</v>
@@ -2391,10 +2391,10 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1.698353636780672</v>
+        <v>1.562485345838218</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3226871909883277</v>
+        <v>0.2968722157092614</v>
       </c>
       <c r="V25" t="n">
         <v>16</v>
@@ -2469,10 +2469,10 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>0.9812435619481353</v>
+        <v>0.9147781961482522</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1864362767701457</v>
+        <v>0.1738078572681679</v>
       </c>
       <c r="V26" t="n">
         <v>7.5</v>
@@ -2547,10 +2547,10 @@
         <v>2</v>
       </c>
       <c r="T27" t="n">
-        <v>1.635405936580226</v>
+        <v>1.524630326913754</v>
       </c>
       <c r="U27" t="n">
-        <v>0.3107271279502429</v>
+        <v>0.2896797621136132</v>
       </c>
       <c r="V27" t="n">
         <v>12.5</v>
@@ -2607,7 +2607,7 @@
         <v>7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="O28" t="n">
         <v>0.71</v>
@@ -2619,16 +2619,16 @@
         <v>0.31</v>
       </c>
       <c r="R28" t="n">
-        <v>0.673</v>
+        <v>0.676</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.289568311212316</v>
+        <v>2.134482457679255</v>
       </c>
       <c r="U28" t="n">
-        <v>0.43501797913034</v>
+        <v>0.4055516669590585</v>
       </c>
       <c r="V28" t="n">
         <v>17.5</v>
@@ -2703,10 +2703,10 @@
         <v>3</v>
       </c>
       <c r="T29" t="n">
-        <v>0.7331555670404936</v>
+        <v>0.6807608636383572</v>
       </c>
       <c r="U29" t="n">
-        <v>0.1392995577376938</v>
+        <v>0.1293445640912879</v>
       </c>
       <c r="V29" t="n">
         <v>6</v>
@@ -2781,10 +2781,10 @@
         <v>2</v>
       </c>
       <c r="T30" t="n">
-        <v>1.221925945067489</v>
+        <v>1.134601439397262</v>
       </c>
       <c r="U30" t="n">
-        <v>0.232165929562823</v>
+        <v>0.2155742734854798</v>
       </c>
       <c r="V30" t="n">
         <v>10</v>
@@ -2859,10 +2859,10 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>1.955081512107983</v>
+        <v>1.815362303035619</v>
       </c>
       <c r="U31" t="n">
-        <v>0.3714654873005167</v>
+        <v>0.3449188375767677</v>
       </c>
       <c r="V31" t="n">
         <v>16</v>
@@ -2937,10 +2937,10 @@
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>1.046042665095654</v>
+        <v>0.9786053127485578</v>
       </c>
       <c r="U32" t="n">
-        <v>0.1987481063681742</v>
+        <v>0.185935009422226</v>
       </c>
       <c r="V32" t="n">
         <v>7.5</v>
@@ -3015,10 +3015,10 @@
         <v>2</v>
       </c>
       <c r="T33" t="n">
-        <v>1.743404441826089</v>
+        <v>1.63100885458093</v>
       </c>
       <c r="U33" t="n">
-        <v>0.331246843946957</v>
+        <v>0.3098916823703767</v>
       </c>
       <c r="V33" t="n">
         <v>12.5</v>
@@ -3093,10 +3093,10 @@
         <v>3</v>
       </c>
       <c r="T34" t="n">
-        <v>2.789447106921743</v>
+        <v>2.609614167329487</v>
       </c>
       <c r="U34" t="n">
-        <v>0.5299949503151312</v>
+        <v>0.4958266917926026</v>
       </c>
       <c r="V34" t="n">
         <v>20</v>
@@ -3171,10 +3171,10 @@
         <v>3</v>
       </c>
       <c r="T35" t="n">
-        <v>0.6739106727341909</v>
+        <v>0.6224046427466493</v>
       </c>
       <c r="U35" t="n">
-        <v>0.1280430278194963</v>
+        <v>0.1182568821218634</v>
       </c>
       <c r="V35" t="n">
         <v>6</v>
@@ -3249,10 +3249,10 @@
         <v>2</v>
       </c>
       <c r="T36" t="n">
-        <v>1.123184454556985</v>
+        <v>1.037341071244415</v>
       </c>
       <c r="U36" t="n">
-        <v>0.2134050463658271</v>
+        <v>0.1970948035364389</v>
       </c>
       <c r="V36" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
         <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>1.572458236379779</v>
+        <v>1.452277499742181</v>
       </c>
       <c r="U37" t="n">
-        <v>0.298767064912158</v>
+        <v>0.2759327249510145</v>
       </c>
       <c r="V37" t="n">
         <v>14</v>
@@ -3405,10 +3405,10 @@
         <v>3</v>
       </c>
       <c r="T38" t="n">
-        <v>0.9108902499594012</v>
+        <v>0.8558295263134812</v>
       </c>
       <c r="U38" t="n">
-        <v>0.1730691474922862</v>
+        <v>0.1626076099995614</v>
       </c>
       <c r="V38" t="n">
         <v>6</v>
@@ -3483,10 +3483,10 @@
         <v>2</v>
       </c>
       <c r="T39" t="n">
-        <v>1.366335374939102</v>
+        <v>1.283744289470222</v>
       </c>
       <c r="U39" t="n">
-        <v>0.2596037212384293</v>
+        <v>0.2439114149993421</v>
       </c>
       <c r="V39" t="n">
         <v>9</v>
@@ -3561,10 +3561,10 @@
         <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>2.277225624898503</v>
+        <v>2.139573815783703</v>
       </c>
       <c r="U40" t="n">
-        <v>0.4326728687307156</v>
+        <v>0.4065190249989036</v>
       </c>
       <c r="V40" t="n">
         <v>15</v>
@@ -3639,10 +3639,10 @@
         <v>2</v>
       </c>
       <c r="T41" t="n">
-        <v>0.8072116849233715</v>
+        <v>0.7537061397529922</v>
       </c>
       <c r="U41" t="n">
-        <v>0.1533702201354406</v>
+        <v>0.1432041665530685</v>
       </c>
       <c r="V41" t="n">
         <v>6</v>
@@ -3717,10 +3717,10 @@
         <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>1.345352808205619</v>
+        <v>1.25617689958832</v>
       </c>
       <c r="U42" t="n">
-        <v>0.2556170335590677</v>
+        <v>0.2386736109217809</v>
       </c>
       <c r="V42" t="n">
         <v>10</v>
@@ -3795,10 +3795,10 @@
         <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>2.152564493128991</v>
+        <v>2.009883039341312</v>
       </c>
       <c r="U43" t="n">
-        <v>0.4089872536945083</v>
+        <v>0.3818777774748494</v>
       </c>
       <c r="V43" t="n">
         <v>16</v>
@@ -3873,10 +3873,10 @@
         <v>1</v>
       </c>
       <c r="T44" t="n">
-        <v>1.046042665095654</v>
+        <v>0.9786053127485578</v>
       </c>
       <c r="U44" t="n">
-        <v>0.1987481063681742</v>
+        <v>0.185935009422226</v>
       </c>
       <c r="V44" t="n">
         <v>7.5</v>
@@ -3951,10 +3951,10 @@
         <v>2</v>
       </c>
       <c r="T45" t="n">
-        <v>1.743404441826089</v>
+        <v>1.63100885458093</v>
       </c>
       <c r="U45" t="n">
-        <v>0.331246843946957</v>
+        <v>0.3098916823703767</v>
       </c>
       <c r="V45" t="n">
         <v>12.5</v>
@@ -4029,10 +4029,10 @@
         <v>3</v>
       </c>
       <c r="T46" t="n">
-        <v>2.789447106921743</v>
+        <v>2.609614167329487</v>
       </c>
       <c r="U46" t="n">
-        <v>0.5299949503151312</v>
+        <v>0.4958266917926026</v>
       </c>
       <c r="V46" t="n">
         <v>20</v>
@@ -4107,10 +4107,10 @@
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>0.9331070853242645</v>
+        <v>0.8777131091478716</v>
       </c>
       <c r="U47" t="n">
-        <v>0.1772903462116102</v>
+        <v>0.1667654907380956</v>
       </c>
       <c r="V47" t="n">
         <v>6</v>
@@ -4185,10 +4185,10 @@
         <v>2</v>
       </c>
       <c r="T48" t="n">
-        <v>1.555178475540441</v>
+        <v>1.462855181913119</v>
       </c>
       <c r="U48" t="n">
-        <v>0.2954839103526837</v>
+        <v>0.2779424845634927</v>
       </c>
       <c r="V48" t="n">
         <v>10</v>
@@ -4263,10 +4263,10 @@
         <v>3</v>
       </c>
       <c r="T49" t="n">
-        <v>2.488285560864705</v>
+        <v>2.340568291060991</v>
       </c>
       <c r="U49" t="n">
-        <v>0.472774256564294</v>
+        <v>0.4447079753015883</v>
       </c>
       <c r="V49" t="n">
         <v>16</v>
@@ -4341,10 +4341,10 @@
         <v>1</v>
       </c>
       <c r="T50" t="n">
-        <v>0.9349584882713364</v>
+        <v>0.8691873985766052</v>
       </c>
       <c r="U50" t="n">
-        <v>0.1776421127715539</v>
+        <v>0.165145605729555</v>
       </c>
       <c r="V50" t="n">
         <v>7.5</v>
@@ -4401,7 +4401,7 @@
         <v>5</v>
       </c>
       <c r="N51" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="O51" t="n">
         <v>0.83</v>
@@ -4413,16 +4413,16 @@
         <v>0.35</v>
       </c>
       <c r="R51" t="n">
-        <v>0.735</v>
+        <v>0.738</v>
       </c>
       <c r="S51" t="n">
         <v>2</v>
       </c>
       <c r="T51" t="n">
-        <v>1.558264147118894</v>
+        <v>1.448645664294342</v>
       </c>
       <c r="U51" t="n">
-        <v>0.2960701879525898</v>
+        <v>0.275242676215925</v>
       </c>
       <c r="V51" t="n">
         <v>12.5</v>
@@ -4497,10 +4497,10 @@
         <v>3</v>
       </c>
       <c r="T52" t="n">
-        <v>2.49322263539023</v>
+        <v>2.317833062870947</v>
       </c>
       <c r="U52" t="n">
-        <v>0.4737123007241438</v>
+        <v>0.44038828194548</v>
       </c>
       <c r="V52" t="n">
         <v>20</v>
@@ -4557,7 +4557,7 @@
         <v>4</v>
       </c>
       <c r="N53" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="O53" t="n">
         <v>0.79</v>
@@ -4569,16 +4569,16 @@
         <v>0.15</v>
       </c>
       <c r="R53" t="n">
-        <v>0.633</v>
+        <v>0.63</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
       </c>
       <c r="T53" t="n">
-        <v>2.229089148274632</v>
+        <v>2.099058947958611</v>
       </c>
       <c r="U53" t="n">
-        <v>0.4235269381721801</v>
+        <v>0.3988212001121362</v>
       </c>
       <c r="V53" t="n">
         <v>14</v>
@@ -4653,10 +4653,10 @@
         <v>2</v>
       </c>
       <c r="T54" t="n">
-        <v>3.343633722411948</v>
+        <v>3.148588421937917</v>
       </c>
       <c r="U54" t="n">
-        <v>0.6352904072582701</v>
+        <v>0.5982318001682043</v>
       </c>
       <c r="V54" t="n">
         <v>21</v>
@@ -4731,10 +4731,10 @@
         <v>3</v>
       </c>
       <c r="T55" t="n">
-        <v>4.458178296549264</v>
+        <v>4.198117895917223</v>
       </c>
       <c r="U55" t="n">
-        <v>0.8470538763443601</v>
+        <v>0.7976424002242724</v>
       </c>
       <c r="V55" t="n">
         <v>28</v>
@@ -4809,10 +4809,10 @@
         <v>3</v>
       </c>
       <c r="T56" t="n">
-        <v>0.6368826137927521</v>
+        <v>0.5859320046893317</v>
       </c>
       <c r="U56" t="n">
-        <v>0.1210076966206229</v>
+        <v>0.111327080890973</v>
       </c>
       <c r="V56" t="n">
         <v>6</v>
@@ -4887,10 +4887,10 @@
         <v>1</v>
       </c>
       <c r="T57" t="n">
-        <v>1.114544574137316</v>
+        <v>1.025381008206331</v>
       </c>
       <c r="U57" t="n">
-        <v>0.2117634690860901</v>
+        <v>0.1948223915592028</v>
       </c>
       <c r="V57" t="n">
         <v>10.5</v>
@@ -4965,10 +4965,10 @@
         <v>2</v>
       </c>
       <c r="T58" t="n">
-        <v>1.59220653448188</v>
+        <v>1.464830011723329</v>
       </c>
       <c r="U58" t="n">
-        <v>0.3025192415515572</v>
+        <v>0.2783177022274326</v>
       </c>
       <c r="V58" t="n">
         <v>15</v>
@@ -5025,7 +5025,7 @@
         <v>5</v>
       </c>
       <c r="N59" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="O59" t="n">
         <v>0.83</v>
@@ -5037,16 +5037,16 @@
         <v>0.15</v>
       </c>
       <c r="R59" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.681</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
       </c>
       <c r="T59" t="n">
-        <v>1.86683130496422</v>
+        <v>1.752584314771988</v>
       </c>
       <c r="U59" t="n">
-        <v>0.3546979479432018</v>
+        <v>0.3329910198066777</v>
       </c>
       <c r="V59" t="n">
         <v>12.5</v>
@@ -5121,10 +5121,10 @@
         <v>2</v>
       </c>
       <c r="T60" t="n">
-        <v>2.986930087942751</v>
+        <v>2.80413490363518</v>
       </c>
       <c r="U60" t="n">
-        <v>0.5675167167091227</v>
+        <v>0.5327856316906843</v>
       </c>
       <c r="V60" t="n">
         <v>20</v>
@@ -5199,10 +5199,10 @@
         <v>3</v>
       </c>
       <c r="T61" t="n">
-        <v>4.480395131914127</v>
+        <v>4.206202355452771</v>
       </c>
       <c r="U61" t="n">
-        <v>0.8512750750636842</v>
+        <v>0.7991784475360264</v>
       </c>
       <c r="V61" t="n">
         <v>30</v>
